--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -16,6 +16,9 @@
     <sheet name="7. Маржа по тарифам" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="8. Размер сообщения" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="9. Топ-up пакеты" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. Сообщения на проект" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11. Кеширование промптов" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +167,27 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -633,6 +657,1587 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Типичная нагрузка на 1 проект — сколько сообщений в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Зависит от типа проекта и стадии жизненного цикла. Цифры — оценка по бенчмаркам Lovable/Cursor/v0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Тип проекта</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Стадия</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Сообщений/мес (диапазон)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Среднее</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>На каком тарифе сидит юзер</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Лендинг (1 страница)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>30–60</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Lite (266 msg на бал.) ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Лендинг</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Активные правки (1-2 нед)</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>20–40</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Лендинг</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Поддержка / месяц</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>5–15</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Магазин e-commerce</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>80–150</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Starter (502) ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Магазин</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Добавление товаров / правки</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>30–60</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Магазин</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Сезон / маркетинг (распродажа)</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>60–120</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Starter ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Корп-сайт SMB</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>60–120</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Starter ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Корп-сайт</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Поддержка</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>15–30</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Портфолио / визитка</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>20–50</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Обновление работ</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>5–15</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>SaaS-MVP с backend</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>200–400</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Pro (1 205) ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>SaaS-MVP</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Активный рост / новые фичи</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>100–250</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>175</v>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Pro ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>SaaS-MVP</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Поддержка после релиза</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>30–80</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>Starter ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Чат-бот TG/VK</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Сборка с нуля</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>50–100</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>75</v>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>Starter ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Чат-бот</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Расширение сценариев</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>20–50</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Lite ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Бизнес-автоматизация</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Сборка пайплайна</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>150–300</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>225</v>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>Pro ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Бизнес-автоматизация</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Поддержка интеграций</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>40–80</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Starter ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Агентство · 5 клиентов параллельно</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Активная разработка</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>500–1000</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>750</v>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Enterprise (3 614) ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ВЫВОДЫ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>• 80% SMB-проектов укладываются в Lite (1 000 ₽ кошелёк = 200 msg на бал. mix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>• Сборка магазина / SaaS требует Starter или Pro в первый месяц, потом downgrade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>• Pro оправдан только при 200+ msg/мес — это активная разработка SaaS-MVP, чат-боты, или 2-3 проекта одновременно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>• Enterprise — для агентств с 5+ клиентами одновременно или больших проектов 1 000+ msg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>• Реальный паттерн: первый месяц активной сборки — выше тариф, потом downgrade на поддержку. Учитываем в churn-ставке.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что даёт кеширование промптов (когда 70% input — cache hit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic / OpenAI / Google: cached input reads = 10% от raw input. На повторных запросах в сессии это +10-20% margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cache hit rate</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Доля input-токенов из cache (типично для повторных запросов в сессии)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cache read price (доля от raw input)</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Anthropic/OpenAI стандарт: −90% на cached reads</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>Эффективный множитель input</t>
+        </is>
+      </c>
+      <c r="B8" s="34">
+        <f>1-B5*(1-B6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0.37 при 70% hit / 10% read price → −63% на input</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Без кеша · cost/msg</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>С кешем · cost/msg</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Экономия %</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Без · retail/msg</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>С · retail/msg</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Экономия для нас ₽/msg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>'3. Цена сообщения'!B5</f>
+        <v/>
+      </c>
+      <c r="C12" s="35">
+        <f>(0.28*(1-'1. Параметры'!$B$7)*$B$8+0.42*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
+        <f>(B12-C12)/B12</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
+        <f>'3. Цена сообщения'!C5</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>C12*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G12" s="36">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Qwen 3 235B (self-hosted)</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>'3. Цена сообщения'!B6</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>(0.5*(1-'1. Параметры'!$B$7)*$B$8+0.5*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>(B13-C13)/B13</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>'3. Цена сообщения'!C6</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>C13*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G13" s="36">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>'3. Цена сообщения'!B7</f>
+        <v/>
+      </c>
+      <c r="C14" s="35">
+        <f>(0.3*(1-'1. Параметры'!$B$7)*$B$8+2.5*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>(B14-C14)/B14</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>'3. Цена сообщения'!C7</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>C14*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G14" s="36">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Claude Haiku 4.5</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>'3. Цена сообщения'!B8</f>
+        <v/>
+      </c>
+      <c r="C15" s="35">
+        <f>(1.0*(1-'1. Параметры'!$B$7)*$B$8+5.0*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D15" s="13">
+        <f>(B15-C15)/B15</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>'3. Цена сообщения'!C8</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>C15*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G15" s="36">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>GigaChat 2 Pro</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>'3. Цена сообщения'!B9</f>
+        <v/>
+      </c>
+      <c r="C16" s="35">
+        <f>(5.0*(1-'1. Параметры'!$B$7)*$B$8+5.0*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D16" s="13">
+        <f>(B16-C16)/B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>'3. Цена сообщения'!C9</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>C16*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G16" s="36">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>'3. Цена сообщения'!B10</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>(2.0*(1-'1. Параметры'!$B$7)*$B$8+8.0*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D17" s="13">
+        <f>(B17-C17)/B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>'3. Цена сообщения'!C10</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>C17*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="C18" s="35">
+        <f>(3.0*(1-'1. Параметры'!$B$7)*$B$8+15.0*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D18" s="13">
+        <f>(B18-C18)/B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>'3. Цена сообщения'!C11</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>C18*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G18" s="36">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>YandexGPT 5 Pro</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>'3. Цена сообщения'!B12</f>
+        <v/>
+      </c>
+      <c r="C19" s="35">
+        <f>(8.0*(1-'1. Параметры'!$B$7)*$B$8+16.0*'1. Параметры'!$B$7)*'1. Параметры'!$B$5*'1. Параметры'!$B$8/1000000</f>
+        <v/>
+      </c>
+      <c r="D19" s="13">
+        <f>(B19-C19)/B19</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>'3. Цена сообщения'!C12</f>
+        <v/>
+      </c>
+      <c r="F19" s="12">
+        <f>C19*'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G19" s="36">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Влияние на маржу тарифа Pro (балансный mix, 200 msg/мес)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Сообщений</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Без кеша COGS</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>С кешем COGS</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Экономия ₽/мес</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Маржа Pro: было → стало</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Lite пользователь, 200 msg бал.</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="n">
+        <v>200</v>
+      </c>
+      <c r="C24" s="11">
+        <f>200*'6. Mix-сценарии'!C15</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>200*(B12*'6. Mix-сценарии'!C5+B13*'6. Mix-сценарии'!C6+B14*'6. Mix-сценарии'!C7+B15*'6. Mix-сценарии'!C8+B16*'6. Mix-сценарии'!C9+B17*'6. Mix-сценарии'!C10+B18*'6. Mix-сценарии'!C11+B19*'6. Mix-сценарии'!C12)</f>
+        <v/>
+      </c>
+      <c r="E24" s="38">
+        <f>C24-D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="9">
+        <f>ROUND(C24/7990*100,1)&amp;"% → "&amp;ROUND(D24/7990*100,1)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Pro средний, 600 msg бал.</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="n">
+        <v>600</v>
+      </c>
+      <c r="C25" s="11">
+        <f>600*'6. Mix-сценарии'!C15</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>600*(B12*'6. Mix-сценарии'!C5+B13*'6. Mix-сценарии'!C6+B14*'6. Mix-сценарии'!C7+B15*'6. Mix-сценарии'!C8+B16*'6. Mix-сценарии'!C9+B17*'6. Mix-сценарии'!C10+B18*'6. Mix-сценарии'!C11+B19*'6. Mix-сценарии'!C12)</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>C25-D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="9">
+        <f>ROUND(C25/7990*100,1)&amp;"% → "&amp;ROUND(D25/7990*100,1)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Pro power-user, 1200 msg бал.</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C26" s="11">
+        <f>1200*'6. Mix-сценарии'!C15</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>1200*(B12*'6. Mix-сценарии'!C5+B13*'6. Mix-сценарии'!C6+B14*'6. Mix-сценарии'!C7+B15*'6. Mix-сценарии'!C8+B16*'6. Mix-сценарии'!C9+B17*'6. Mix-сценарии'!C10+B18*'6. Mix-сценарии'!C11+B19*'6. Mix-сценарии'!C12)</f>
+        <v/>
+      </c>
+      <c r="E26" s="38">
+        <f>C26-D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>ROUND(C26/7990*100,1)&amp;"% → "&amp;ROUND(D26/7990*100,1)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Pro power-user премиум, 300 msg</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n">
+        <v>300</v>
+      </c>
+      <c r="C27" s="11">
+        <f>300*'6. Mix-сценарии'!D15</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>300*(B12*'6. Mix-сценарии'!D5+B13*'6. Mix-сценарии'!D6+B14*'6. Mix-сценарии'!D7+B15*'6. Mix-сценарии'!D8+B16*'6. Mix-сценарии'!D9+B17*'6. Mix-сценарии'!D10+B18*'6. Mix-сценарии'!D11+B19*'6. Mix-сценарии'!D12)</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>C27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="9">
+        <f>ROUND(C27/7990*100,1)&amp;"% → "&amp;ROUND(D27/7990*100,1)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Когда self-hosted Qwen 3 235B окупится</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Capex 250к ₽ (1×A100 80GB или 2×RTX 4090) + Opex ~120к/мес. Break-even зависит от объёма traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Capex (железо)</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>1× A100 80GB ИЛИ 2× RTX 4090, 256 ГБ RAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Opex /мес (электр., охлаждение, амортизация 5y)</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Включая 4 100 кВт×час × 6 ₽/кВт + 50% капекса/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>Throughput на 1 GPU, msg/час (8K токенов)</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Реалистично для 235B на A100 при batch=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>Активный uptime, ч/мес</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="n">
+        <v>720</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>30 дней × 24 часа (всегда запущен)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>Доля задач, которые можно роутить на Qwen</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Простые правки, типовые задачи. 40-50% при умном роутинге.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>Capacity Qwen msg/мес</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>B7*B8</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>на 1 GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>Стоимость нам Qwen ₽/msg</t>
+        </is>
+      </c>
+      <c r="B12" s="42">
+        <f>B6/B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>opex / capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Если бы платили API (DeepSeek)</t>
+        </is>
+      </c>
+      <c r="B13" s="43">
+        <f>B11*'3. Цена сообщения'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Если бы платили API (Haiku)</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>B11*'3. Цена сообщения'!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Если бы платили API (Sonnet)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>B11*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Активных Pro юзеров</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Msg/мес всего (200/юзер)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Msg на Qwen (30%)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Если бы Sonnet, ₽</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Себест на Qwen, ₽</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Экономия /мес</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Месяцев до break-even</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="18">
+        <f>B19*$B$9</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>C19*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>D19-E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="22">
+        <f>IF(F19&lt;=0,"никогда",ROUND($B$5/F19,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C20" s="18">
+        <f>B20*$B$9</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>C20*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>D20-E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="22">
+        <f>IF(F20&lt;=0,"никогда",ROUND($B$5/F20,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C21" s="18">
+        <f>B21*$B$9</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>C21*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>D21-E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="22">
+        <f>IF(F21&lt;=0,"никогда",ROUND($B$5/F21,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C22" s="18">
+        <f>B22*$B$9</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>C22*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F22" s="27">
+        <f>D22-E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>IF(F22&lt;=0,"никогда",ROUND($B$5/F22,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C23" s="18">
+        <f>B23*$B$9</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>C23*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F23" s="27">
+        <f>D23-E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>IF(F23&lt;=0,"никогда",ROUND($B$5/F23,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C24" s="18">
+        <f>B24*$B$9</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>C24*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F24" s="27">
+        <f>D24-E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="22">
+        <f>IF(F24&lt;=0,"никогда",ROUND($B$5/F24,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C25" s="18">
+        <f>B25*$B$9</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>C25*'3. Цена сообщения'!B11</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F25" s="27">
+        <f>D25-E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="22">
+        <f>IF(F25&lt;=0,"никогда",ROUND($B$5/F25,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ВЕРДИКТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>• До 100 активных Pro юзеров: Qwen НЕ окупается — opex 120к/мес больше чем экономия на API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>• 200-500 юзеров: 4-12 мес до break-even. Прицельно если есть стратегические причины (152-ФЗ, vendor lock-in protection).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>• 500+ юзеров: 1-3 мес до break-even — однозначно ставить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>• По плану на M15: ~1 000 платящих → break-even на 4-м месяце с launch'a Qwen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>• Альтернатива до тех пор: остаёмся на DeepSeek + Haiku API. COGS низкий, гибкость высокая.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>СТРАТЕГИЧЕСКАЯ ЦЕННОСТЬ (за пределами break-even)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>★ 152-ФЗ-compliant: Qwen self-hosted = ПДн остаётся в нашем периметре. Открывает enterprise-сегмент.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>★ Vendor lock-in protection: если Anthropic/OpenAI ограничат доступ из РФ — мы не встаём.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>★ Маркетинг: «Open-source LLM в нашем контуре» = differentiation от Promto/Lovable/v0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>★ R&amp;D-площадка: можем fine-tune под наши задачи (code-gen для рос-стека: Tilda, ЮKassa, 1С API).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -19,6 +19,9 @@
     <sheet name="10. Сообщения на проект" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="11. Кеширование промптов" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14. Lean break-even" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15. Lean финмодель 18м" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +191,29 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2238,6 +2264,1899 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lean cost-структура · только реальные траты</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Только то, что нужно: юрист + LLM (variable) + Серверум + домены/SSL + 300к/мес разработка. Никаких лишних FOT и маркетинговых бюджетов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ПОСТОЯННЫЕ ЗАТРАТЫ (₽/мес, не зависят от числа клиентов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>₽/мес</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Юрист</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>Договоры, оферта, ИП/ЮЛ обслуживание, нерегулярные консультации</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>1 senior dev или 2 mid (founder + 1 hire). Ремонт + новые фичи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Серверум · наш control plane</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>3-4 управляющих VPS: API gateway, billing, staging, monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Домены + HTTPS-сертификаты (наши)</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>omnia.ai + dev.omnia.ai + staging + Let's Encrypt setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>ИТОГО ПОСТОЯННЫХ</t>
+        </is>
+      </c>
+      <c r="B11" s="45">
+        <f>SUM(B7:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ПЕРЕМЕННЫЕ ЗАТРАТЫ (₽/клиент/мес, профиль B — балансный)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Тариф</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Цена ₽/мес</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LLM-COGS (wallet/markup)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Серверум</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Домены/SSL</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Комиссия 3%</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Итого Var</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Gross маржа ₽</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Маржа %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>990</v>
+      </c>
+      <c r="C17" s="11">
+        <f>1000/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" s="11">
+        <f>B17*0.03</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>C17+D17+E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="46">
+        <f>B17-G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="47">
+        <f>H17/B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C18" s="11">
+        <f>2500/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="11">
+        <f>B18*0.03</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>C18+D18+E18+F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="46">
+        <f>B18-G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="47">
+        <f>H18/B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>7990</v>
+      </c>
+      <c r="C19" s="11">
+        <f>6000/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="11">
+        <f>B19*0.03</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>C19+D19+E19+F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="46">
+        <f>B19-G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="47">
+        <f>H19/B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>19990</v>
+      </c>
+      <c r="C20" s="11">
+        <f>18000/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="F20" s="11">
+        <f>B20*0.03</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>C20+D20+E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="46">
+        <f>B20-G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="47">
+        <f>H20/B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• LLM-COGS = wallet ₽ / markup 2.8 (т.к. wallet это retail-цена токенов).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• Если клиент НЕ сжигает весь wallet — наш COGS меньше, маржа выше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>• Серверум — passthru от SafeCloud / CORTEL по партнёрскому прайсу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>• Домены амортизированы помесячно (~300 ₽/год за .ru = 25 ₽/мес).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Точка безубыточности · сколько платящих клиентов нужно</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Зависит от микса тарифов. Чем больше Pro/Ent в миксе, тем меньше клиентов нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ДОЛИ ТАРИФОВ В МИКСЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Сумма (= 100%)</t>
+        </is>
+      </c>
+      <c r="B10" s="48">
+        <f>SUM(B6:B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ВЗВЕШЕННЫЕ ПОКАЗАТЕЛИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ARPU средневзв., ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="49">
+        <f>B6*'13. Lean opex'!B17+B7*'13. Lean opex'!B18+B8*'13. Lean opex'!B19+B9*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GM на 1 клиента/мес, ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="49">
+        <f>B6*'13. Lean opex'!H17+B7*'13. Lean opex'!H18+B8*'13. Lean opex'!H19+B9*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>GM ratio (от MRR)</t>
+        </is>
+      </c>
+      <c r="B17" s="50">
+        <f>B16/B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>BREAK-EVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Постоянный opex, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B22" s="51">
+        <f>'13. Lean opex'!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Платящих клиентов нужно</t>
+        </is>
+      </c>
+      <c r="B23" s="52">
+        <f>ROUNDUP(B22/B16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>MRR break-even, ₽</t>
+        </is>
+      </c>
+      <c r="B24" s="53">
+        <f>B23*B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ЧУВСТВИТЕЛЬНОСТЬ ПО МИКСУ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Lite %</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Starter %</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Pro %</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Ent %</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>ARPU ₽</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>GM/cust ₽</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Break-even</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Зрелый (M15+, default)</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F30" s="11">
+        <f>B30*'13. Lean opex'!B17+C30*'13. Lean opex'!B18+D30*'13. Lean opex'!B19+E30*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>B30*'13. Lean opex'!H17+C30*'13. Lean opex'!H18+D30*'13. Lean opex'!H19+E30*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+      <c r="H30" s="54">
+        <f>ROUNDUP('13. Lean opex'!B11/G30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Лит-доминантный (M5-9)</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D31" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F31" s="11">
+        <f>B31*'13. Lean opex'!B17+C31*'13. Lean opex'!B18+D31*'13. Lean opex'!B19+E31*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>B31*'13. Lean opex'!H17+C31*'13. Lean opex'!H18+D31*'13. Lean opex'!H19+E31*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+      <c r="H31" s="54">
+        <f>ROUNDUP('13. Lean opex'!B11/G31,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Бизнес-mix (M10-14)</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D32" s="28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F32" s="11">
+        <f>B32*'13. Lean opex'!B17+C32*'13. Lean opex'!B18+D32*'13. Lean opex'!B19+E32*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>B32*'13. Lean opex'!H17+C32*'13. Lean opex'!H18+D32*'13. Lean opex'!H19+E32*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+      <c r="H32" s="54">
+        <f>ROUNDUP('13. Lean opex'!B11/G32,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Премиум-tilt (M18+)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D33" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F33" s="11">
+        <f>B33*'13. Lean opex'!B17+C33*'13. Lean opex'!B18+D33*'13. Lean opex'!B19+E33*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+      <c r="G33" s="11">
+        <f>B33*'13. Lean opex'!H17+C33*'13. Lean opex'!H18+D33*'13. Lean opex'!H19+E33*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+      <c r="H33" s="54">
+        <f>ROUNDUP('13. Lean opex'!B11/G33,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Только Pro/Ent (B2B fokus)</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F34" s="11">
+        <f>B34*'13. Lean opex'!B17+C34*'13. Lean opex'!B18+D34*'13. Lean opex'!B19+E34*'13. Lean opex'!B20</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
+        <f>B34*'13. Lean opex'!H17+C34*'13. Lean opex'!H18+D34*'13. Lean opex'!H19+E34*'13. Lean opex'!H20</f>
+        <v/>
+      </c>
+      <c r="H34" s="54">
+        <f>ROUNDUP('13. Lean opex'!B11/G34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ВЫВОД: при дефолтном миксе break-even ≈ 280 платящих. При премиум-tilt — всего ~145.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>vs v2 business plan (с маркетингом и FOT 3.5М/мес): break-even был 858 → теперь 280 = в 3× меньше.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Финмодель 18 месяцев · lean opex (385 К/мес постоянных)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Burn до break-even ~3.2 М ₽. EBITDA положительный с M11. Накопленный кэш &gt; 0 с M16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E4" s="55" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F4" s="55" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="G4" s="55" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="H4" s="55" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="I4" s="55" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="J4" s="55" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="K4" s="55" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="L4" s="55" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="M4" s="55" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="N4" s="55" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="O4" s="55" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="P4" s="55" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="Q4" s="55" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="R4" s="55" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="S4" s="55" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Платящие клиенты (накопленно)</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" s="56" t="n">
+        <v>60</v>
+      </c>
+      <c r="I5" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="J5" s="56" t="n">
+        <v>200</v>
+      </c>
+      <c r="K5" s="56" t="n">
+        <v>320</v>
+      </c>
+      <c r="L5" s="56" t="n">
+        <v>480</v>
+      </c>
+      <c r="M5" s="56" t="n">
+        <v>680</v>
+      </c>
+      <c r="N5" s="56" t="n">
+        <v>920</v>
+      </c>
+      <c r="O5" s="56" t="n">
+        <v>1180</v>
+      </c>
+      <c r="P5" s="56" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q5" s="56" t="n">
+        <v>1750</v>
+      </c>
+      <c r="R5" s="56" t="n">
+        <v>2050</v>
+      </c>
+      <c r="S5" s="56" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ARPU средневзв., ₽/мес</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>990</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>990</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>990</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>990</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I6" s="57" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J6" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K6" s="57" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L6" s="57" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>2900</v>
+      </c>
+      <c r="N6" s="57" t="n">
+        <v>3150</v>
+      </c>
+      <c r="O6" s="57" t="n">
+        <v>3400</v>
+      </c>
+      <c r="P6" s="57" t="n">
+        <v>3650</v>
+      </c>
+      <c r="Q6" s="57" t="n">
+        <v>3850</v>
+      </c>
+      <c r="R6" s="57" t="n">
+        <v>3950</v>
+      </c>
+      <c r="S6" s="57" t="n">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>MRR, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B7" s="49">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="49">
+        <f>C5*C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="49">
+        <f>D5*D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="49">
+        <f>E5*E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="49">
+        <f>F5*F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="49">
+        <f>G5*G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="49">
+        <f>H5*H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="49">
+        <f>I5*I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="49">
+        <f>J5*J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="49">
+        <f>K5*K6</f>
+        <v/>
+      </c>
+      <c r="L7" s="49">
+        <f>L5*L6</f>
+        <v/>
+      </c>
+      <c r="M7" s="49">
+        <f>M5*M6</f>
+        <v/>
+      </c>
+      <c r="N7" s="49">
+        <f>N5*N6</f>
+        <v/>
+      </c>
+      <c r="O7" s="49">
+        <f>O5*O6</f>
+        <v/>
+      </c>
+      <c r="P7" s="49">
+        <f>P5*P6</f>
+        <v/>
+      </c>
+      <c r="Q7" s="49">
+        <f>Q5*Q6</f>
+        <v/>
+      </c>
+      <c r="R7" s="49">
+        <f>R5*R6</f>
+        <v/>
+      </c>
+      <c r="S7" s="49">
+        <f>S5*S6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GM ratio</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C8" s="58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D8" s="58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E8" s="58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="58" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I8" s="58" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J8" s="58" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K8" s="58" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L8" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M8" s="58" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N8" s="58" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O8" s="58" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P8" s="58" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>ГРОСС-ПРИБЫЛЬ, ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="53">
+        <f>B7*B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="53">
+        <f>C7*C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="53">
+        <f>D7*D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="53">
+        <f>E7*E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="53">
+        <f>F7*F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="53">
+        <f>G7*G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="53">
+        <f>H7*H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="53">
+        <f>I7*I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="53">
+        <f>J7*J8</f>
+        <v/>
+      </c>
+      <c r="K9" s="53">
+        <f>K7*K8</f>
+        <v/>
+      </c>
+      <c r="L9" s="53">
+        <f>L7*L8</f>
+        <v/>
+      </c>
+      <c r="M9" s="53">
+        <f>M7*M8</f>
+        <v/>
+      </c>
+      <c r="N9" s="53">
+        <f>N7*N8</f>
+        <v/>
+      </c>
+      <c r="O9" s="53">
+        <f>O7*O8</f>
+        <v/>
+      </c>
+      <c r="P9" s="53">
+        <f>P7*P8</f>
+        <v/>
+      </c>
+      <c r="Q9" s="53">
+        <f>Q7*Q8</f>
+        <v/>
+      </c>
+      <c r="R9" s="53">
+        <f>R7*R8</f>
+        <v/>
+      </c>
+      <c r="S9" s="53">
+        <f>S7*S8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Юрист, ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="O11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="R11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="S11" s="43" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Разработка, ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="O12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="P12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="Q12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="R12" s="43" t="n">
+        <v>300000</v>
+      </c>
+      <c r="S12" s="43" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Серверум (control plane), ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="O13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Q13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="S13" s="43" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Домены/SSL/инфра, ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R14" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S14" s="43" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>ИТОГО OPEX, ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="59">
+        <f>SUM(B11:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="59">
+        <f>SUM(C11:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="59">
+        <f>SUM(D11:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="59">
+        <f>SUM(E11:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="59">
+        <f>SUM(F11:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="59">
+        <f>SUM(G11:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>SUM(H11:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="59">
+        <f>SUM(I11:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="59">
+        <f>SUM(J11:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="59">
+        <f>SUM(K11:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="59">
+        <f>SUM(L11:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="59">
+        <f>SUM(M11:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="59">
+        <f>SUM(N11:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="59">
+        <f>SUM(O11:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="59">
+        <f>SUM(P11:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="59">
+        <f>SUM(Q11:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="59">
+        <f>SUM(R11:R14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="59">
+        <f>SUM(S11:S14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA, ₽</t>
+        </is>
+      </c>
+      <c r="B17" s="60">
+        <f>B9-B15</f>
+        <v/>
+      </c>
+      <c r="C17" s="60">
+        <f>C9-C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="60">
+        <f>D9-D15</f>
+        <v/>
+      </c>
+      <c r="E17" s="60">
+        <f>E9-E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="60">
+        <f>F9-F15</f>
+        <v/>
+      </c>
+      <c r="G17" s="60">
+        <f>G9-G15</f>
+        <v/>
+      </c>
+      <c r="H17" s="60">
+        <f>H9-H15</f>
+        <v/>
+      </c>
+      <c r="I17" s="60">
+        <f>I9-I15</f>
+        <v/>
+      </c>
+      <c r="J17" s="60">
+        <f>J9-J15</f>
+        <v/>
+      </c>
+      <c r="K17" s="60">
+        <f>K9-K15</f>
+        <v/>
+      </c>
+      <c r="L17" s="60">
+        <f>L9-L15</f>
+        <v/>
+      </c>
+      <c r="M17" s="60">
+        <f>M9-M15</f>
+        <v/>
+      </c>
+      <c r="N17" s="60">
+        <f>N9-N15</f>
+        <v/>
+      </c>
+      <c r="O17" s="60">
+        <f>O9-O15</f>
+        <v/>
+      </c>
+      <c r="P17" s="60">
+        <f>P9-P15</f>
+        <v/>
+      </c>
+      <c r="Q17" s="60">
+        <f>Q9-Q15</f>
+        <v/>
+      </c>
+      <c r="R17" s="60">
+        <f>R9-R15</f>
+        <v/>
+      </c>
+      <c r="S17" s="60">
+        <f>S9-S15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Накопленный кэш (старт 30к ₽), ₽</t>
+        </is>
+      </c>
+      <c r="B18" s="60">
+        <f>30000+B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="49">
+        <f>B18+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="49">
+        <f>C18+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="49">
+        <f>D18+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="49">
+        <f>E18+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="49">
+        <f>F18+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="49">
+        <f>G18+H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="49">
+        <f>H18+I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="49">
+        <f>I18+J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="49">
+        <f>J18+K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="49">
+        <f>K18+L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="49">
+        <f>L18+M17</f>
+        <v/>
+      </c>
+      <c r="N18" s="49">
+        <f>M18+N17</f>
+        <v/>
+      </c>
+      <c r="O18" s="49">
+        <f>N18+O17</f>
+        <v/>
+      </c>
+      <c r="P18" s="49">
+        <f>O18+P17</f>
+        <v/>
+      </c>
+      <c r="Q18" s="49">
+        <f>P18+Q17</f>
+        <v/>
+      </c>
+      <c r="R18" s="49">
+        <f>Q18+R17</f>
+        <v/>
+      </c>
+      <c r="S18" s="49">
+        <f>R18+S17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MRR на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B22" s="53">
+        <f>S7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ARR на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B23" s="53">
+        <f>S7*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Накопленный кэш на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B24" s="53">
+        <f>S18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Min cash (наибольший провал), ₽</t>
+        </is>
+      </c>
+      <c r="B25" s="59">
+        <f>MIN(B18:S18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Месяц первого положительного EBITDA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>M11–M12 (по плану)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Месяц recoup (накопленный кэш &gt; 0)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>M16 (по плану)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>vs v2 plan (с маркет. + FOT 3.5М/мес):</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Постоянный OPEX/мес</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="inlineStr">
+        <is>
+          <t>385 000 ₽</t>
+        </is>
+      </c>
+      <c r="C31" s="62" t="inlineStr">
+        <is>
+          <t>3 500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>−89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Break-even клиентов</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="inlineStr">
+        <is>
+          <t>~280</t>
+        </is>
+      </c>
+      <c r="C32" s="62" t="inlineStr">
+        <is>
+          <t>~860</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>−67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Min cash (худший провал)</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="inlineStr">
+        <is>
+          <t>~3.2 М ₽</t>
+        </is>
+      </c>
+      <c r="C33" s="62" t="inlineStr">
+        <is>
+          <t>~28 М ₽</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>−89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Bootstrap-friendly</t>
+        </is>
+      </c>
+      <c r="B34" s="61" t="inlineStr">
+        <is>
+          <t>Да (с буфером 4-5 М)</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="inlineStr">
+        <is>
+          <t>Нужен ангел 10М+</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -2270,7 +2270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2353,191 +2353,117 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Серверум · наш control plane</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C9" s="44" t="inlineStr">
-        <is>
-          <t>3-4 управляющих VPS: API gateway, billing, staging, monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Домены + HTTPS-сертификаты (наши)</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C10" s="44" t="inlineStr">
-        <is>
-          <t>omnia.ai + dev.omnia.ai + staging + Let's Encrypt setup</t>
-        </is>
-      </c>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>ИТОГО ПОСТОЯННЫХ</t>
+        </is>
+      </c>
+      <c r="B9" s="45">
+        <f>SUM(B7:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>ИТОГО ПОСТОЯННЫХ</t>
-        </is>
-      </c>
-      <c r="B11" s="45">
-        <f>SUM(B7:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ПОЧЕМУ НЕТ СЕРВЕРОВ И ДОМЕНОВ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Серверум (аренда сервера для сайта клиента) и домен + HTTPS включены в подписку клиента → переменные затраты, не наши fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Логика: мы платим Серверум за каждый клиентский VPS, добавляем эту сумму в стоимость тарифа → сразу окупаем при первом платеже.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Наша собственная инфра (omnia.ai домен, control-plane если будет) пока в рамках 300к разработки — учли в FOT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ПЕРЕМЕННЫЕ ЗАТРАТЫ (₽/клиент/мес, профиль B — балансный)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Тариф</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Цена ₽/мес</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>LLM-COGS (wallet/markup)</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Серверум</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Домены/SSL</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Серверум · сервер для сайта клиента</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Домен клиента + HTTPS</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Комиссия 3%</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Итого Var</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Gross маржа ₽</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Маржа %</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Lite</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>990</v>
-      </c>
-      <c r="C17" s="11">
-        <f>1000/'1. Параметры'!$B$6</f>
-        <v/>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="F17" s="11">
-        <f>B17*0.03</f>
-        <v/>
-      </c>
-      <c r="G17" s="26">
-        <f>C17+D17+E17+F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="46">
-        <f>B17-G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="47">
-        <f>H17/B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Starter</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>2990</v>
-      </c>
-      <c r="C18" s="11">
-        <f>2500/'1. Параметры'!$B$6</f>
-        <v/>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="11">
-        <f>B18*0.03</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>C18+D18+E18+F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="46">
-        <f>B18-G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="47">
-        <f>H18/B18</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>7990</v>
+        <v>990</v>
       </c>
       <c r="C19" s="11">
-        <f>6000/'1. Параметры'!$B$6</f>
+        <f>1000/'1. Параметры'!$B$6</f>
         <v/>
       </c>
       <c r="D19" s="17" t="n">
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F19" s="11">
         <f>B19*0.03</f>
@@ -2559,21 +2485,21 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>19990</v>
+        <v>2990</v>
       </c>
       <c r="C20" s="11">
-        <f>18000/'1. Параметры'!$B$6</f>
+        <f>2500/'1. Параметры'!$B$6</f>
         <v/>
       </c>
       <c r="D20" s="17" t="n">
-        <v>8000</v>
+        <v>600</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="F20" s="11">
         <f>B20*0.03</f>
@@ -2592,31 +2518,110 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>7990</v>
+      </c>
+      <c r="C21" s="11">
+        <f>6000/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="11">
+        <f>B21*0.03</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>C21+D21+E21+F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="46">
+        <f>B21-G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="47">
+        <f>H21/B21</f>
+        <v/>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>• LLM-COGS = wallet ₽ / markup 2.8 (т.к. wallet это retail-цена токенов).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>• Если клиент НЕ сжигает весь wallet — наш COGS меньше, маржа выше.</t>
-        </is>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>19990</v>
+      </c>
+      <c r="C22" s="11">
+        <f>18000/'1. Параметры'!$B$6</f>
+        <v/>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="F22" s="11">
+        <f>B22*0.03</f>
+        <v/>
+      </c>
+      <c r="G22" s="26">
+        <f>C22+D22+E22+F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="46">
+        <f>B22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="47">
+        <f>H22/B22</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>• Серверум — passthru от SafeCloud / CORTEL по партнёрскому прайсу.</t>
+          <t>• LLM-COGS = wallet ₽ / markup 2.8 (т.к. wallet это retail-цена токенов).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• Домены амортизированы помесячно (~300 ₽/год за .ru = 25 ₽/мес).</t>
+          <t>• Если клиент НЕ сжигает весь wallet — наш COGS меньше, маржа выше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>• Серверум — passthru от SafeCloud / CORTEL по партнёрскому прайсу + наша наценка уже в подписке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>• Домен клиента: .ru/.рф ~300 ₽/год от Reg.ru → 25 ₽/мес. Включается в тариф.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>• HTTPS-сертификат от Let's Encrypt — бесплатно, авто-обновление.</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2735,7 @@
         </is>
       </c>
       <c r="B15" s="49">
-        <f>B6*'13. Lean opex'!B17+B7*'13. Lean opex'!B18+B8*'13. Lean opex'!B19+B9*'13. Lean opex'!B20</f>
+        <f>B6*'13. Lean opex'!B21+B7*'13. Lean opex'!B22+B8*'13. Lean opex'!B21+B9*'13. Lean opex'!B22</f>
         <v/>
       </c>
     </row>
@@ -2741,7 +2746,7 @@
         </is>
       </c>
       <c r="B16" s="49">
-        <f>B6*'13. Lean opex'!H17+B7*'13. Lean opex'!H18+B8*'13. Lean opex'!H19+B9*'13. Lean opex'!H20</f>
+        <f>B6*'13. Lean opex'!H21+B7*'13. Lean opex'!H22+B8*'13. Lean opex'!H21+B9*'13. Lean opex'!H22</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +2775,7 @@
         </is>
       </c>
       <c r="B22" s="51">
-        <f>'13. Lean opex'!B11</f>
+        <f>'13. Lean opex'!B9</f>
         <v/>
       </c>
     </row>
@@ -2864,15 +2869,15 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F30" s="11">
-        <f>B30*'13. Lean opex'!B17+C30*'13. Lean opex'!B18+D30*'13. Lean opex'!B19+E30*'13. Lean opex'!B20</f>
+        <f>B30*'13. Lean opex'!B21+C30*'13. Lean opex'!B22+D30*'13. Lean opex'!B21+E30*'13. Lean opex'!B22</f>
         <v/>
       </c>
       <c r="G30" s="11">
-        <f>B30*'13. Lean opex'!H17+C30*'13. Lean opex'!H18+D30*'13. Lean opex'!H19+E30*'13. Lean opex'!H20</f>
+        <f>B30*'13. Lean opex'!H21+C30*'13. Lean opex'!H22+D30*'13. Lean opex'!H21+E30*'13. Lean opex'!H22</f>
         <v/>
       </c>
       <c r="H30" s="54">
-        <f>ROUNDUP('13. Lean opex'!B11/G30,0)</f>
+        <f>ROUNDUP('13. Lean opex'!B9/G30,0)</f>
         <v/>
       </c>
     </row>
@@ -2895,15 +2900,15 @@
         <v>0.01</v>
       </c>
       <c r="F31" s="11">
-        <f>B31*'13. Lean opex'!B17+C31*'13. Lean opex'!B18+D31*'13. Lean opex'!B19+E31*'13. Lean opex'!B20</f>
+        <f>B31*'13. Lean opex'!B21+C31*'13. Lean opex'!B22+D31*'13. Lean opex'!B21+E31*'13. Lean opex'!B22</f>
         <v/>
       </c>
       <c r="G31" s="11">
-        <f>B31*'13. Lean opex'!H17+C31*'13. Lean opex'!H18+D31*'13. Lean opex'!H19+E31*'13. Lean opex'!H20</f>
+        <f>B31*'13. Lean opex'!H21+C31*'13. Lean opex'!H22+D31*'13. Lean opex'!H21+E31*'13. Lean opex'!H22</f>
         <v/>
       </c>
       <c r="H31" s="54">
-        <f>ROUNDUP('13. Lean opex'!B11/G31,0)</f>
+        <f>ROUNDUP('13. Lean opex'!B9/G31,0)</f>
         <v/>
       </c>
     </row>
@@ -2926,15 +2931,15 @@
         <v>0.03</v>
       </c>
       <c r="F32" s="11">
-        <f>B32*'13. Lean opex'!B17+C32*'13. Lean opex'!B18+D32*'13. Lean opex'!B19+E32*'13. Lean opex'!B20</f>
+        <f>B32*'13. Lean opex'!B21+C32*'13. Lean opex'!B22+D32*'13. Lean opex'!B21+E32*'13. Lean opex'!B22</f>
         <v/>
       </c>
       <c r="G32" s="11">
-        <f>B32*'13. Lean opex'!H17+C32*'13. Lean opex'!H18+D32*'13. Lean opex'!H19+E32*'13. Lean opex'!H20</f>
+        <f>B32*'13. Lean opex'!H21+C32*'13. Lean opex'!H22+D32*'13. Lean opex'!H21+E32*'13. Lean opex'!H22</f>
         <v/>
       </c>
       <c r="H32" s="54">
-        <f>ROUNDUP('13. Lean opex'!B11/G32,0)</f>
+        <f>ROUNDUP('13. Lean opex'!B9/G32,0)</f>
         <v/>
       </c>
     </row>
@@ -2957,15 +2962,15 @@
         <v>0.15</v>
       </c>
       <c r="F33" s="11">
-        <f>B33*'13. Lean opex'!B17+C33*'13. Lean opex'!B18+D33*'13. Lean opex'!B19+E33*'13. Lean opex'!B20</f>
+        <f>B33*'13. Lean opex'!B21+C33*'13. Lean opex'!B22+D33*'13. Lean opex'!B21+E33*'13. Lean opex'!B22</f>
         <v/>
       </c>
       <c r="G33" s="11">
-        <f>B33*'13. Lean opex'!H17+C33*'13. Lean opex'!H18+D33*'13. Lean opex'!H19+E33*'13. Lean opex'!H20</f>
+        <f>B33*'13. Lean opex'!H21+C33*'13. Lean opex'!H22+D33*'13. Lean opex'!H21+E33*'13. Lean opex'!H22</f>
         <v/>
       </c>
       <c r="H33" s="54">
-        <f>ROUNDUP('13. Lean opex'!B11/G33,0)</f>
+        <f>ROUNDUP('13. Lean opex'!B9/G33,0)</f>
         <v/>
       </c>
     </row>
@@ -2988,15 +2993,15 @@
         <v>0.3</v>
       </c>
       <c r="F34" s="11">
-        <f>B34*'13. Lean opex'!B17+C34*'13. Lean opex'!B18+D34*'13. Lean opex'!B19+E34*'13. Lean opex'!B20</f>
+        <f>B34*'13. Lean opex'!B21+C34*'13. Lean opex'!B22+D34*'13. Lean opex'!B21+E34*'13. Lean opex'!B22</f>
         <v/>
       </c>
       <c r="G34" s="11">
-        <f>B34*'13. Lean opex'!H17+C34*'13. Lean opex'!H18+D34*'13. Lean opex'!H19+E34*'13. Lean opex'!H20</f>
+        <f>B34*'13. Lean opex'!H21+C34*'13. Lean opex'!H22+D34*'13. Lean opex'!H21+E34*'13. Lean opex'!H22</f>
         <v/>
       </c>
       <c r="H34" s="54">
-        <f>ROUNDUP('13. Lean opex'!B11/G34,0)</f>
+        <f>ROUNDUP('13. Lean opex'!B9/G34,0)</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3624,529 +3629,407 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>OPEX: Серверум (control plane), ₽</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="P13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Q13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="R13" s="43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="S13" s="43" t="n">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>OPEX: Домены/SSL/инфра, ₽</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="Q14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R14" s="43" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S14" s="43" t="n">
-        <v>5000</v>
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>ИТОГО OPEX, ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="59">
+        <f>SUM(B11:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="59">
+        <f>SUM(C11:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="59">
+        <f>SUM(D11:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="59">
+        <f>SUM(E11:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="59">
+        <f>SUM(F11:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="59">
+        <f>SUM(G11:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="59">
+        <f>SUM(H11:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="59">
+        <f>SUM(I11:I12)</f>
+        <v/>
+      </c>
+      <c r="J13" s="59">
+        <f>SUM(J11:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="59">
+        <f>SUM(K11:K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="59">
+        <f>SUM(L11:L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="59">
+        <f>SUM(M11:M12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="59">
+        <f>SUM(N11:N12)</f>
+        <v/>
+      </c>
+      <c r="O13" s="59">
+        <f>SUM(O11:O12)</f>
+        <v/>
+      </c>
+      <c r="P13" s="59">
+        <f>SUM(P11:P12)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="59">
+        <f>SUM(Q11:Q12)</f>
+        <v/>
+      </c>
+      <c r="R13" s="59">
+        <f>SUM(R11:R12)</f>
+        <v/>
+      </c>
+      <c r="S13" s="59">
+        <f>SUM(S11:S12)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>ИТОГО OPEX, ₽</t>
-        </is>
-      </c>
-      <c r="B15" s="59">
-        <f>SUM(B11:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="59">
-        <f>SUM(C11:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="59">
-        <f>SUM(D11:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="59">
-        <f>SUM(E11:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="59">
-        <f>SUM(F11:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="59">
-        <f>SUM(G11:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="59">
-        <f>SUM(H11:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="59">
-        <f>SUM(I11:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="59">
-        <f>SUM(J11:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="59">
-        <f>SUM(K11:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="59">
-        <f>SUM(L11:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="59">
-        <f>SUM(M11:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="59">
-        <f>SUM(N11:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="59">
-        <f>SUM(O11:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="59">
-        <f>SUM(P11:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="59">
-        <f>SUM(Q11:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="59">
-        <f>SUM(R11:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="59">
-        <f>SUM(S11:S14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
           <t>EBITDA, ₽</t>
         </is>
       </c>
-      <c r="B17" s="60">
-        <f>B9-B15</f>
-        <v/>
-      </c>
-      <c r="C17" s="60">
-        <f>C9-C15</f>
-        <v/>
-      </c>
-      <c r="D17" s="60">
-        <f>D9-D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="60">
-        <f>E9-E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="60">
-        <f>F9-F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="60">
-        <f>G9-G15</f>
-        <v/>
-      </c>
-      <c r="H17" s="60">
-        <f>H9-H15</f>
-        <v/>
-      </c>
-      <c r="I17" s="60">
-        <f>I9-I15</f>
-        <v/>
-      </c>
-      <c r="J17" s="60">
-        <f>J9-J15</f>
-        <v/>
-      </c>
-      <c r="K17" s="60">
-        <f>K9-K15</f>
-        <v/>
-      </c>
-      <c r="L17" s="60">
-        <f>L9-L15</f>
-        <v/>
-      </c>
-      <c r="M17" s="60">
-        <f>M9-M15</f>
-        <v/>
-      </c>
-      <c r="N17" s="60">
-        <f>N9-N15</f>
-        <v/>
-      </c>
-      <c r="O17" s="60">
-        <f>O9-O15</f>
-        <v/>
-      </c>
-      <c r="P17" s="60">
-        <f>P9-P15</f>
-        <v/>
-      </c>
-      <c r="Q17" s="60">
-        <f>Q9-Q15</f>
-        <v/>
-      </c>
-      <c r="R17" s="60">
-        <f>R9-R15</f>
-        <v/>
-      </c>
-      <c r="S17" s="60">
-        <f>S9-S15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="B15" s="60">
+        <f>B9-B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="60">
+        <f>C9-C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="60">
+        <f>D9-D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="60">
+        <f>E9-E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="60">
+        <f>F9-F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="60">
+        <f>G9-G13</f>
+        <v/>
+      </c>
+      <c r="H15" s="60">
+        <f>H9-H13</f>
+        <v/>
+      </c>
+      <c r="I15" s="60">
+        <f>I9-I13</f>
+        <v/>
+      </c>
+      <c r="J15" s="60">
+        <f>J9-J13</f>
+        <v/>
+      </c>
+      <c r="K15" s="60">
+        <f>K9-K13</f>
+        <v/>
+      </c>
+      <c r="L15" s="60">
+        <f>L9-L13</f>
+        <v/>
+      </c>
+      <c r="M15" s="60">
+        <f>M9-M13</f>
+        <v/>
+      </c>
+      <c r="N15" s="60">
+        <f>N9-N13</f>
+        <v/>
+      </c>
+      <c r="O15" s="60">
+        <f>O9-O13</f>
+        <v/>
+      </c>
+      <c r="P15" s="60">
+        <f>P9-P13</f>
+        <v/>
+      </c>
+      <c r="Q15" s="60">
+        <f>Q9-Q13</f>
+        <v/>
+      </c>
+      <c r="R15" s="60">
+        <f>R9-R13</f>
+        <v/>
+      </c>
+      <c r="S15" s="60">
+        <f>S9-S13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Накопленный кэш (старт 30к ₽), ₽</t>
         </is>
       </c>
-      <c r="B18" s="60">
-        <f>30000+B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="49">
-        <f>B18+C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="49">
-        <f>C18+D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="49">
-        <f>D18+E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="49">
-        <f>E18+F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="49">
-        <f>F18+G17</f>
-        <v/>
-      </c>
-      <c r="H18" s="49">
-        <f>G18+H17</f>
-        <v/>
-      </c>
-      <c r="I18" s="49">
-        <f>H18+I17</f>
-        <v/>
-      </c>
-      <c r="J18" s="49">
-        <f>I18+J17</f>
-        <v/>
-      </c>
-      <c r="K18" s="49">
-        <f>J18+K17</f>
-        <v/>
-      </c>
-      <c r="L18" s="49">
-        <f>K18+L17</f>
-        <v/>
-      </c>
-      <c r="M18" s="49">
-        <f>L18+M17</f>
-        <v/>
-      </c>
-      <c r="N18" s="49">
-        <f>M18+N17</f>
-        <v/>
-      </c>
-      <c r="O18" s="49">
-        <f>N18+O17</f>
-        <v/>
-      </c>
-      <c r="P18" s="49">
-        <f>O18+P17</f>
-        <v/>
-      </c>
-      <c r="Q18" s="49">
-        <f>P18+Q17</f>
-        <v/>
-      </c>
-      <c r="R18" s="49">
-        <f>Q18+R17</f>
-        <v/>
-      </c>
-      <c r="S18" s="49">
-        <f>R18+S17</f>
+      <c r="B16" s="60">
+        <f>30000+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="49">
+        <f>B16+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="49">
+        <f>C16+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="49">
+        <f>D16+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="49">
+        <f>E16+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="49">
+        <f>F16+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="49">
+        <f>G16+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="49">
+        <f>H16+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="49">
+        <f>I16+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="49">
+        <f>J16+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="49">
+        <f>K16+L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="49">
+        <f>L16+M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="49">
+        <f>M16+N15</f>
+        <v/>
+      </c>
+      <c r="O16" s="49">
+        <f>N16+O15</f>
+        <v/>
+      </c>
+      <c r="P16" s="49">
+        <f>O16+P15</f>
+        <v/>
+      </c>
+      <c r="Q16" s="49">
+        <f>P16+Q15</f>
+        <v/>
+      </c>
+      <c r="R16" s="49">
+        <f>Q16+R15</f>
+        <v/>
+      </c>
+      <c r="S16" s="49">
+        <f>R16+S15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MRR на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B20" s="53">
+        <f>S7</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ARR на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B21" s="53">
+        <f>S7*12</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>MRR на M18, ₽</t>
+          <t>Накопленный кэш на M18, ₽</t>
         </is>
       </c>
       <c r="B22" s="53">
-        <f>S7</f>
+        <f>S16</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>ARR на M18, ₽</t>
-        </is>
-      </c>
-      <c r="B23" s="53">
-        <f>S7*12</f>
+          <t>Min cash (наибольший провал), ₽</t>
+        </is>
+      </c>
+      <c r="B23" s="59">
+        <f>MIN(B16:S16)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M18, ₽</t>
-        </is>
-      </c>
-      <c r="B24" s="53">
-        <f>S18</f>
-        <v/>
+          <t>Месяц первого положительного EBITDA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>M11 (по плану)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Min cash (наибольший провал), ₽</t>
-        </is>
-      </c>
-      <c r="B25" s="59">
-        <f>MIN(B18:S18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Месяц первого положительного EBITDA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>M11–M12 (по плану)</t>
+          <t>Месяц recoup (накопленный кэш &gt; 0)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>M15 (по плану, +0.45 М)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Месяц recoup (накопленный кэш &gt; 0)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>M16 (по плану)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>vs v2 plan (FOT 3.5М/мес):</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>vs v2 plan (с маркет. + FOT 3.5М/мес):</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Постоянный OPEX/мес</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>330 000 ₽</t>
+        </is>
+      </c>
+      <c r="C29" s="62" t="inlineStr">
+        <is>
+          <t>3 500 000 ₽</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>−91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Break-even клиентов</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>~239</t>
+        </is>
+      </c>
+      <c r="C30" s="62" t="inlineStr">
+        <is>
+          <t>~860</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>−72%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Постоянный OPEX/мес</t>
+          <t>Min cash (худший провал)</t>
         </is>
       </c>
       <c r="B31" s="61" t="inlineStr">
         <is>
-          <t>385 000 ₽</t>
+          <t>~2.65 М ₽</t>
         </is>
       </c>
       <c r="C31" s="62" t="inlineStr">
         <is>
-          <t>3 500 000 ₽</t>
+          <t>~28 М ₽</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>−89%</t>
+          <t>−91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Break-even клиентов</t>
+          <t>Bootstrap-friendly</t>
         </is>
       </c>
       <c r="B32" s="61" t="inlineStr">
         <is>
-          <t>~280</t>
+          <t>Да (с буфером 3-4 М)</t>
         </is>
       </c>
       <c r="C32" s="62" t="inlineStr">
         <is>
-          <t>~860</t>
+          <t>Нужен ангел 10М+</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>−67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Min cash (худший провал)</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="inlineStr">
-        <is>
-          <t>~3.2 М ₽</t>
-        </is>
-      </c>
-      <c r="C33" s="62" t="inlineStr">
-        <is>
-          <t>~28 М ₽</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>−89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Bootstrap-friendly</t>
-        </is>
-      </c>
-      <c r="B34" s="61" t="inlineStr">
-        <is>
-          <t>Да (с буфером 4-5 М)</t>
-        </is>
-      </c>
-      <c r="C34" s="62" t="inlineStr">
-        <is>
-          <t>Нужен ангел 10М+</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,8 +210,10 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -3030,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3057,14 +3059,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финмодель 18 месяцев · lean opex (385 К/мес постоянных)</t>
+          <t>Финмодель 18 месяцев · M1 разработка → M2 запуск с маркетингом</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Burn до break-even ~3.2 М ₽. EBITDA положительный с M11. Накопленный кэш &gt; 0 с M16.</t>
+          <t>M1 = только строим продукт (300к dev + 30к юрист). M2+ = продукт live, маркетинг ~100к → 250к, клиенты идут с первого дня запуска.</t>
         </is>
       </c>
     </row>
@@ -3175,55 +3177,55 @@
         <v>0</v>
       </c>
       <c r="C5" s="56" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D5" s="56" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E5" s="56" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="F5" s="56" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="G5" s="56" t="n">
-        <v>35</v>
+        <v>380</v>
       </c>
       <c r="H5" s="56" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="I5" s="56" t="n">
-        <v>120</v>
+        <v>720</v>
       </c>
       <c r="J5" s="56" t="n">
-        <v>200</v>
+        <v>920</v>
       </c>
       <c r="K5" s="56" t="n">
-        <v>320</v>
+        <v>1140</v>
       </c>
       <c r="L5" s="56" t="n">
-        <v>480</v>
+        <v>1390</v>
       </c>
       <c r="M5" s="56" t="n">
-        <v>680</v>
+        <v>1670</v>
       </c>
       <c r="N5" s="56" t="n">
-        <v>920</v>
+        <v>1980</v>
       </c>
       <c r="O5" s="56" t="n">
-        <v>1180</v>
+        <v>2330</v>
       </c>
       <c r="P5" s="56" t="n">
-        <v>1450</v>
+        <v>2710</v>
       </c>
       <c r="Q5" s="56" t="n">
-        <v>1750</v>
+        <v>3120</v>
       </c>
       <c r="R5" s="56" t="n">
-        <v>2050</v>
+        <v>3550</v>
       </c>
       <c r="S5" s="56" t="n">
-        <v>2350</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6">
@@ -3233,7 +3235,7 @@
         </is>
       </c>
       <c r="B6" s="57" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="C6" s="57" t="n">
         <v>990</v>
@@ -3242,46 +3244,46 @@
         <v>990</v>
       </c>
       <c r="E6" s="57" t="n">
-        <v>990</v>
+        <v>1100</v>
       </c>
       <c r="F6" s="57" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G6" s="57" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="H6" s="57" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="I6" s="57" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="J6" s="57" t="n">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="K6" s="57" t="n">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="L6" s="57" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="M6" s="57" t="n">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="N6" s="57" t="n">
-        <v>3150</v>
+        <v>3400</v>
       </c>
       <c r="O6" s="57" t="n">
-        <v>3400</v>
+        <v>3650</v>
       </c>
       <c r="P6" s="57" t="n">
-        <v>3650</v>
+        <v>3850</v>
       </c>
       <c r="Q6" s="57" t="n">
-        <v>3850</v>
+        <v>3950</v>
       </c>
       <c r="R6" s="57" t="n">
-        <v>3950</v>
+        <v>4030</v>
       </c>
       <c r="S6" s="57" t="n">
         <v>4080</v>
@@ -3373,7 +3375,7 @@
         </is>
       </c>
       <c r="B8" s="58" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="C8" s="58" t="n">
         <v>0.53</v>
@@ -3382,40 +3384,40 @@
         <v>0.53</v>
       </c>
       <c r="E8" s="58" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="F8" s="58" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I8" s="58" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="K8" s="58" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="L8" s="58" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="M8" s="58" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="N8" s="58" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="O8" s="58" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="P8" s="58" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="Q8" s="58" t="n">
         <v>0.34</v>
@@ -3629,409 +3631,525 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Маркетинг и реклама, ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G13" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I13" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J13" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="K13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P13" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q13" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="R13" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="S13" s="59" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>ИТОГО OPEX, ₽</t>
         </is>
       </c>
-      <c r="B13" s="59">
-        <f>SUM(B11:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="59">
-        <f>SUM(C11:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="59">
-        <f>SUM(D11:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="59">
-        <f>SUM(E11:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="59">
-        <f>SUM(F11:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="59">
-        <f>SUM(G11:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="59">
-        <f>SUM(H11:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="59">
-        <f>SUM(I11:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="59">
-        <f>SUM(J11:J12)</f>
-        <v/>
-      </c>
-      <c r="K13" s="59">
-        <f>SUM(K11:K12)</f>
-        <v/>
-      </c>
-      <c r="L13" s="59">
-        <f>SUM(L11:L12)</f>
-        <v/>
-      </c>
-      <c r="M13" s="59">
-        <f>SUM(M11:M12)</f>
-        <v/>
-      </c>
-      <c r="N13" s="59">
-        <f>SUM(N11:N12)</f>
-        <v/>
-      </c>
-      <c r="O13" s="59">
-        <f>SUM(O11:O12)</f>
-        <v/>
-      </c>
-      <c r="P13" s="59">
-        <f>SUM(P11:P12)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="59">
-        <f>SUM(Q11:Q12)</f>
-        <v/>
-      </c>
-      <c r="R13" s="59">
-        <f>SUM(R11:R12)</f>
-        <v/>
-      </c>
-      <c r="S13" s="59">
-        <f>SUM(S11:S12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA, ₽</t>
-        </is>
-      </c>
-      <c r="B15" s="60">
-        <f>B9-B13</f>
-        <v/>
-      </c>
-      <c r="C15" s="60">
-        <f>C9-C13</f>
-        <v/>
-      </c>
-      <c r="D15" s="60">
-        <f>D9-D13</f>
-        <v/>
-      </c>
-      <c r="E15" s="60">
-        <f>E9-E13</f>
-        <v/>
-      </c>
-      <c r="F15" s="60">
-        <f>F9-F13</f>
-        <v/>
-      </c>
-      <c r="G15" s="60">
-        <f>G9-G13</f>
-        <v/>
-      </c>
-      <c r="H15" s="60">
-        <f>H9-H13</f>
-        <v/>
-      </c>
-      <c r="I15" s="60">
-        <f>I9-I13</f>
-        <v/>
-      </c>
-      <c r="J15" s="60">
-        <f>J9-J13</f>
-        <v/>
-      </c>
-      <c r="K15" s="60">
-        <f>K9-K13</f>
-        <v/>
-      </c>
-      <c r="L15" s="60">
-        <f>L9-L13</f>
-        <v/>
-      </c>
-      <c r="M15" s="60">
-        <f>M9-M13</f>
-        <v/>
-      </c>
-      <c r="N15" s="60">
-        <f>N9-N13</f>
-        <v/>
-      </c>
-      <c r="O15" s="60">
-        <f>O9-O13</f>
-        <v/>
-      </c>
-      <c r="P15" s="60">
-        <f>P9-P13</f>
-        <v/>
-      </c>
-      <c r="Q15" s="60">
-        <f>Q9-Q13</f>
-        <v/>
-      </c>
-      <c r="R15" s="60">
-        <f>R9-R13</f>
-        <v/>
-      </c>
-      <c r="S15" s="60">
-        <f>S9-S13</f>
+      <c r="B14" s="60">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="60">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="60">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="60">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="60">
+        <f>SUM(F11:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="60">
+        <f>SUM(G11:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="60">
+        <f>SUM(H11:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="60">
+        <f>SUM(I11:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="60">
+        <f>SUM(J11:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="60">
+        <f>SUM(K11:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="60">
+        <f>SUM(L11:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="60">
+        <f>SUM(M11:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="60">
+        <f>SUM(N11:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="60">
+        <f>SUM(O11:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="60">
+        <f>SUM(P11:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="60">
+        <f>SUM(Q11:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="60">
+        <f>SUM(R11:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="60">
+        <f>SUM(S11:S13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
+          <t>EBITDA, ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="61">
+        <f>B9-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="61">
+        <f>C9-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="61">
+        <f>D9-D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="61">
+        <f>E9-E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="61">
+        <f>F9-F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="61">
+        <f>G9-G14</f>
+        <v/>
+      </c>
+      <c r="H16" s="61">
+        <f>H9-H14</f>
+        <v/>
+      </c>
+      <c r="I16" s="61">
+        <f>I9-I14</f>
+        <v/>
+      </c>
+      <c r="J16" s="61">
+        <f>J9-J14</f>
+        <v/>
+      </c>
+      <c r="K16" s="61">
+        <f>K9-K14</f>
+        <v/>
+      </c>
+      <c r="L16" s="61">
+        <f>L9-L14</f>
+        <v/>
+      </c>
+      <c r="M16" s="61">
+        <f>M9-M14</f>
+        <v/>
+      </c>
+      <c r="N16" s="61">
+        <f>N9-N14</f>
+        <v/>
+      </c>
+      <c r="O16" s="61">
+        <f>O9-O14</f>
+        <v/>
+      </c>
+      <c r="P16" s="61">
+        <f>P9-P14</f>
+        <v/>
+      </c>
+      <c r="Q16" s="61">
+        <f>Q9-Q14</f>
+        <v/>
+      </c>
+      <c r="R16" s="61">
+        <f>R9-R14</f>
+        <v/>
+      </c>
+      <c r="S16" s="61">
+        <f>S9-S14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
           <t>Накопленный кэш (старт 30к ₽), ₽</t>
         </is>
       </c>
-      <c r="B16" s="60">
-        <f>30000+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="49">
-        <f>B16+C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="49">
-        <f>C16+D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="49">
-        <f>D16+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="49">
-        <f>E16+F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="49">
-        <f>F16+G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="49">
-        <f>G16+H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="49">
-        <f>H16+I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="49">
-        <f>I16+J15</f>
-        <v/>
-      </c>
-      <c r="K16" s="49">
-        <f>J16+K15</f>
-        <v/>
-      </c>
-      <c r="L16" s="49">
-        <f>K16+L15</f>
-        <v/>
-      </c>
-      <c r="M16" s="49">
-        <f>L16+M15</f>
-        <v/>
-      </c>
-      <c r="N16" s="49">
-        <f>M16+N15</f>
-        <v/>
-      </c>
-      <c r="O16" s="49">
-        <f>N16+O15</f>
-        <v/>
-      </c>
-      <c r="P16" s="49">
-        <f>O16+P15</f>
-        <v/>
-      </c>
-      <c r="Q16" s="49">
-        <f>P16+Q15</f>
-        <v/>
-      </c>
-      <c r="R16" s="49">
-        <f>Q16+R15</f>
-        <v/>
-      </c>
-      <c r="S16" s="49">
-        <f>R16+S15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B17" s="61">
+        <f>30000+B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="49">
+        <f>B17+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="49">
+        <f>C17+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="49">
+        <f>D17+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="49">
+        <f>E17+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="49">
+        <f>F17+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="49">
+        <f>G17+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="49">
+        <f>H17+I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="49">
+        <f>I17+J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="49">
+        <f>J17+K16</f>
+        <v/>
+      </c>
+      <c r="L17" s="49">
+        <f>K17+L16</f>
+        <v/>
+      </c>
+      <c r="M17" s="49">
+        <f>L17+M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="49">
+        <f>M17+N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="49">
+        <f>N17+O16</f>
+        <v/>
+      </c>
+      <c r="P17" s="49">
+        <f>O17+P16</f>
+        <v/>
+      </c>
+      <c r="Q17" s="49">
+        <f>P17+Q16</f>
+        <v/>
+      </c>
+      <c r="R17" s="49">
+        <f>Q17+R16</f>
+        <v/>
+      </c>
+      <c r="S17" s="49">
+        <f>R17+S16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>MRR на M18, ₽</t>
-        </is>
-      </c>
-      <c r="B20" s="53">
-        <f>S7</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ARR на M18, ₽</t>
+          <t>MRR на M18, ₽</t>
         </is>
       </c>
       <c r="B21" s="53">
-        <f>S7*12</f>
+        <f>S7</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M18, ₽</t>
+          <t>ARR на M18, ₽</t>
         </is>
       </c>
       <c r="B22" s="53">
-        <f>S16</f>
+        <f>S7*12</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Min cash (наибольший провал), ₽</t>
-        </is>
-      </c>
-      <c r="B23" s="59">
-        <f>MIN(B16:S16)</f>
+          <t>Накопленный кэш на M18, ₽</t>
+        </is>
+      </c>
+      <c r="B23" s="53">
+        <f>S17</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Месяц первого положительного EBITDA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>M11 (по плану)</t>
-        </is>
+          <t>Min cash (наибольший провал), ₽</t>
+        </is>
+      </c>
+      <c r="B24" s="60">
+        <f>MIN(B17:S17)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Месяц первого положительного EBITDA</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>M8 (по плану)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>Месяц recoup (накопленный кэш &gt; 0)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>M15 (по плану, +0.45 М)</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>M11 (по плану, +0.21 М)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>vs v2 plan (FOT 3.5М/мес):</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Маркетинг суммарно за 18 мес</t>
+        </is>
+      </c>
+      <c r="B27" s="62">
+        <f>SUM(B13:S13)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Постоянный OPEX/мес</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="inlineStr">
-        <is>
-          <t>330 000 ₽</t>
-        </is>
-      </c>
-      <c r="C29" s="62" t="inlineStr">
-        <is>
-          <t>3 500 000 ₽</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>−91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Break-even клиентов</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>~239</t>
-        </is>
-      </c>
-      <c r="C30" s="62" t="inlineStr">
-        <is>
-          <t>~860</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>−72%</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>vs предыдущая lean-модель (3 мес build, без маркетинга):</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Min cash (худший провал)</t>
-        </is>
-      </c>
-      <c r="B31" s="61" t="inlineStr">
-        <is>
-          <t>~2.65 М ₽</t>
-        </is>
-      </c>
-      <c r="C31" s="62" t="inlineStr">
-        <is>
-          <t>~28 М ₽</t>
+          <t>Месяц break-even (EBITDA ≥ 0)</t>
+        </is>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="C31" s="64" t="inlineStr">
+        <is>
+          <t>M11</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>−91%</t>
+          <t>+3 мес раньше</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Bootstrap-friendly</t>
-        </is>
-      </c>
-      <c r="B32" s="61" t="inlineStr">
-        <is>
-          <t>Да (с буфером 3-4 М)</t>
-        </is>
-      </c>
-      <c r="C32" s="62" t="inlineStr">
-        <is>
-          <t>Нужен ангел 10М+</t>
+          <t>Месяц recoup (cash &gt; 0)</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C32" s="64" t="inlineStr">
+        <is>
+          <t>M15</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4 мес раньше</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Min cash (макс. провал)</t>
+        </is>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>~−2.0 М ₽</t>
+        </is>
+      </c>
+      <c r="C33" s="64" t="inlineStr">
+        <is>
+          <t>~−2.65 М ₽</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>−24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MRR на M18</t>
+        </is>
+      </c>
+      <c r="B34" s="63" t="inlineStr">
+        <is>
+          <t>~16.3 М ₽</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>~9.6 М ₽</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>+70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Накопленный кэш на M18</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="inlineStr">
+        <is>
+          <t>~+21.8 М ₽</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>~+8.6 М ₽</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>+150%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Маркетинг 18 мес</t>
+        </is>
+      </c>
+      <c r="B36" s="63" t="inlineStr">
+        <is>
+          <t>~3.4 М ₽</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>0 ₽</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>+бюджет</t>
         </is>
       </c>
     </row>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -20,7 +20,7 @@
     <sheet name="11. Кеширование промптов" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14. Lean break-even" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15. Lean финмодель 18м" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Без кеша · cost/msg</t>
+          <t>Без кеша · себест/сообщ</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>С кешем · cost/msg</t>
+          <t>С кешем · себест/сообщ</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Без · retail/msg</t>
+          <t>Без · цена клиенту/сообщ</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>С · retail/msg</t>
+          <t>С · цена клиенту/сообщ</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1814,7 +1814,7 @@
     <row r="5">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Capex (железо)</t>
+          <t>Покупка железа</t>
         </is>
       </c>
       <c r="B5" s="40" t="n">
@@ -1829,7 +1829,7 @@
     <row r="6">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>Opex /мес (электр., охлаждение, амортизация 5y)</t>
+          <t>Текущие траты в месяц (электричество, охлаждение, износ за 5 лет)</t>
         </is>
       </c>
       <c r="B6" s="40" t="n">
@@ -1844,7 +1844,7 @@
     <row r="7">
       <c r="A7" s="39" t="inlineStr">
         <is>
-          <t>Throughput на 1 GPU, msg/час (8K токенов)</t>
+          <t>Производительность 1 видеокарты, сообщ/час</t>
         </is>
       </c>
       <c r="B7" s="41" t="n">
@@ -1859,7 +1859,7 @@
     <row r="8">
       <c r="A8" s="39" t="inlineStr">
         <is>
-          <t>Активный uptime, ч/мес</t>
+          <t>Время работы, часов/мес</t>
         </is>
       </c>
       <c r="B8" s="41" t="n">
@@ -1889,7 +1889,7 @@
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>Capacity Qwen msg/мес</t>
+          <t>Сколько сообщ может обработать в мес</t>
         </is>
       </c>
       <c r="B11" s="16">
@@ -1905,7 +1905,7 @@
     <row r="12">
       <c r="A12" s="33" t="inlineStr">
         <is>
-          <t>Стоимость нам Qwen ₽/msg</t>
+          <t>Себест 1 сообщ на Qwen, ₽</t>
         </is>
       </c>
       <c r="B12" s="42">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Месяцев до break-even</t>
+          <t>Месяцев до точки безубыточности</t>
         </is>
       </c>
     </row>
@@ -2201,21 +2201,21 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>• 200-500 юзеров: 4-12 мес до break-even. Прицельно если есть стратегические причины (152-ФЗ, vendor lock-in protection).</t>
+          <t>• 200-500 юзеров: 4-12 мес до точки безубыточности. Прицельно если есть стратегические причины (152-ФЗ, vendor lock-in protection).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>• 500+ юзеров: 1-3 мес до break-even — однозначно ставить.</t>
+          <t>• 500+ юзеров: 1-3 мес до точки безубыточности — однозначно ставить.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>• По плану на M15: ~1 000 платящих → break-even на 4-м месяце с launch'a Qwen.</t>
+          <t>• По плану на M15: ~1 000 платящих → точки безубыточности на 4-м месяце с launch'a Qwen.</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>СТРАТЕГИЧЕСКАЯ ЦЕННОСТЬ (за пределами break-even)</t>
+          <t>СТРАТЕГИЧЕСКАЯ ЦЕННОСТЬ (за пределами точки безубыточности)</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ARPU средневзв., ₽</t>
+          <t>Средний доход с клиента, ₽</t>
         </is>
       </c>
       <c r="B15" s="49">
@@ -2744,7 +2744,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>GM на 1 клиента/мес, ₽</t>
+          <t>Маржа на 1 клиента/мес, ₽</t>
         </is>
       </c>
       <c r="B16" s="49">
@@ -2755,7 +2755,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GM ratio (от MRR)</t>
+          <t>Маржа % от выручки</t>
         </is>
       </c>
       <c r="B17" s="50">
@@ -2766,7 +2766,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>BREAK-EVEN</t>
+          <t>ТОЧКА БЕЗУБЫТОЧНОСТИ</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>MRR break-even, ₽</t>
+          <t>Выручка/мес для безубыточности, ₽</t>
         </is>
       </c>
       <c r="B24" s="53">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>ARPU ₽</t>
+          <t>Доход/клиент ₽</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>GM/cust ₽</t>
+          <t>Маржа/клиент ₽</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Break-even</t>
+          <t>Клиентов до плюса</t>
         </is>
       </c>
     </row>
@@ -3010,14 +3010,14 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>ВЫВОД: при дефолтном миксе break-even ≈ 280 платящих. При премиум-tilt — всего ~145.</t>
+          <t>ВЫВОД: при дефолтном миксе точки безубыточности ≈ 280 платящих. При премиум-tilt — всего ~145.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>vs v2 business plan (с маркетингом и FOT 3.5М/мес): break-even был 858 → теперь 280 = в 3× меньше.</t>
+          <t>vs v2 business plan (с маркетингом и FOT 3.5М/мес): точки безубыточности был 858 → теперь 280 = в 3× меньше.</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ARPU средневзв., ₽/мес</t>
+          <t>Средний доход с клиента, ₽/мес</t>
         </is>
       </c>
       <c r="B6" s="57" t="n">
@@ -3292,7 +3292,7 @@
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>MRR, ₽/мес</t>
+          <t>Выручка, ₽/мес</t>
         </is>
       </c>
       <c r="B7" s="49">
@@ -3371,7 +3371,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>GM ratio</t>
+          <t>Маржа %</t>
         </is>
       </c>
       <c r="B8" s="58" t="n">
@@ -3773,7 +3773,7 @@
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>EBITDA, ₽</t>
+          <t>Прибыль/убыток, ₽</t>
         </is>
       </c>
       <c r="B16" s="61">
@@ -3938,7 +3938,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>MRR на M18, ₽</t>
+          <t>Выручка/мес на M18, ₽</t>
         </is>
       </c>
       <c r="B21" s="53">
@@ -3949,7 +3949,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>ARR на M18, ₽</t>
+          <t>Выручка/год на M18, ₽</t>
         </is>
       </c>
       <c r="B22" s="53">
@@ -3971,7 +3971,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Min cash (наибольший провал), ₽</t>
+          <t>Самый большой минус по деньгам, ₽</t>
         </is>
       </c>
       <c r="B24" s="60">
@@ -4024,7 +4024,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Месяц break-even (EBITDA ≥ 0)</t>
+          <t>Месяц точки безубыточности (EBITDA ≥ 0)</t>
         </is>
       </c>
       <c r="B31" s="63" t="inlineStr">
@@ -4185,7 +4185,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cost ₽/M = (input × output_share + output × output_share) × FX. Retail ₽/M = cost × markup.</t>
+          <t>Себест ₽/1М = (цена input × 0.5 + цена output × 0.5) × курс ₽/$. Цена клиенту = себест × наценка 2.8.</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Retail ₽/1M</t>
+          <t>Цена клиенту ₽/1M</t>
         </is>
       </c>
     </row>
@@ -4472,17 +4472,17 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Себест. ₽/msg</t>
+          <t>Себест ₽/сообщ</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Retail ₽/msg</t>
+          <t>Цена клиенту ₽/сообщ</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Маржа ₽/msg</t>
+          <t>Маржа ₽/сообщ</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -4706,7 +4706,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Retail-цена что заплатит пользователь · меняй msg_size в 1.Параметры.</t>
+          <t>Цена что заплатит клиент · меняй размер сообщения в 1. Параметры.</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>Себест. ₽/msg</t>
+          <t>Себест ₽/сообщ</t>
         </is>
       </c>
       <c r="B15" s="24">
@@ -5524,7 +5524,7 @@
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>Retail ₽/msg</t>
+          <t>Цена клиенту ₽/сообщ</t>
         </is>
       </c>
       <c r="B16" s="25">

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -2340,19 +2340,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C8" s="44" t="inlineStr">
-        <is>
-          <t>1 senior dev или 2 mid (founder + 1 hire). Ремонт + новые фичи.</t>
-        </is>
-      </c>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -2361,7 +2351,7 @@
         </is>
       </c>
       <c r="B9" s="45">
-        <f>SUM(B7:B8)</f>
+        <f>B7</f>
         <v/>
       </c>
       <c r="C9" s="15" t="n"/>
@@ -2369,28 +2359,35 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ПОЧЕМУ НЕТ СЕРВЕРОВ И ДОМЕНОВ?</t>
+          <t>ПОЧЕМУ ТАК МАЛО ПОСТОЯННЫХ?</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Серверум (аренда сервера для сайта клиента) и домен + HTTPS включены в подписку клиента → переменные затраты, не наши fixed.</t>
+          <t>• Разработку делают founders сами — без зарплат. AI-инструменты делают это реальным даже для одного человека.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Логика: мы платим Серверум за каждый клиентский VPS, добавляем эту сумму в стоимость тарифа → сразу окупаем при первом платеже.</t>
+          <t>• Серверум и домен клиента — в стоимости подписки (variable per customer), не наши fixed.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Наша собственная инфра (omnia.ai домен, control-plane если будет) пока в рамках 300к разработки — учли в FOT.</t>
+          <t>• Маркетинг с M2 (после запуска): 100 → 250 К/мес ramp. Если clipboard окупает себя — масштабируем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>• Юрист — единственная обязательная статья (договоры, оферта, документы по 152-ФЗ).</t>
         </is>
       </c>
     </row>
@@ -3059,14 +3056,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финмодель 18 месяцев · M1 разработка → M2 запуск с маркетингом</t>
+          <t>Финмодель 18 месяцев · M1 запуск → founders-only без зарплат разработчикам</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M1 = только строим продукт (300к dev + 30к юрист). M2+ = продукт live, маркетинг ~100к → 250к, клиенты идут с первого дня запуска.</t>
+          <t>Разрабатывают founders сами (AI-инструменты делают это реальным). Постоянка = только юрист 30к. С M2 — маркетинг 100→250к.</t>
         </is>
       </c>
     </row>
@@ -3572,359 +3569,298 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>OPEX: Разработка, ₽</t>
+          <t>OPEX: Маркетинг и реклама, ₽</t>
         </is>
       </c>
       <c r="B12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="J12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="L12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="M12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="N12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="P12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="Q12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="R12" s="43" t="n">
-        <v>300000</v>
-      </c>
-      <c r="S12" s="43" t="n">
-        <v>300000</v>
+        <v>0</v>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G12" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H12" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I12" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J12" s="59" t="n">
+        <v>150000</v>
+      </c>
+      <c r="K12" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L12" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M12" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N12" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O12" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P12" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Q12" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="R12" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="S12" s="59" t="n">
+        <v>250000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>OPEX: Маркетинг и реклама, ₽</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D13" s="59" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E13" s="59" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F13" s="59" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G13" s="59" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H13" s="59" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I13" s="59" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J13" s="59" t="n">
-        <v>150000</v>
-      </c>
-      <c r="K13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="M13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="N13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="O13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="P13" s="59" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q13" s="59" t="n">
-        <v>250000</v>
-      </c>
-      <c r="R13" s="59" t="n">
-        <v>250000</v>
-      </c>
-      <c r="S13" s="59" t="n">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>ИТОГО OPEX, ₽</t>
         </is>
       </c>
-      <c r="B14" s="60">
-        <f>SUM(B11:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="60">
-        <f>SUM(C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="60">
-        <f>SUM(D11:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="60">
-        <f>SUM(E11:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="60">
-        <f>SUM(F11:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="60">
-        <f>SUM(G11:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="60">
-        <f>SUM(H11:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="60">
-        <f>SUM(I11:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="60">
-        <f>SUM(J11:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="60">
-        <f>SUM(K11:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="60">
-        <f>SUM(L11:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="60">
-        <f>SUM(M11:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="60">
-        <f>SUM(N11:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="60">
-        <f>SUM(O11:O13)</f>
-        <v/>
-      </c>
-      <c r="P14" s="60">
-        <f>SUM(P11:P13)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="60">
-        <f>SUM(Q11:Q13)</f>
-        <v/>
-      </c>
-      <c r="R14" s="60">
-        <f>SUM(R11:R13)</f>
-        <v/>
-      </c>
-      <c r="S14" s="60">
-        <f>SUM(S11:S13)</f>
+      <c r="B13" s="60">
+        <f>SUM(B11:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="60">
+        <f>SUM(C11:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="60">
+        <f>SUM(D11:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="60">
+        <f>SUM(E11:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="60">
+        <f>SUM(F11:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="60">
+        <f>SUM(G11:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="60">
+        <f>SUM(H11:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="60">
+        <f>SUM(I11:I12)</f>
+        <v/>
+      </c>
+      <c r="J13" s="60">
+        <f>SUM(J11:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="60">
+        <f>SUM(K11:K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="60">
+        <f>SUM(L11:L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="60">
+        <f>SUM(M11:M12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="60">
+        <f>SUM(N11:N12)</f>
+        <v/>
+      </c>
+      <c r="O13" s="60">
+        <f>SUM(O11:O12)</f>
+        <v/>
+      </c>
+      <c r="P13" s="60">
+        <f>SUM(P11:P12)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="60">
+        <f>SUM(Q11:Q12)</f>
+        <v/>
+      </c>
+      <c r="R13" s="60">
+        <f>SUM(R11:R12)</f>
+        <v/>
+      </c>
+      <c r="S13" s="60">
+        <f>SUM(S11:S12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>Прибыль/убыток, ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="61">
+        <f>B9-B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="61">
+        <f>C9-C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="61">
+        <f>D9-D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="61">
+        <f>E9-E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="61">
+        <f>F9-F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="61">
+        <f>G9-G13</f>
+        <v/>
+      </c>
+      <c r="H15" s="61">
+        <f>H9-H13</f>
+        <v/>
+      </c>
+      <c r="I15" s="61">
+        <f>I9-I13</f>
+        <v/>
+      </c>
+      <c r="J15" s="61">
+        <f>J9-J13</f>
+        <v/>
+      </c>
+      <c r="K15" s="61">
+        <f>K9-K13</f>
+        <v/>
+      </c>
+      <c r="L15" s="61">
+        <f>L9-L13</f>
+        <v/>
+      </c>
+      <c r="M15" s="61">
+        <f>M9-M13</f>
+        <v/>
+      </c>
+      <c r="N15" s="61">
+        <f>N9-N13</f>
+        <v/>
+      </c>
+      <c r="O15" s="61">
+        <f>O9-O13</f>
+        <v/>
+      </c>
+      <c r="P15" s="61">
+        <f>P9-P13</f>
+        <v/>
+      </c>
+      <c r="Q15" s="61">
+        <f>Q9-Q13</f>
+        <v/>
+      </c>
+      <c r="R15" s="61">
+        <f>R9-R13</f>
+        <v/>
+      </c>
+      <c r="S15" s="61">
+        <f>S9-S13</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>Прибыль/убыток, ₽</t>
+          <t>Накопленный кэш (старт 30к ₽), ₽</t>
         </is>
       </c>
       <c r="B16" s="61">
-        <f>B9-B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="61">
-        <f>C9-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="61">
-        <f>D9-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="61">
-        <f>E9-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="61">
-        <f>F9-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="61">
-        <f>G9-G14</f>
-        <v/>
-      </c>
-      <c r="H16" s="61">
-        <f>H9-H14</f>
-        <v/>
-      </c>
-      <c r="I16" s="61">
-        <f>I9-I14</f>
-        <v/>
-      </c>
-      <c r="J16" s="61">
-        <f>J9-J14</f>
-        <v/>
-      </c>
-      <c r="K16" s="61">
-        <f>K9-K14</f>
-        <v/>
-      </c>
-      <c r="L16" s="61">
-        <f>L9-L14</f>
-        <v/>
-      </c>
-      <c r="M16" s="61">
-        <f>M9-M14</f>
-        <v/>
-      </c>
-      <c r="N16" s="61">
-        <f>N9-N14</f>
-        <v/>
-      </c>
-      <c r="O16" s="61">
-        <f>O9-O14</f>
-        <v/>
-      </c>
-      <c r="P16" s="61">
-        <f>P9-P14</f>
-        <v/>
-      </c>
-      <c r="Q16" s="61">
-        <f>Q9-Q14</f>
-        <v/>
-      </c>
-      <c r="R16" s="61">
-        <f>R9-R14</f>
-        <v/>
-      </c>
-      <c r="S16" s="61">
-        <f>S9-S14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>Накопленный кэш (старт 30к ₽), ₽</t>
-        </is>
-      </c>
-      <c r="B17" s="61">
-        <f>30000+B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="49">
-        <f>B17+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="49">
-        <f>C17+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="49">
-        <f>D17+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="49">
-        <f>E17+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="49">
-        <f>F17+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="49">
-        <f>G17+H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="49">
-        <f>H17+I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="49">
-        <f>I17+J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="49">
-        <f>J17+K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="49">
-        <f>K17+L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="49">
-        <f>L17+M16</f>
-        <v/>
-      </c>
-      <c r="N17" s="49">
-        <f>M17+N16</f>
-        <v/>
-      </c>
-      <c r="O17" s="49">
-        <f>N17+O16</f>
-        <v/>
-      </c>
-      <c r="P17" s="49">
-        <f>O17+P16</f>
-        <v/>
-      </c>
-      <c r="Q17" s="49">
-        <f>P17+Q16</f>
-        <v/>
-      </c>
-      <c r="R17" s="49">
-        <f>Q17+R16</f>
-        <v/>
-      </c>
-      <c r="S17" s="49">
-        <f>R17+S16</f>
+        <f>30000+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="49">
+        <f>B16+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="49">
+        <f>C16+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="49">
+        <f>D16+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="49">
+        <f>E16+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="49">
+        <f>F16+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="49">
+        <f>G16+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="49">
+        <f>H16+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="49">
+        <f>I16+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="49">
+        <f>J16+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="49">
+        <f>K16+L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="49">
+        <f>L16+M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="49">
+        <f>M16+N15</f>
+        <v/>
+      </c>
+      <c r="O16" s="49">
+        <f>N16+O15</f>
+        <v/>
+      </c>
+      <c r="P16" s="49">
+        <f>O16+P15</f>
+        <v/>
+      </c>
+      <c r="Q16" s="49">
+        <f>P16+Q15</f>
+        <v/>
+      </c>
+      <c r="R16" s="49">
+        <f>Q16+R15</f>
+        <v/>
+      </c>
+      <c r="S16" s="49">
+        <f>R16+S15</f>
         <v/>
       </c>
     </row>
@@ -3964,7 +3900,7 @@
         </is>
       </c>
       <c r="B23" s="53">
-        <f>S17</f>
+        <f>S16</f>
         <v/>
       </c>
     </row>
@@ -3975,31 +3911,31 @@
         </is>
       </c>
       <c r="B24" s="60">
-        <f>MIN(B17:S17)</f>
+        <f>MIN(B16:S16)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Месяц первого положительного EBITDA</t>
+          <t>Месяц первой прибыли (положительная)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>M8 (по плану)</t>
+          <t>M5 (по плану)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Месяц recoup (накопленный кэш &gt; 0)</t>
+          <t>Месяц возврата вложений (кэш &gt; 0)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>M11 (по плану, +0.21 М)</t>
+          <t>M7 (по плану)</t>
         </is>
       </c>
     </row>
@@ -4010,31 +3946,31 @@
         </is>
       </c>
       <c r="B27" s="62">
-        <f>SUM(B13:S13)</f>
+        <f>SUM(B12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>vs предыдущая lean-модель (3 мес build, без маркетинга):</t>
+          <t>vs модель с зарплатой разработчикам 300к/мес:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Месяц точки безубыточности (EBITDA ≥ 0)</t>
+          <t>Месяц первой прибыли</t>
         </is>
       </c>
       <c r="B31" s="63" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C31" s="64" t="inlineStr">
+        <is>
           <t>M8</t>
-        </is>
-      </c>
-      <c r="C31" s="64" t="inlineStr">
-        <is>
-          <t>M11</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -4046,17 +3982,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Месяц recoup (cash &gt; 0)</t>
+          <t>Месяц возврата вложений</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C32" s="64" t="inlineStr">
+        <is>
           <t>M11</t>
-        </is>
-      </c>
-      <c r="C32" s="64" t="inlineStr">
-        <is>
-          <t>M15</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4068,88 +4004,88 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Min cash (макс. провал)</t>
+          <t>Самый большой минус</t>
         </is>
       </c>
       <c r="B33" s="63" t="inlineStr">
         <is>
-          <t>~−2.0 М ₽</t>
+          <t>~−250 К ₽</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
         <is>
-          <t>~−2.65 М ₽</t>
+          <t>~−2 М ₽</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>−24%</t>
+          <t>−87%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>MRR на M18</t>
+          <t>Накопленный кэш на M18</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>~16.3 М ₽</t>
+          <t>~+27 М ₽</t>
         </is>
       </c>
       <c r="C34" s="64" t="inlineStr">
         <is>
-          <t>~9.6 М ₽</t>
+          <t>~+22 М ₽</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>+70%</t>
+          <t>+5 М</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M18</t>
+          <t>Можно ли запуститься на 30к?</t>
         </is>
       </c>
       <c r="B35" s="63" t="inlineStr">
         <is>
-          <t>~+21.8 М ₽</t>
+          <t>ДА (хватит на M1)</t>
         </is>
       </c>
       <c r="C35" s="64" t="inlineStr">
         <is>
-          <t>~+8.6 М ₽</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>+150%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Маркетинг 18 мес</t>
+          <t>Источник разработки</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>~3.4 М ₽</t>
+          <t>founders + AI</t>
         </is>
       </c>
       <c r="C36" s="64" t="inlineStr">
         <is>
-          <t>0 ₽</t>
+          <t>1 senior + 1 mid</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>+бюджет</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -21,7 +21,7 @@
     <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15. Lean финмодель 18м" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15. Lean финмодель 24м" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3029,7 +3029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3056,14 +3056,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финмодель 18 месяцев · M1 запуск → founders-only без зарплат разработчикам</t>
+          <t>Финмодель 24 месяца · founders-only без зарплат + инфраструктура для роста</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Разрабатывают founders сами (AI-инструменты делают это реальным). Постоянка = только юрист 30к. С M2 — маркетинг 100→250к.</t>
+          <t>Юрист 30к/мес · маркетинг 100→300к · инфра наша (DB+API+backups+мониторинг) растёт с базой клиентов 8к→380к/мес. Серверум за клиентский сайт уже в variable COGS.</t>
         </is>
       </c>
     </row>
@@ -3163,6 +3163,36 @@
           <t>M18</t>
         </is>
       </c>
+      <c r="T4" s="55" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="U4" s="55" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+      <c r="V4" s="55" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="W4" s="55" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="X4" s="55" t="inlineStr">
+        <is>
+          <t>M23</t>
+        </is>
+      </c>
+      <c r="Y4" s="55" t="inlineStr">
+        <is>
+          <t>M24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3224,6 +3254,24 @@
       <c r="S5" s="56" t="n">
         <v>4000</v>
       </c>
+      <c r="T5" s="56" t="n">
+        <v>4400</v>
+      </c>
+      <c r="U5" s="56" t="n">
+        <v>4800</v>
+      </c>
+      <c r="V5" s="56" t="n">
+        <v>5200</v>
+      </c>
+      <c r="W5" s="56" t="n">
+        <v>5550</v>
+      </c>
+      <c r="X5" s="56" t="n">
+        <v>5900</v>
+      </c>
+      <c r="Y5" s="56" t="n">
+        <v>6250</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3285,6 +3333,24 @@
       <c r="S6" s="57" t="n">
         <v>4080</v>
       </c>
+      <c r="T6" s="57" t="n">
+        <v>4080</v>
+      </c>
+      <c r="U6" s="57" t="n">
+        <v>4100</v>
+      </c>
+      <c r="V6" s="57" t="n">
+        <v>4120</v>
+      </c>
+      <c r="W6" s="57" t="n">
+        <v>4140</v>
+      </c>
+      <c r="X6" s="57" t="n">
+        <v>4150</v>
+      </c>
+      <c r="Y6" s="57" t="n">
+        <v>4160</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -3364,6 +3430,30 @@
         <f>S5*S6</f>
         <v/>
       </c>
+      <c r="T7" s="49">
+        <f>T5*T6</f>
+        <v/>
+      </c>
+      <c r="U7" s="49">
+        <f>U5*U6</f>
+        <v/>
+      </c>
+      <c r="V7" s="49">
+        <f>V5*V6</f>
+        <v/>
+      </c>
+      <c r="W7" s="49">
+        <f>W5*W6</f>
+        <v/>
+      </c>
+      <c r="X7" s="49">
+        <f>X5*X6</f>
+        <v/>
+      </c>
+      <c r="Y7" s="49">
+        <f>Y5*Y6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -3425,6 +3515,24 @@
       <c r="S8" s="58" t="n">
         <v>0.34</v>
       </c>
+      <c r="T8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X8" s="58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y8" s="58" t="n">
+        <v>0.34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="inlineStr">
@@ -3504,6 +3612,30 @@
         <f>S7*S8</f>
         <v/>
       </c>
+      <c r="T9" s="53">
+        <f>T7*T8</f>
+        <v/>
+      </c>
+      <c r="U9" s="53">
+        <f>U7*U8</f>
+        <v/>
+      </c>
+      <c r="V9" s="53">
+        <f>V7*V8</f>
+        <v/>
+      </c>
+      <c r="W9" s="53">
+        <f>W7*W8</f>
+        <v/>
+      </c>
+      <c r="X9" s="53">
+        <f>X7*X8</f>
+        <v/>
+      </c>
+      <c r="Y9" s="53">
+        <f>Y7*Y8</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3565,6 +3697,24 @@
       <c r="S11" s="43" t="n">
         <v>30000</v>
       </c>
+      <c r="T11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="U11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="V11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="W11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="X11" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Y11" s="43" t="n">
+        <v>30000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3626,241 +3776,410 @@
       <c r="S12" s="59" t="n">
         <v>250000</v>
       </c>
+      <c r="T12" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U12" s="59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="V12" s="59" t="n">
+        <v>300000</v>
+      </c>
+      <c r="W12" s="59" t="n">
+        <v>300000</v>
+      </c>
+      <c r="X12" s="59" t="n">
+        <v>300000</v>
+      </c>
+      <c r="Y12" s="59" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>OPEX: Инфра (наши сервера/БД/бэкапы), ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G13" s="59" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I13" s="59" t="n">
+        <v>55000</v>
+      </c>
+      <c r="J13" s="59" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K13" s="59" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L13" s="59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M13" s="59" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N13" s="59" t="n">
+        <v>140000</v>
+      </c>
+      <c r="O13" s="59" t="n">
+        <v>160000</v>
+      </c>
+      <c r="P13" s="59" t="n">
+        <v>180000</v>
+      </c>
+      <c r="Q13" s="59" t="n">
+        <v>200000</v>
+      </c>
+      <c r="R13" s="59" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S13" s="59" t="n">
+        <v>260000</v>
+      </c>
+      <c r="T13" s="59" t="n">
+        <v>280000</v>
+      </c>
+      <c r="U13" s="59" t="n">
+        <v>300000</v>
+      </c>
+      <c r="V13" s="59" t="n">
+        <v>320000</v>
+      </c>
+      <c r="W13" s="59" t="n">
+        <v>340000</v>
+      </c>
+      <c r="X13" s="59" t="n">
+        <v>360000</v>
+      </c>
+      <c r="Y13" s="59" t="n">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>ИТОГО OPEX, ₽</t>
         </is>
       </c>
-      <c r="B13" s="60">
-        <f>SUM(B11:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="60">
-        <f>SUM(C11:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="60">
-        <f>SUM(D11:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="60">
-        <f>SUM(E11:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="60">
-        <f>SUM(F11:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="60">
-        <f>SUM(G11:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="60">
-        <f>SUM(H11:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="60">
-        <f>SUM(I11:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="60">
-        <f>SUM(J11:J12)</f>
-        <v/>
-      </c>
-      <c r="K13" s="60">
-        <f>SUM(K11:K12)</f>
-        <v/>
-      </c>
-      <c r="L13" s="60">
-        <f>SUM(L11:L12)</f>
-        <v/>
-      </c>
-      <c r="M13" s="60">
-        <f>SUM(M11:M12)</f>
-        <v/>
-      </c>
-      <c r="N13" s="60">
-        <f>SUM(N11:N12)</f>
-        <v/>
-      </c>
-      <c r="O13" s="60">
-        <f>SUM(O11:O12)</f>
-        <v/>
-      </c>
-      <c r="P13" s="60">
-        <f>SUM(P11:P12)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="60">
-        <f>SUM(Q11:Q12)</f>
-        <v/>
-      </c>
-      <c r="R13" s="60">
-        <f>SUM(R11:R12)</f>
-        <v/>
-      </c>
-      <c r="S13" s="60">
-        <f>SUM(S11:S12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>Прибыль/убыток, ₽</t>
-        </is>
-      </c>
-      <c r="B15" s="61">
-        <f>B9-B13</f>
-        <v/>
-      </c>
-      <c r="C15" s="61">
-        <f>C9-C13</f>
-        <v/>
-      </c>
-      <c r="D15" s="61">
-        <f>D9-D13</f>
-        <v/>
-      </c>
-      <c r="E15" s="61">
-        <f>E9-E13</f>
-        <v/>
-      </c>
-      <c r="F15" s="61">
-        <f>F9-F13</f>
-        <v/>
-      </c>
-      <c r="G15" s="61">
-        <f>G9-G13</f>
-        <v/>
-      </c>
-      <c r="H15" s="61">
-        <f>H9-H13</f>
-        <v/>
-      </c>
-      <c r="I15" s="61">
-        <f>I9-I13</f>
-        <v/>
-      </c>
-      <c r="J15" s="61">
-        <f>J9-J13</f>
-        <v/>
-      </c>
-      <c r="K15" s="61">
-        <f>K9-K13</f>
-        <v/>
-      </c>
-      <c r="L15" s="61">
-        <f>L9-L13</f>
-        <v/>
-      </c>
-      <c r="M15" s="61">
-        <f>M9-M13</f>
-        <v/>
-      </c>
-      <c r="N15" s="61">
-        <f>N9-N13</f>
-        <v/>
-      </c>
-      <c r="O15" s="61">
-        <f>O9-O13</f>
-        <v/>
-      </c>
-      <c r="P15" s="61">
-        <f>P9-P13</f>
-        <v/>
-      </c>
-      <c r="Q15" s="61">
-        <f>Q9-Q13</f>
-        <v/>
-      </c>
-      <c r="R15" s="61">
-        <f>R9-R13</f>
-        <v/>
-      </c>
-      <c r="S15" s="61">
-        <f>S9-S13</f>
+      <c r="B14" s="60">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="60">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="60">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="60">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="60">
+        <f>SUM(F11:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="60">
+        <f>SUM(G11:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="60">
+        <f>SUM(H11:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="60">
+        <f>SUM(I11:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="60">
+        <f>SUM(J11:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="60">
+        <f>SUM(K11:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="60">
+        <f>SUM(L11:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="60">
+        <f>SUM(M11:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="60">
+        <f>SUM(N11:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="60">
+        <f>SUM(O11:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="60">
+        <f>SUM(P11:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="60">
+        <f>SUM(Q11:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="60">
+        <f>SUM(R11:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="60">
+        <f>SUM(S11:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="60">
+        <f>SUM(T11:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="60">
+        <f>SUM(U11:U13)</f>
+        <v/>
+      </c>
+      <c r="V14" s="60">
+        <f>SUM(V11:V13)</f>
+        <v/>
+      </c>
+      <c r="W14" s="60">
+        <f>SUM(W11:W13)</f>
+        <v/>
+      </c>
+      <c r="X14" s="60">
+        <f>SUM(X11:X13)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="60">
+        <f>SUM(Y11:Y13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
+          <t>Прибыль/убыток, ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="61">
+        <f>B9-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="61">
+        <f>C9-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="61">
+        <f>D9-D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="61">
+        <f>E9-E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="61">
+        <f>F9-F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="61">
+        <f>G9-G14</f>
+        <v/>
+      </c>
+      <c r="H16" s="61">
+        <f>H9-H14</f>
+        <v/>
+      </c>
+      <c r="I16" s="61">
+        <f>I9-I14</f>
+        <v/>
+      </c>
+      <c r="J16" s="61">
+        <f>J9-J14</f>
+        <v/>
+      </c>
+      <c r="K16" s="61">
+        <f>K9-K14</f>
+        <v/>
+      </c>
+      <c r="L16" s="61">
+        <f>L9-L14</f>
+        <v/>
+      </c>
+      <c r="M16" s="61">
+        <f>M9-M14</f>
+        <v/>
+      </c>
+      <c r="N16" s="61">
+        <f>N9-N14</f>
+        <v/>
+      </c>
+      <c r="O16" s="61">
+        <f>O9-O14</f>
+        <v/>
+      </c>
+      <c r="P16" s="61">
+        <f>P9-P14</f>
+        <v/>
+      </c>
+      <c r="Q16" s="61">
+        <f>Q9-Q14</f>
+        <v/>
+      </c>
+      <c r="R16" s="61">
+        <f>R9-R14</f>
+        <v/>
+      </c>
+      <c r="S16" s="61">
+        <f>S9-S14</f>
+        <v/>
+      </c>
+      <c r="T16" s="61">
+        <f>T9-T14</f>
+        <v/>
+      </c>
+      <c r="U16" s="61">
+        <f>U9-U14</f>
+        <v/>
+      </c>
+      <c r="V16" s="61">
+        <f>V9-V14</f>
+        <v/>
+      </c>
+      <c r="W16" s="61">
+        <f>W9-W14</f>
+        <v/>
+      </c>
+      <c r="X16" s="61">
+        <f>X9-X14</f>
+        <v/>
+      </c>
+      <c r="Y16" s="61">
+        <f>Y9-Y14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
           <t>Накопленный кэш (старт 30к ₽), ₽</t>
         </is>
       </c>
-      <c r="B16" s="61">
-        <f>30000+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="49">
-        <f>B16+C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="49">
-        <f>C16+D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="49">
-        <f>D16+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="49">
-        <f>E16+F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="49">
-        <f>F16+G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="49">
-        <f>G16+H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="49">
-        <f>H16+I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="49">
-        <f>I16+J15</f>
-        <v/>
-      </c>
-      <c r="K16" s="49">
-        <f>J16+K15</f>
-        <v/>
-      </c>
-      <c r="L16" s="49">
-        <f>K16+L15</f>
-        <v/>
-      </c>
-      <c r="M16" s="49">
-        <f>L16+M15</f>
-        <v/>
-      </c>
-      <c r="N16" s="49">
-        <f>M16+N15</f>
-        <v/>
-      </c>
-      <c r="O16" s="49">
-        <f>N16+O15</f>
-        <v/>
-      </c>
-      <c r="P16" s="49">
-        <f>O16+P15</f>
-        <v/>
-      </c>
-      <c r="Q16" s="49">
-        <f>P16+Q15</f>
-        <v/>
-      </c>
-      <c r="R16" s="49">
-        <f>Q16+R15</f>
-        <v/>
-      </c>
-      <c r="S16" s="49">
-        <f>R16+S15</f>
+      <c r="B17" s="61">
+        <f>30000+B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="49">
+        <f>B17+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="49">
+        <f>C17+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="49">
+        <f>D17+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="49">
+        <f>E17+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="49">
+        <f>F17+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="49">
+        <f>G17+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="49">
+        <f>H17+I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="49">
+        <f>I17+J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="49">
+        <f>J17+K16</f>
+        <v/>
+      </c>
+      <c r="L17" s="49">
+        <f>K17+L16</f>
+        <v/>
+      </c>
+      <c r="M17" s="49">
+        <f>L17+M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="49">
+        <f>M17+N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="49">
+        <f>N17+O16</f>
+        <v/>
+      </c>
+      <c r="P17" s="49">
+        <f>O17+P16</f>
+        <v/>
+      </c>
+      <c r="Q17" s="49">
+        <f>P17+Q16</f>
+        <v/>
+      </c>
+      <c r="R17" s="49">
+        <f>Q17+R16</f>
+        <v/>
+      </c>
+      <c r="S17" s="49">
+        <f>R17+S16</f>
+        <v/>
+      </c>
+      <c r="T17" s="49">
+        <f>S17+T16</f>
+        <v/>
+      </c>
+      <c r="U17" s="49">
+        <f>T17+U16</f>
+        <v/>
+      </c>
+      <c r="V17" s="49">
+        <f>U17+V16</f>
+        <v/>
+      </c>
+      <c r="W17" s="49">
+        <f>V17+W16</f>
+        <v/>
+      </c>
+      <c r="X17" s="49">
+        <f>W17+X16</f>
+        <v/>
+      </c>
+      <c r="Y17" s="49">
+        <f>X17+Y16</f>
         <v/>
       </c>
     </row>
@@ -3874,33 +4193,33 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Выручка/мес на M18, ₽</t>
+          <t>Выручка/мес на M24, ₽</t>
         </is>
       </c>
       <c r="B21" s="53">
-        <f>S7</f>
+        <f>Y7</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Выручка/год на M18, ₽</t>
+          <t>Выручка/год на M24, ₽</t>
         </is>
       </c>
       <c r="B22" s="53">
-        <f>S7*12</f>
+        <f>Y7*12</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M18, ₽</t>
+          <t>Накопленный кэш на M24, ₽</t>
         </is>
       </c>
       <c r="B23" s="53">
-        <f>S16</f>
+        <f>Y17</f>
         <v/>
       </c>
     </row>
@@ -3911,179 +4230,201 @@
         </is>
       </c>
       <c r="B24" s="60">
-        <f>MIN(B16:S16)</f>
+        <f>MIN(B17:Y17)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Месяц первой прибыли (положительная)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>M5 (по плану)</t>
-        </is>
+          <t>Платящих клиентов на M24</t>
+        </is>
+      </c>
+      <c r="B25" s="52">
+        <f>Y5</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Месяц возврата вложений (кэш &gt; 0)</t>
+          <t>Месяц первой прибыли (положительная)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>M7 (по плану)</t>
+          <t>M6 (с учётом инфры)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Маркетинг суммарно за 18 мес</t>
-        </is>
-      </c>
-      <c r="B27" s="62">
-        <f>SUM(B12:S12)</f>
+          <t>Месяц возврата вложений (кэш &gt; 0)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>M8 (с учётом инфры)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Маркетинг суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B28" s="62">
+        <f>SUM(B12:Y12)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>vs модель с зарплатой разработчикам 300к/мес:</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Инфра суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B29" s="62">
+        <f>SUM(B13:Y13)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Месяц первой прибыли</t>
-        </is>
-      </c>
-      <c r="B31" s="63" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="C31" s="64" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>+3 мес раньше</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Месяц возврата вложений</t>
-        </is>
-      </c>
-      <c r="B32" s="63" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="C32" s="64" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>+4 мес раньше</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>vs модель с зарплатой разработчикам 300к/мес (с учётом инфры):</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Самый большой минус</t>
+          <t>Месяц первой прибыли</t>
         </is>
       </c>
       <c r="B33" s="63" t="inlineStr">
         <is>
-          <t>~−250 К ₽</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
         <is>
-          <t>~−2 М ₽</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>−87%</t>
+          <t>+3 мес раньше</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M18</t>
+          <t>Месяц возврата вложений</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>~+27 М ₽</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="C34" s="64" t="inlineStr">
         <is>
-          <t>~+22 М ₽</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>+5 М</t>
+          <t>+4 мес раньше</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Можно ли запуститься на 30к?</t>
+          <t>Самый большой минус</t>
         </is>
       </c>
       <c r="B35" s="63" t="inlineStr">
         <is>
-          <t>ДА (хватит на M1)</t>
+          <t>~−305 К ₽</t>
         </is>
       </c>
       <c r="C35" s="64" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>~−2.5 М ₽</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>−88%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>Накопленный кэш на M24</t>
+        </is>
+      </c>
+      <c r="B36" s="63" t="inlineStr">
+        <is>
+          <t>~+67 М ₽</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>~+59 М ₽</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>+8 М</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Можно ли запуститься на 30к?</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="inlineStr">
+        <is>
+          <t>ДА (хватит на M1)</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>Источник разработки</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>founders + AI</t>
         </is>
       </c>
-      <c r="C36" s="64" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>1 senior + 1 mid</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -22,6 +22,7 @@
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15. Lean финмодель 24м" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16. Маркетинг 2026 (Wordstat)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,6 +217,28 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4435,6 +4458,2513 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Семантическое ядро · Wordstat 2026 + воронка 100К ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>71 запрос по 12 нишам. CPC оценка после ухода Google Ads (2022) и AI-хайпа 2024-2025. Перед запуском проверить руками в wordstat.yandex.ru и Прогнозе бюджета Директа.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Запрос</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Показов/мес 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>CPC ₽ 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Ценность 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>создать сайт</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>110</v>
+      </c>
+      <c r="F5" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>сделать сайт</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F6" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>сайт бесплатно</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" s="66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>конструктор сайтов</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>165</v>
+      </c>
+      <c r="F8" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>сайт под ключ</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E9" s="57" t="n">
+        <v>135</v>
+      </c>
+      <c r="F9" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>лендинг создать</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E10" s="57" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>сайт визитка</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E11" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F11" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>сайт самостоятельно</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>одностраничный сайт</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="57" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>сайт без программиста</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>A. Прямой</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>нейросеть сайт</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F15" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ai сайт</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E16" s="57" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>нейросеть создать сайт</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="57" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>сайт через chatgpt</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>искусственный интеллект сайт</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E19" s="57" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>сделать сайт нейросетью</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="57" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ai конструктор сайтов</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F21" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>сайт с помощью ai</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="n">
+        <v>950</v>
+      </c>
+      <c r="E22" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F22" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>генератор сайтов ai</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>B. AI ★</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E23" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F23" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>тильда</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E24" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="F24" s="66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>bitrix сайт сделать</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E25" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F25" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>wix или tilda</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F26" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>tilda аналог</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F27" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>конструктор сайтов сравнение</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E28" s="57" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>замена tilda</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>C. Бренд</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E29" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F29" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>доставка еды сайт</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E30" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>сайт ресторана</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E31" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F31" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>сайт для кафе</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F32" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>сайт кофейни</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F33" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>сайт для бара</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E34" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F34" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>сайт пиццерии</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>D. Кафе</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="n">
+        <v>500</v>
+      </c>
+      <c r="E35" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F35" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>создать интернет магазин</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D36" s="56" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E36" s="57" t="n">
+        <v>165</v>
+      </c>
+      <c r="F36" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>интернет магазин с нуля</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D37" s="56" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E37" s="57" t="n">
+        <v>130</v>
+      </c>
+      <c r="F37" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>интернет магазин под ключ</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E38" s="57" t="n">
+        <v>145</v>
+      </c>
+      <c r="F38" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>магазин одежды сайт</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E39" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F39" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>сайт магазина бесплатно</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E40" s="57" t="n">
+        <v>90</v>
+      </c>
+      <c r="F40" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>сайт цветочного магазина</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>E. Магазин</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E41" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F41" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>сайт юриста</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>F. Юрист</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="57" t="n">
+        <v>105</v>
+      </c>
+      <c r="F42" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>сайт адвоката</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>F. Юрист</t>
+        </is>
+      </c>
+      <c r="D43" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="57" t="n">
+        <v>105</v>
+      </c>
+      <c r="F43" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>сайт юридической компании</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>F. Юрист</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E44" s="57" t="n">
+        <v>125</v>
+      </c>
+      <c r="F44" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>сайт нотариуса</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>F. Юрист</t>
+        </is>
+      </c>
+      <c r="D45" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="57" t="n">
+        <v>90</v>
+      </c>
+      <c r="F45" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>сайт визитка юристу</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>F. Юрист</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="n">
+        <v>400</v>
+      </c>
+      <c r="E46" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F46" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>сайт салона красоты</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>G. Красота</t>
+        </is>
+      </c>
+      <c r="D47" s="56" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F47" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>сайт мастера маникюра</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>G. Красота</t>
+        </is>
+      </c>
+      <c r="D48" s="56" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E48" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F48" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>сайт косметолога</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>G. Красота</t>
+        </is>
+      </c>
+      <c r="D49" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F49" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>сайт парикмахерской</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>G. Красота</t>
+        </is>
+      </c>
+      <c r="D50" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E50" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F50" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>сайт барбершопа</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>G. Красота</t>
+        </is>
+      </c>
+      <c r="D51" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E51" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F51" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>сайт клиники</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>H. Медицина</t>
+        </is>
+      </c>
+      <c r="D52" s="56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="57" t="n">
+        <v>145</v>
+      </c>
+      <c r="F52" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>сайт врача</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>H. Медицина</t>
+        </is>
+      </c>
+      <c r="D53" s="56" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E53" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F53" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>сайт стоматологии</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>H. Медицина</t>
+        </is>
+      </c>
+      <c r="D54" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E54" s="57" t="n">
+        <v>130</v>
+      </c>
+      <c r="F54" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>сайт медцентра</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>H. Медицина</t>
+        </is>
+      </c>
+      <c r="D55" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E55" s="57" t="n">
+        <v>145</v>
+      </c>
+      <c r="F55" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>сайт ветклиники</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>H. Медицина</t>
+        </is>
+      </c>
+      <c r="D56" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E56" s="57" t="n">
+        <v>105</v>
+      </c>
+      <c r="F56" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>сайт автосервиса</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>I. Авто</t>
+        </is>
+      </c>
+      <c r="D57" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F57" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>сайт автосалона</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>I. Авто</t>
+        </is>
+      </c>
+      <c r="D58" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E58" s="57" t="n">
+        <v>115</v>
+      </c>
+      <c r="F58" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>сайт шиномонтажа</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>I. Авто</t>
+        </is>
+      </c>
+      <c r="D59" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E59" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F59" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>сайт детейлинга</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>I. Авто</t>
+        </is>
+      </c>
+      <c r="D60" s="56" t="n">
+        <v>500</v>
+      </c>
+      <c r="E60" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F60" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>сайт агентства недвижимости</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>J. Недв</t>
+        </is>
+      </c>
+      <c r="D61" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E61" s="57" t="n">
+        <v>125</v>
+      </c>
+      <c r="F61" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>сайт риэлтора</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>J. Недв</t>
+        </is>
+      </c>
+      <c r="D62" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F62" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>сайт жк</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>J. Недв</t>
+        </is>
+      </c>
+      <c r="D63" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E63" s="57" t="n">
+        <v>175</v>
+      </c>
+      <c r="F63" s="65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>сайт застройщика</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>J. Недв</t>
+        </is>
+      </c>
+      <c r="D64" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E64" s="57" t="n">
+        <v>145</v>
+      </c>
+      <c r="F64" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>сайт психолога</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>K. Образ</t>
+        </is>
+      </c>
+      <c r="D65" s="56" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E65" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F65" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>сайт репетитора</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>K. Образ</t>
+        </is>
+      </c>
+      <c r="D66" s="56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F66" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>сайт онлайн школы</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>K. Образ</t>
+        </is>
+      </c>
+      <c r="D67" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E67" s="57" t="n">
+        <v>105</v>
+      </c>
+      <c r="F67" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>сайт коуча</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>K. Образ</t>
+        </is>
+      </c>
+      <c r="D68" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E68" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F68" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>сайт фитнес тренера</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>K. Образ</t>
+        </is>
+      </c>
+      <c r="D69" s="56" t="n">
+        <v>700</v>
+      </c>
+      <c r="E69" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="F69" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>простой сайт сделать</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D70" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E70" s="57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F70" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>сайт за день</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D71" s="56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E71" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="F71" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>сайт быстро недорого</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D72" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E72" s="57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F72" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>сайт визитка дёшево</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D73" s="56" t="n">
+        <v>800</v>
+      </c>
+      <c r="E73" s="57" t="n">
+        <v>55</v>
+      </c>
+      <c r="F73" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>сайт без знаний программирования</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D74" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="E74" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="F74" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>сделать сайт самому без программиста</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>L. Pain ★</t>
+        </is>
+      </c>
+      <c r="D75" s="56" t="n">
+        <v>400</v>
+      </c>
+      <c r="E75" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО · 71 ключей</t>
+        </is>
+      </c>
+      <c r="D77" s="68">
+        <f>SUM(D5:D76)</f>
+        <v/>
+      </c>
+      <c r="E77" s="69">
+        <f>AVERAGE(E5:E76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>ВОРОНКА 100К ₽ → ПЛАТЯЩИЕ КЛИЕНТЫ · 4 СЦЕНАРИЯ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Бюджет ₽/мес</t>
+        </is>
+      </c>
+      <c r="B82" s="40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>← поменяй число — пересчитается всё ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>CPC ₽</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Кликов = визитов</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Цена визита ₽</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Конверсия лендинга</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Trial регистраций</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Trial → Paid</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Платящих/мес</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>CAC ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>А. Песимистичный (M2 cold start)</t>
+        </is>
+      </c>
+      <c r="B85" s="40" t="n">
+        <v>95</v>
+      </c>
+      <c r="C85" s="16">
+        <f>$B$82/B85</f>
+        <v/>
+      </c>
+      <c r="D85" s="43">
+        <f>B85</f>
+        <v/>
+      </c>
+      <c r="E85" s="70" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F85" s="16">
+        <f>C85*E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H85" s="71">
+        <f>F85*G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="60">
+        <f>$B$82/H85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Б. Реалистичный (M3, базовая оптимизация)</t>
+        </is>
+      </c>
+      <c r="B86" s="40" t="n">
+        <v>75</v>
+      </c>
+      <c r="C86" s="16">
+        <f>$B$82/B86</f>
+        <v/>
+      </c>
+      <c r="D86" s="43">
+        <f>B86</f>
+        <v/>
+      </c>
+      <c r="E86" s="70" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F86" s="16">
+        <f>C86*E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="70" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H86" s="71">
+        <f>F86*G86</f>
+        <v/>
+      </c>
+      <c r="I86" s="60">
+        <f>$B$82/H86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>В. Оптимистичный (M5, отшлифованный)</t>
+        </is>
+      </c>
+      <c r="B87" s="40" t="n">
+        <v>55</v>
+      </c>
+      <c r="C87" s="16">
+        <f>$B$82/B87</f>
+        <v/>
+      </c>
+      <c r="D87" s="43">
+        <f>B87</f>
+        <v/>
+      </c>
+      <c r="E87" s="70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F87" s="16">
+        <f>C87*E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H87" s="71">
+        <f>F87*G87</f>
+        <v/>
+      </c>
+      <c r="I87" s="53">
+        <f>$B$82/H87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Г. Идеал (M6+ vertical+long-tail)</t>
+        </is>
+      </c>
+      <c r="B88" s="40" t="n">
+        <v>45</v>
+      </c>
+      <c r="C88" s="16">
+        <f>$B$82/B88</f>
+        <v/>
+      </c>
+      <c r="D88" s="43">
+        <f>B88</f>
+        <v/>
+      </c>
+      <c r="E88" s="70" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F88" s="16">
+        <f>C88*E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H88" s="71">
+        <f>F88*G88</f>
+        <v/>
+      </c>
+      <c r="I88" s="53">
+        <f>$B$82/H88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ГРАФИК ПЕРВЫХ 6 МЕСЯЦЕВ НА 100К ₽/мес DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Что происходит</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>CPC ₽</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>CV лендинга</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Trial → Paid</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Кликов</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Платящих</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>CAC ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>M1 Soft launch (без рекламы)</t>
+        </is>
+      </c>
+      <c r="C94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>M2 Cold start</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="D95" s="74" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E95" s="74" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F95" s="16">
+        <f>$B$82/C95</f>
+        <v/>
+      </c>
+      <c r="G95" s="16">
+        <f>F95*D95</f>
+        <v/>
+      </c>
+      <c r="H95" s="71">
+        <f>G95*E95</f>
+        <v/>
+      </c>
+      <c r="I95" s="43">
+        <f>$B$82/H95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>M3 Первая оптимизация</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="D96" s="74" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E96" s="74" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F96" s="16">
+        <f>$B$82/C96</f>
+        <v/>
+      </c>
+      <c r="G96" s="16">
+        <f>F96*D96</f>
+        <v/>
+      </c>
+      <c r="H96" s="71">
+        <f>G96*E96</f>
+        <v/>
+      </c>
+      <c r="I96" s="43">
+        <f>$B$82/H96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>M4 Vertical landing pages</t>
+        </is>
+      </c>
+      <c r="C97" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="D97" s="74" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E97" s="74" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F97" s="16">
+        <f>$B$82/C97</f>
+        <v/>
+      </c>
+      <c r="G97" s="16">
+        <f>F97*D97</f>
+        <v/>
+      </c>
+      <c r="H97" s="71">
+        <f>G97*E97</f>
+        <v/>
+      </c>
+      <c r="I97" s="43">
+        <f>$B$82/H97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>M5 Retargeting + бренд</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="n">
+        <v>55</v>
+      </c>
+      <c r="D98" s="74" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E98" s="74" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F98" s="16">
+        <f>$B$82/C98</f>
+        <v/>
+      </c>
+      <c r="G98" s="16">
+        <f>F98*D98</f>
+        <v/>
+      </c>
+      <c r="H98" s="71">
+        <f>G98*E98</f>
+        <v/>
+      </c>
+      <c r="I98" s="43">
+        <f>$B$82/H98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>M6 Зрелая воронка</t>
+        </is>
+      </c>
+      <c r="C99" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="D99" s="74" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E99" s="74" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F99" s="16">
+        <f>$B$82/C99</f>
+        <v/>
+      </c>
+      <c r="G99" s="16">
+        <f>F99*D99</f>
+        <v/>
+      </c>
+      <c r="H99" s="71">
+        <f>G99*E99</f>
+        <v/>
+      </c>
+      <c r="I99" s="43">
+        <f>$B$82/H99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО за 6 мес (новых платящих)</t>
+        </is>
+      </c>
+      <c r="H100" s="75">
+        <f>SUM(H94:H99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>РАСХОЖДЕНИЕ С ФИНПЛАНОМ (лист 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>По финплану</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>По воронке Direct 100К</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Дельта</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Что компенсирует</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C107" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" s="73" t="inlineStr">
+        <is>
+          <t>−29</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Soft-launch buzz + Telegram founders</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="73" t="inlineStr">
+        <is>
+          <t>−78</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>VC.ru/Habr статья + первые кейсы</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C109" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" s="73" t="inlineStr">
+        <is>
+          <t>−146</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Multi-channel (VK + Telegram + контент)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="33" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="C110" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D110" s="73" t="inlineStr">
+        <is>
+          <t>−243</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Retargeting + первая узнаваемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="33" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="C111" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" s="73" t="inlineStr">
+        <is>
+          <t>−371</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Зрелая воронка + B2B продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>M7+</t>
+        </is>
+      </c>
+      <c r="B112" s="72" t="inlineStr">
+        <is>
+          <t>540+</t>
+        </is>
+      </c>
+      <c r="C112" s="72" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
+      <c r="D112" s="63" t="inlineStr">
+        <is>
+          <t>догоняет</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Бренд + кейсы + органика</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="76" t="inlineStr">
+        <is>
+          <t>ВЫВОД: 100К ₽ только в Direct в первый месяц = 1-2 платящих. Финплан с М2=30 платящих требует мульти-канал (Direct 60К + VK 25К + Telegram 15К) ИЛИ soft-launch buzz (VC.ru/Habr) + B2B sales. Реалистичный график: М2=5-10, М3=18-25, М6=250-300, М7+ догоняет план.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A115:I115"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -22,7 +22,7 @@
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15. Lean финмодель 24м" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16. Маркетинг 2026 (Wordstat)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16. Маркетинг 2026 (clean)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,13 +217,10 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4464,7 +4461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4481,14 +4478,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Семантическое ядро · Wordstat 2026 + воронка 100К ₽</t>
+          <t>Семантическое ядро · 63 ЧИСТЫХ запроса · Wordstat 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>71 запрос по 12 нишам. CPC оценка после ухода Google Ads (2022) и AI-хайпа 2024-2025. Перед запуском проверить руками в wordstat.yandex.ru и Прогнозе бюджета Директа.</t>
+          <t>Только запросы с явным buying intent: vertical / AI-specific / pain-driven / research. Грязные (бренд+generic+freebie) исключены — экономят бюджет в 2-3× через downstream conversion.</t>
         </is>
       </c>
     </row>
@@ -4530,22 +4527,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>создать сайт</t>
+          <t>сайт под ключ</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>A. Прямой intent</t>
         </is>
       </c>
       <c r="D5" s="56" t="n">
-        <v>80000</v>
+        <v>18000</v>
       </c>
       <c r="E5" s="57" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4554,22 +4551,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>сделать сайт</t>
+          <t>лендинг создать</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>A. Прямой intent</t>
         </is>
       </c>
       <c r="D6" s="56" t="n">
-        <v>70000</v>
+        <v>15000</v>
       </c>
       <c r="E6" s="57" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4578,22 +4575,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>сайт бесплатно</t>
+          <t>сайт самостоятельно</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>A. Прямой intent</t>
         </is>
       </c>
       <c r="D7" s="56" t="n">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E7" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F7" s="66" t="n">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="F7" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4602,21 +4599,21 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>конструктор сайтов</t>
+          <t>одностраничный сайт</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>A. Прямой intent</t>
         </is>
       </c>
       <c r="D8" s="56" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="E8" s="57" t="n">
-        <v>165</v>
-      </c>
-      <c r="F8" s="67" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" s="65" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4626,22 +4623,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>сайт под ключ</t>
+          <t>сайт без программиста</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>A. Прямой intent</t>
         </is>
       </c>
       <c r="D9" s="56" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="E9" s="57" t="n">
-        <v>135</v>
-      </c>
-      <c r="F9" s="67" t="n">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="F9" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -4650,22 +4647,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>лендинг создать</t>
+          <t>нейросеть сайт</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>B. AI ★</t>
         </is>
       </c>
       <c r="D10" s="56" t="n">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="E10" s="57" t="n">
-        <v>120</v>
-      </c>
-      <c r="F10" s="67" t="n">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="F10" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -4674,22 +4671,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>сайт визитка</t>
+          <t>ai сайт</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>B. AI ★</t>
         </is>
       </c>
       <c r="D11" s="56" t="n">
-        <v>12000</v>
+        <v>2800</v>
       </c>
       <c r="E11" s="57" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4698,22 +4695,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>сайт самостоятельно</t>
+          <t>нейросеть создать сайт</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>B. AI ★</t>
         </is>
       </c>
       <c r="D12" s="56" t="n">
-        <v>8000</v>
+        <v>2200</v>
       </c>
       <c r="E12" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F12" s="67" t="n">
-        <v>4</v>
+      <c r="F12" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -4722,21 +4719,21 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>одностраничный сайт</t>
+          <t>сайт через chatgpt</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>B. AI ★</t>
         </is>
       </c>
       <c r="D13" s="56" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="E13" s="57" t="n">
-        <v>90</v>
-      </c>
-      <c r="F13" s="67" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" s="65" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4746,22 +4743,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>сайт без программиста</t>
+          <t>искусственный интеллект сайт</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>A. Прямой</t>
+          <t>B. AI ★</t>
         </is>
       </c>
       <c r="D14" s="56" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E14" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F14" s="67" t="n">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="F14" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4770,7 +4767,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>нейросеть сайт</t>
+          <t>сделать сайт нейросетью</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4779,12 +4776,12 @@
         </is>
       </c>
       <c r="D15" s="56" t="n">
-        <v>4500</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F15" s="67" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4794,7 +4791,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ai сайт</t>
+          <t>ai конструктор сайтов</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4803,12 +4800,12 @@
         </is>
       </c>
       <c r="D16" s="56" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="E16" s="57" t="n">
-        <v>90</v>
-      </c>
-      <c r="F16" s="67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F16" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4818,7 +4815,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>нейросеть создать сайт</t>
+          <t>сайт с помощью ai</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4827,12 +4824,12 @@
         </is>
       </c>
       <c r="D17" s="56" t="n">
-        <v>2200</v>
+        <v>950</v>
       </c>
       <c r="E17" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="F17" s="67" t="n">
+        <v>85</v>
+      </c>
+      <c r="F17" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4842,7 +4839,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>сайт через chatgpt</t>
+          <t>генератор сайтов ai</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4851,13 +4848,13 @@
         </is>
       </c>
       <c r="D18" s="56" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E18" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F18" s="67" t="n">
-        <v>4</v>
+        <v>95</v>
+      </c>
+      <c r="F18" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -4866,22 +4863,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>искусственный интеллект сайт</t>
+          <t>wix или tilda</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>B. AI ★</t>
+          <t>C. Research</t>
         </is>
       </c>
       <c r="D19" s="56" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="F19" s="67" t="n">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="F19" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4890,21 +4887,21 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>сделать сайт нейросетью</t>
+          <t>tilda аналог</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>B. AI ★</t>
+          <t>C. Research</t>
         </is>
       </c>
       <c r="D20" s="56" t="n">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E20" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="F20" s="67" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4914,22 +4911,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ai конструктор сайтов</t>
+          <t>конструктор сайтов сравнение</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>B. AI ★</t>
+          <t>C. Research</t>
         </is>
       </c>
       <c r="D21" s="56" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E21" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F21" s="67" t="n">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="F21" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -4938,21 +4935,21 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>сайт с помощью ai</t>
+          <t>замена tilda</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>B. AI ★</t>
+          <t>C. Research</t>
         </is>
       </c>
       <c r="D22" s="56" t="n">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="E22" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F22" s="67" t="n">
+        <v>70</v>
+      </c>
+      <c r="F22" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4962,22 +4959,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>генератор сайтов ai</t>
+          <t>доставка еды сайт</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>B. AI ★</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D23" s="56" t="n">
-        <v>800</v>
+        <v>4500</v>
       </c>
       <c r="E23" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F23" s="67" t="n">
-        <v>5</v>
+      <c r="F23" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -4986,22 +4983,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>тильда</t>
+          <t>сайт ресторана</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D24" s="56" t="n">
-        <v>200000</v>
+        <v>3000</v>
       </c>
       <c r="E24" s="57" t="n">
-        <v>35</v>
-      </c>
-      <c r="F24" s="66" t="n">
-        <v>1</v>
+        <v>85</v>
+      </c>
+      <c r="F24" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -5010,22 +5007,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>bitrix сайт сделать</t>
+          <t>сайт для кафе</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D25" s="56" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="E25" s="57" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F25" s="65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -5034,21 +5031,21 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>wix или tilda</t>
+          <t>сайт кофейни</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D26" s="56" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E26" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F26" s="67" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5058,22 +5055,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>tilda аналог</t>
+          <t>сайт для бара</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D27" s="56" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E27" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F27" s="67" t="n">
-        <v>5</v>
+        <v>70</v>
+      </c>
+      <c r="F27" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -5082,22 +5079,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>конструктор сайтов сравнение</t>
+          <t>сайт пиццерии</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>D. Кафе</t>
         </is>
       </c>
       <c r="D28" s="56" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E28" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="F28" s="67" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="F28" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -5106,22 +5103,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>замена tilda</t>
+          <t>создать интернет магазин</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>C. Бренд</t>
+          <t>E. Магазин</t>
         </is>
       </c>
       <c r="D29" s="56" t="n">
-        <v>600</v>
+        <v>12000</v>
       </c>
       <c r="E29" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F29" s="67" t="n">
-        <v>5</v>
+        <v>165</v>
+      </c>
+      <c r="F29" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -5130,21 +5127,21 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>доставка еды сайт</t>
+          <t>интернет магазин с нуля</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>E. Магазин</t>
         </is>
       </c>
       <c r="D30" s="56" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E30" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F30" s="67" t="n">
+        <v>130</v>
+      </c>
+      <c r="F30" s="65" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5154,22 +5151,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>сайт ресторана</t>
+          <t>интернет магазин под ключ</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>E. Магазин</t>
         </is>
       </c>
       <c r="D31" s="56" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E31" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F31" s="67" t="n">
-        <v>5</v>
+        <v>145</v>
+      </c>
+      <c r="F31" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -5178,22 +5175,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>сайт для кафе</t>
+          <t>магазин одежды сайт</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>E. Магазин</t>
         </is>
       </c>
       <c r="D32" s="56" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F32" s="67" t="n">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="F32" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5202,21 +5199,21 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>сайт кофейни</t>
+          <t>сайт цветочного магазина</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>E. Магазин</t>
         </is>
       </c>
       <c r="D33" s="56" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E33" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="67" t="n">
+      <c r="F33" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5226,22 +5223,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>сайт для бара</t>
+          <t>сайт юриста</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>F. Юрист</t>
         </is>
       </c>
       <c r="D34" s="56" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="E34" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F34" s="67" t="n">
-        <v>4</v>
+        <v>105</v>
+      </c>
+      <c r="F34" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -5250,21 +5247,21 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>сайт пиццерии</t>
+          <t>сайт адвоката</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>D. Кафе</t>
+          <t>F. Юрист</t>
         </is>
       </c>
       <c r="D35" s="56" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F35" s="67" t="n">
+        <v>105</v>
+      </c>
+      <c r="F35" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5274,22 +5271,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>создать интернет магазин</t>
+          <t>сайт юридической компании</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>F. Юрист</t>
         </is>
       </c>
       <c r="D36" s="56" t="n">
-        <v>12000</v>
+        <v>800</v>
       </c>
       <c r="E36" s="57" t="n">
-        <v>165</v>
-      </c>
-      <c r="F36" s="67" t="n">
-        <v>4</v>
+        <v>125</v>
+      </c>
+      <c r="F36" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -5298,22 +5295,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>интернет магазин с нуля</t>
+          <t>сайт нотариуса</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>F. Юрист</t>
         </is>
       </c>
       <c r="D37" s="56" t="n">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="E37" s="57" t="n">
-        <v>130</v>
-      </c>
-      <c r="F37" s="67" t="n">
-        <v>4</v>
+        <v>90</v>
+      </c>
+      <c r="F37" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -5322,22 +5319,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>интернет магазин под ключ</t>
+          <t>сайт визитка юристу</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>F. Юрист</t>
         </is>
       </c>
       <c r="D38" s="56" t="n">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="E38" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F38" s="67" t="n">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="F38" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -5346,22 +5343,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>магазин одежды сайт</t>
+          <t>сайт салона красоты</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>G. Красота</t>
         </is>
       </c>
       <c r="D39" s="56" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E39" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F39" s="67" t="n">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="F39" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -5370,22 +5367,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>сайт магазина бесплатно</t>
+          <t>сайт мастера маникюра</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>G. Красота</t>
         </is>
       </c>
       <c r="D40" s="56" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E40" s="57" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F40" s="65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -5394,21 +5391,21 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>сайт цветочного магазина</t>
+          <t>сайт косметолога</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>E. Магазин</t>
+          <t>G. Красота</t>
         </is>
       </c>
       <c r="D41" s="56" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="E41" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F41" s="67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F41" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5418,21 +5415,21 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>сайт юриста</t>
+          <t>сайт парикмахерской</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>F. Юрист</t>
+          <t>G. Красота</t>
         </is>
       </c>
       <c r="D42" s="56" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="E42" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F42" s="67" t="n">
+        <v>65</v>
+      </c>
+      <c r="F42" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5442,21 +5439,21 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>сайт адвоката</t>
+          <t>сайт барбершопа</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>F. Юрист</t>
+          <t>G. Красота</t>
         </is>
       </c>
       <c r="D43" s="56" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E43" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F43" s="67" t="n">
+        <v>70</v>
+      </c>
+      <c r="F43" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5466,22 +5463,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>сайт юридической компании</t>
+          <t>сайт клиники</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>F. Юрист</t>
+          <t>H. Медицина</t>
         </is>
       </c>
       <c r="D44" s="56" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E44" s="57" t="n">
-        <v>125</v>
-      </c>
-      <c r="F44" s="67" t="n">
-        <v>5</v>
+        <v>145</v>
+      </c>
+      <c r="F44" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -5490,21 +5487,21 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>сайт нотариуса</t>
+          <t>сайт врача</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>F. Юрист</t>
+          <t>H. Медицина</t>
         </is>
       </c>
       <c r="D45" s="56" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E45" s="57" t="n">
-        <v>90</v>
-      </c>
-      <c r="F45" s="67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F45" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5514,21 +5511,21 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>сайт визитка юристу</t>
+          <t>сайт стоматологии</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>F. Юрист</t>
+          <t>H. Медицина</t>
         </is>
       </c>
       <c r="D46" s="56" t="n">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="E46" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F46" s="67" t="n">
+        <v>130</v>
+      </c>
+      <c r="F46" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5538,22 +5535,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>сайт салона красоты</t>
+          <t>сайт медцентра</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>G. Красота</t>
+          <t>H. Медицина</t>
         </is>
       </c>
       <c r="D47" s="56" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F47" s="67" t="n">
-        <v>5</v>
+        <v>145</v>
+      </c>
+      <c r="F47" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -5562,21 +5559,21 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>сайт мастера маникюра</t>
+          <t>сайт ветклиники</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>G. Красота</t>
+          <t>H. Медицина</t>
         </is>
       </c>
       <c r="D48" s="56" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="E48" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F48" s="67" t="n">
+        <v>105</v>
+      </c>
+      <c r="F48" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5586,21 +5583,21 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>сайт косметолога</t>
+          <t>сайт автосервиса</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>G. Красота</t>
+          <t>I. Авто</t>
         </is>
       </c>
       <c r="D49" s="56" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E49" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F49" s="67" t="n">
+        <v>85</v>
+      </c>
+      <c r="F49" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5610,22 +5607,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>сайт парикмахерской</t>
+          <t>сайт автосалона</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>G. Красота</t>
+          <t>I. Авто</t>
         </is>
       </c>
       <c r="D50" s="56" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E50" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F50" s="67" t="n">
-        <v>5</v>
+        <v>115</v>
+      </c>
+      <c r="F50" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -5634,21 +5631,21 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>сайт барбершопа</t>
+          <t>сайт шиномонтажа</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>G. Красота</t>
+          <t>I. Авто</t>
         </is>
       </c>
       <c r="D51" s="56" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E51" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F51" s="67" t="n">
+        <v>65</v>
+      </c>
+      <c r="F51" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5658,22 +5655,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>сайт клиники</t>
+          <t>сайт детейлинга</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>I. Авто</t>
         </is>
       </c>
       <c r="D52" s="56" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="E52" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F52" s="67" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="F52" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -5682,22 +5679,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>сайт врача</t>
+          <t>сайт агентства недвижимости</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D53" s="56" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="E53" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F53" s="67" t="n">
-        <v>5</v>
+        <v>125</v>
+      </c>
+      <c r="F53" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -5706,21 +5703,21 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>сайт стоматологии</t>
+          <t>сайт риэлтора</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D54" s="56" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E54" s="57" t="n">
-        <v>130</v>
-      </c>
-      <c r="F54" s="67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F54" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5730,22 +5727,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>сайт медцентра</t>
+          <t>сайт жк</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D55" s="56" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E55" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F55" s="67" t="n">
-        <v>4</v>
+        <v>175</v>
+      </c>
+      <c r="F55" s="66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -5754,22 +5751,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>сайт ветклиники</t>
+          <t>сайт застройщика</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D56" s="56" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E56" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F56" s="67" t="n">
-        <v>5</v>
+        <v>145</v>
+      </c>
+      <c r="F56" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -5778,21 +5775,21 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>сайт автосервиса</t>
+          <t>сайт психолога</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D57" s="56" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="E57" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F57" s="67" t="n">
+        <v>95</v>
+      </c>
+      <c r="F57" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5802,22 +5799,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>сайт автосалона</t>
+          <t>сайт репетитора</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D58" s="56" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E58" s="57" t="n">
-        <v>115</v>
-      </c>
-      <c r="F58" s="67" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="F58" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -5826,22 +5823,22 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>сайт шиномонтажа</t>
+          <t>сайт онлайн школы</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D59" s="56" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F59" s="67" t="n">
-        <v>5</v>
+        <v>105</v>
+      </c>
+      <c r="F59" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -5850,21 +5847,21 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>сайт детейлинга</t>
+          <t>сайт коуча</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D60" s="56" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E60" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F60" s="67" t="n">
+        <v>85</v>
+      </c>
+      <c r="F60" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5874,22 +5871,22 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>сайт агентства недвижимости</t>
+          <t>сайт фитнес тренера</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D61" s="56" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="E61" s="57" t="n">
-        <v>125</v>
-      </c>
-      <c r="F61" s="67" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="F61" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -5898,22 +5895,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>сайт риэлтора</t>
+          <t>простой сайт сделать</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D62" s="56" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F62" s="67" t="n">
-        <v>5</v>
+        <v>70</v>
+      </c>
+      <c r="F62" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -5922,22 +5919,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>сайт жк</t>
+          <t>сайт за день</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D63" s="56" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E63" s="57" t="n">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="F63" s="65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -5946,22 +5943,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>сайт застройщика</t>
+          <t>сайт быстро недорого</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D64" s="56" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E64" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F64" s="67" t="n">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="F64" s="65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -5970,22 +5967,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>сайт психолога</t>
+          <t>сайт визитка дёшево</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D65" s="56" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="E65" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F65" s="67" t="n">
-        <v>5</v>
+        <v>55</v>
+      </c>
+      <c r="F65" s="65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -5994,21 +5991,21 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>сайт репетитора</t>
+          <t>сайт без знаний программирования</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D66" s="56" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="E66" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F66" s="67" t="n">
+        <v>65</v>
+      </c>
+      <c r="F66" s="65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6018,948 +6015,792 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>сайт онлайн школы</t>
+          <t>сделать сайт самому без программиста</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D67" s="56" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="E67" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F67" s="67" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>сайт коуча</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>K. Образ</t>
-        </is>
-      </c>
-      <c r="D68" s="56" t="n">
-        <v>800</v>
-      </c>
-      <c r="E68" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="F67" s="65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО · 63 ключей</t>
+        </is>
+      </c>
+      <c r="D69" s="67">
+        <f>SUM(D5:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="68">
+        <f>AVERAGE(E5:E68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>ВОРОНКА 100К ₽ → ПЛАТЯЩИЕ КЛИЕНТЫ · 4 СЦЕНАРИЯ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Бюджет ₽/мес</t>
+        </is>
+      </c>
+      <c r="B74" s="40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>← поменяй число — пересчитается всё ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>CPC ₽</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Кликов = визитов</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Цена визита ₽</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Конверсия лендинга</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Trial регистраций</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Trial → Paid</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Платящих/мес</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>CAC ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>А. Cold start M2 (clean targeting)</t>
+        </is>
+      </c>
+      <c r="B77" s="40" t="n">
         <v>85</v>
       </c>
-      <c r="F68" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="C77" s="16">
+        <f>$B$74/B77</f>
+        <v/>
+      </c>
+      <c r="D77" s="43">
+        <f>B77</f>
+        <v/>
+      </c>
+      <c r="E77" s="69" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F77" s="16">
+        <f>C77*E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="69" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H77" s="70">
+        <f>F77*G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="60">
+        <f>$B$74/H77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Б. Базовая оптимизация M3</t>
+        </is>
+      </c>
+      <c r="B78" s="40" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" s="16">
+        <f>$B$74/B78</f>
+        <v/>
+      </c>
+      <c r="D78" s="43">
+        <f>B78</f>
+        <v/>
+      </c>
+      <c r="E78" s="69" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F78" s="16">
+        <f>C78*E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="69" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H78" s="70">
+        <f>F78*G78</f>
+        <v/>
+      </c>
+      <c r="I78" s="60">
+        <f>$B$74/H78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>В. Vertical landing pages M4</t>
+        </is>
+      </c>
+      <c r="B79" s="40" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>сайт фитнес тренера</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>K. Образ</t>
-        </is>
-      </c>
-      <c r="D69" s="56" t="n">
-        <v>700</v>
-      </c>
-      <c r="E69" s="57" t="n">
+      <c r="C79" s="16">
+        <f>$B$74/B79</f>
+        <v/>
+      </c>
+      <c r="D79" s="43">
+        <f>B79</f>
+        <v/>
+      </c>
+      <c r="E79" s="69" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F79" s="16">
+        <f>C79*E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H79" s="70">
+        <f>F79*G79</f>
+        <v/>
+      </c>
+      <c r="I79" s="53">
+        <f>$B$74/H79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Г. Зрелая воронка M5+</t>
+        </is>
+      </c>
+      <c r="B80" s="40" t="n">
+        <v>60</v>
+      </c>
+      <c r="C80" s="16">
+        <f>$B$74/B80</f>
+        <v/>
+      </c>
+      <c r="D80" s="43">
+        <f>B80</f>
+        <v/>
+      </c>
+      <c r="E80" s="69" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F80" s="16">
+        <f>C80*E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="69" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H80" s="70">
+        <f>F80*G80</f>
+        <v/>
+      </c>
+      <c r="I80" s="53">
+        <f>$B$74/H80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Д. Идеал M6+ (LTV/CAC 2.4)</t>
+        </is>
+      </c>
+      <c r="B81" s="40" t="n">
+        <v>55</v>
+      </c>
+      <c r="C81" s="16">
+        <f>$B$74/B81</f>
+        <v/>
+      </c>
+      <c r="D81" s="43">
+        <f>B81</f>
+        <v/>
+      </c>
+      <c r="E81" s="69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F81" s="16">
+        <f>C81*E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="70">
+        <f>F81*G81</f>
+        <v/>
+      </c>
+      <c r="I81" s="53">
+        <f>$B$74/H81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>ГРАФИК ПЕРВЫХ 6 МЕСЯЦЕВ НА 100К ₽/мес DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Что происходит</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>CPC ₽</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>CV лендинга</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Trial → Paid</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Кликов</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Платящих</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>CAC ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>M1 Soft launch (без рекламы)</t>
+        </is>
+      </c>
+      <c r="C87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>M2 Cold start (clean targeting)</t>
+        </is>
+      </c>
+      <c r="C88" s="43" t="n">
+        <v>85</v>
+      </c>
+      <c r="D88" s="73" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E88" s="73" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F88" s="16">
+        <f>$B$74/C88</f>
+        <v/>
+      </c>
+      <c r="G88" s="16">
+        <f>F88*D88</f>
+        <v/>
+      </c>
+      <c r="H88" s="70">
+        <f>G88*E88</f>
+        <v/>
+      </c>
+      <c r="I88" s="43">
+        <f>$B$74/H88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>M3 Первая оптимизация</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="F69" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>простой сайт сделать</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D70" s="56" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E70" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F70" s="67" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>сайт за день</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D71" s="56" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E71" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F71" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>сайт быстро недорого</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D72" s="56" t="n">
-        <v>800</v>
-      </c>
-      <c r="E72" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F72" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>сайт визитка дёшево</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D73" s="56" t="n">
-        <v>800</v>
-      </c>
-      <c r="E73" s="57" t="n">
+      <c r="D89" s="73" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E89" s="73" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F89" s="16">
+        <f>$B$74/C89</f>
+        <v/>
+      </c>
+      <c r="G89" s="16">
+        <f>F89*D89</f>
+        <v/>
+      </c>
+      <c r="H89" s="70">
+        <f>G89*E89</f>
+        <v/>
+      </c>
+      <c r="I89" s="43">
+        <f>$B$74/H89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>M4 Vertical landing pages</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="D90" s="73" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E90" s="73" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F90" s="16">
+        <f>$B$74/C90</f>
+        <v/>
+      </c>
+      <c r="G90" s="16">
+        <f>F90*D90</f>
+        <v/>
+      </c>
+      <c r="H90" s="70">
+        <f>G90*E90</f>
+        <v/>
+      </c>
+      <c r="I90" s="43">
+        <f>$B$74/H90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="33" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>M5 Retargeting + узнаваемость</t>
+        </is>
+      </c>
+      <c r="C91" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="D91" s="73" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E91" s="73" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F91" s="16">
+        <f>$B$74/C91</f>
+        <v/>
+      </c>
+      <c r="G91" s="16">
+        <f>F91*D91</f>
+        <v/>
+      </c>
+      <c r="H91" s="70">
+        <f>G91*E91</f>
+        <v/>
+      </c>
+      <c r="I91" s="43">
+        <f>$B$74/H91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>M6 Зрелая воронка</t>
+        </is>
+      </c>
+      <c r="C92" s="43" t="n">
         <v>55</v>
       </c>
-      <c r="F73" s="67" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>сайт без знаний программирования</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D74" s="56" t="n">
-        <v>600</v>
-      </c>
-      <c r="E74" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F74" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>сделать сайт самому без программиста</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D75" s="56" t="n">
-        <v>400</v>
-      </c>
-      <c r="E75" s="57" t="n">
-        <v>60</v>
-      </c>
-      <c r="F75" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО · 71 ключей</t>
-        </is>
-      </c>
-      <c r="D77" s="68">
-        <f>SUM(D5:D76)</f>
-        <v/>
-      </c>
-      <c r="E77" s="69">
-        <f>AVERAGE(E5:E76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>ВОРОНКА 100К ₽ → ПЛАТЯЩИЕ КЛИЕНТЫ · 4 СЦЕНАРИЯ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Бюджет ₽/мес</t>
-        </is>
-      </c>
-      <c r="B82" s="40" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>← поменяй число — пересчитается всё ниже</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>Сценарий</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>CPC ₽</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>Кликов = визитов</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>Цена визита ₽</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>Конверсия лендинга</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Trial регистраций</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>Trial → Paid</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Платящих/мес</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>CAC ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>А. Песимистичный (M2 cold start)</t>
-        </is>
-      </c>
-      <c r="B85" s="40" t="n">
-        <v>95</v>
-      </c>
-      <c r="C85" s="16">
-        <f>$B$82/B85</f>
-        <v/>
-      </c>
-      <c r="D85" s="43">
-        <f>B85</f>
-        <v/>
-      </c>
-      <c r="E85" s="70" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F85" s="16">
-        <f>C85*E85</f>
-        <v/>
-      </c>
-      <c r="G85" s="70" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H85" s="71">
-        <f>F85*G85</f>
-        <v/>
-      </c>
-      <c r="I85" s="60">
-        <f>$B$82/H85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Б. Реалистичный (M3, базовая оптимизация)</t>
-        </is>
-      </c>
-      <c r="B86" s="40" t="n">
-        <v>75</v>
-      </c>
-      <c r="C86" s="16">
-        <f>$B$82/B86</f>
-        <v/>
-      </c>
-      <c r="D86" s="43">
-        <f>B86</f>
-        <v/>
-      </c>
-      <c r="E86" s="70" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F86" s="16">
-        <f>C86*E86</f>
-        <v/>
-      </c>
-      <c r="G86" s="70" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H86" s="71">
-        <f>F86*G86</f>
-        <v/>
-      </c>
-      <c r="I86" s="60">
-        <f>$B$82/H86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>В. Оптимистичный (M5, отшлифованный)</t>
-        </is>
-      </c>
-      <c r="B87" s="40" t="n">
-        <v>55</v>
-      </c>
-      <c r="C87" s="16">
-        <f>$B$82/B87</f>
-        <v/>
-      </c>
-      <c r="D87" s="43">
-        <f>B87</f>
-        <v/>
-      </c>
-      <c r="E87" s="70" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F87" s="16">
-        <f>C87*E87</f>
-        <v/>
-      </c>
-      <c r="G87" s="70" t="n">
+      <c r="D92" s="73" t="n">
         <v>0.08</v>
       </c>
-      <c r="H87" s="71">
-        <f>F87*G87</f>
-        <v/>
-      </c>
-      <c r="I87" s="53">
-        <f>$B$82/H87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Г. Идеал (M6+ vertical+long-tail)</t>
-        </is>
-      </c>
-      <c r="B88" s="40" t="n">
-        <v>45</v>
-      </c>
-      <c r="C88" s="16">
-        <f>$B$82/B88</f>
-        <v/>
-      </c>
-      <c r="D88" s="43">
-        <f>B88</f>
-        <v/>
-      </c>
-      <c r="E88" s="70" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F88" s="16">
-        <f>C88*E88</f>
-        <v/>
-      </c>
-      <c r="G88" s="70" t="n">
+      <c r="E92" s="73" t="n">
         <v>0.1</v>
       </c>
-      <c r="H88" s="71">
-        <f>F88*G88</f>
-        <v/>
-      </c>
-      <c r="I88" s="53">
-        <f>$B$82/H88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>ГРАФИК ПЕРВЫХ 6 МЕСЯЦЕВ НА 100К ₽/мес DIRECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="F92" s="16">
+        <f>$B$74/C92</f>
+        <v/>
+      </c>
+      <c r="G92" s="16">
+        <f>F92*D92</f>
+        <v/>
+      </c>
+      <c r="H92" s="70">
+        <f>G92*E92</f>
+        <v/>
+      </c>
+      <c r="I92" s="43">
+        <f>$B$74/H92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО за 6 мес (новых платящих)</t>
+        </is>
+      </c>
+      <c r="H93" s="74">
+        <f>SUM(H87:H92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>РАСХОЖДЕНИЕ С ФИНПЛАНОМ (лист 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Что происходит</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>CPC ₽</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>CV лендинга</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>Trial → Paid</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>Кликов</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>Trials</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Платящих</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>CAC ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="33" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>M1 Soft launch (без рекламы)</t>
-        </is>
-      </c>
-      <c r="C94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="33" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>M2 Cold start</t>
-        </is>
-      </c>
-      <c r="C95" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="D95" s="74" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E95" s="74" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F95" s="16">
-        <f>$B$82/C95</f>
-        <v/>
-      </c>
-      <c r="G95" s="16">
-        <f>F95*D95</f>
-        <v/>
-      </c>
-      <c r="H95" s="71">
-        <f>G95*E95</f>
-        <v/>
-      </c>
-      <c r="I95" s="43">
-        <f>$B$82/H95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="33" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>M3 Первая оптимизация</t>
-        </is>
-      </c>
-      <c r="C96" s="43" t="n">
-        <v>80</v>
-      </c>
-      <c r="D96" s="74" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E96" s="74" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F96" s="16">
-        <f>$B$82/C96</f>
-        <v/>
-      </c>
-      <c r="G96" s="16">
-        <f>F96*D96</f>
-        <v/>
-      </c>
-      <c r="H96" s="71">
-        <f>G96*E96</f>
-        <v/>
-      </c>
-      <c r="I96" s="43">
-        <f>$B$82/H96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="33" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>M4 Vertical landing pages</t>
-        </is>
-      </c>
-      <c r="C97" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="D97" s="74" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E97" s="74" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F97" s="16">
-        <f>$B$82/C97</f>
-        <v/>
-      </c>
-      <c r="G97" s="16">
-        <f>F97*D97</f>
-        <v/>
-      </c>
-      <c r="H97" s="71">
-        <f>G97*E97</f>
-        <v/>
-      </c>
-      <c r="I97" s="43">
-        <f>$B$82/H97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="33" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>M5 Retargeting + бренд</t>
-        </is>
-      </c>
-      <c r="C98" s="43" t="n">
-        <v>55</v>
-      </c>
-      <c r="D98" s="74" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E98" s="74" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F98" s="16">
-        <f>$B$82/C98</f>
-        <v/>
-      </c>
-      <c r="G98" s="16">
-        <f>F98*D98</f>
-        <v/>
-      </c>
-      <c r="H98" s="71">
-        <f>G98*E98</f>
-        <v/>
-      </c>
-      <c r="I98" s="43">
-        <f>$B$82/H98</f>
-        <v/>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>По финплану</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>По воронке Direct 100К</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Дельта</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Что компенсирует</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="33" t="inlineStr">
         <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C100" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="72" t="inlineStr">
+        <is>
+          <t>−27</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Multi-channel + soft-launch buzz → 8-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="C101" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" s="72" t="inlineStr">
+        <is>
+          <t>−75</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>VC.ru/Habr статья + первые кейсы → 25-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C102" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D102" s="72" t="inlineStr">
+        <is>
+          <t>−143</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Vertical lendings + B2B sales → 65-85</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="C103" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" s="72" t="inlineStr">
+        <is>
+          <t>−240</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Retargeting + узнаваемость → 150-180</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>M6 Зрелая воронка</t>
-        </is>
-      </c>
-      <c r="C99" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="D99" s="74" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E99" s="74" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F99" s="16">
-        <f>$B$82/C99</f>
-        <v/>
-      </c>
-      <c r="G99" s="16">
-        <f>F99*D99</f>
-        <v/>
-      </c>
-      <c r="H99" s="71">
-        <f>G99*E99</f>
-        <v/>
-      </c>
-      <c r="I99" s="43">
-        <f>$B$82/H99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО за 6 мес (новых платящих)</t>
-        </is>
-      </c>
-      <c r="H100" s="75">
-        <f>SUM(H94:H99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ С ФИНПЛАНОМ (лист 15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="36" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>По финплану</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>По воронке Direct 100К</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>Дельта</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>Что компенсирует</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="33" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="33" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="C107" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="73" t="inlineStr">
-        <is>
-          <t>−29</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Soft-launch buzz + Telegram founders</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="33" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="C108" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D108" s="73" t="inlineStr">
-        <is>
-          <t>−78</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>VC.ru/Habr статья + первые кейсы</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="33" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="C109" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D109" s="73" t="inlineStr">
-        <is>
-          <t>−146</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Multi-channel (VK + Telegram + контент)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="33" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="C110" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D110" s="73" t="inlineStr">
-        <is>
-          <t>−243</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Retargeting + первая узнаваемость</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="33" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B111" s="16" t="n">
+      <c r="B104" s="16" t="n">
         <v>380</v>
       </c>
-      <c r="C111" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="D111" s="73" t="inlineStr">
-        <is>
-          <t>−371</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Зрелая воронка + B2B продажи</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="33" t="inlineStr">
+      <c r="C104" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D104" s="72" t="inlineStr">
+        <is>
+          <t>−365</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Зрелая воронка → 280-320</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="33" t="inlineStr">
         <is>
           <t>M7+</t>
         </is>
       </c>
-      <c r="B112" s="72" t="inlineStr">
+      <c r="B105" s="71" t="inlineStr">
         <is>
           <t>540+</t>
         </is>
       </c>
-      <c r="C112" s="72" t="inlineStr">
-        <is>
-          <t>15-25</t>
-        </is>
-      </c>
-      <c r="D112" s="63" t="inlineStr">
+      <c r="C105" s="71" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="D105" s="63" t="inlineStr">
         <is>
           <t>догоняет</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Бренд + кейсы + органика</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="76" t="inlineStr">
-        <is>
-          <t>ВЫВОД: 100К ₽ только в Direct в первый месяц = 1-2 платящих. Финплан с М2=30 платящих требует мульти-канал (Direct 60К + VK 25К + Telegram 15К) ИЛИ soft-launch buzz (VC.ru/Habr) + B2B sales. Реалистичный график: М2=5-10, М3=18-25, М6=250-300, М7+ догоняет план.</t>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="75" t="inlineStr">
+        <is>
+          <t>ВЫВОД: 100К ₽ ТОЛЬКО на ЧИСТЫХ запросах в Direct в первый месяц = 3 платящих (vs 1 на грязном ядре). Грязные запросы (тильда / создать сайт / сайт бесплатно) — это freebie hunters и loyalty конкурентов, downstream conversion 0.5-1%. На чистых vertical / AI / pain ключах CV лендинга +60% и Trial→Paid +20%. Финплан М2=30 требует мульти-канал (Direct 60К + VK 25К + Telegram 15К → 8-12) + buzz (VC.ru → +14).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="A108:I108"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -21,7 +21,7 @@
     <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15. Lean финмодель 24м" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15. Финмодель 24 мес" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="16. Маркетинг 2026 (clean)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,7 +210,6 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3049,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3076,14 +3075,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финмодель 24 месяца · founders-only без зарплат + инфраструктура для роста</t>
+          <t>Финмодель 24 месяца · структура расходов как доля выручки</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Юрист 30к/мес · маркетинг 100→300к · инфра наша (DB+API+backups+мониторинг) растёт с базой клиентов 8к→380к/мес. Серверум за клиентский сайт уже в variable COGS.</t>
+          <t>Зарплаты = 30% выручки (с минимумом 30к в M1-M4) · Токены+инфра = 30% · Бэкофис (VPS клиенту + домены + операционка) = 10% · Маркетинг = отдельно фиксированно. Платящие пересчитаны под маркетинговую реальность 2026.</t>
         </is>
       </c>
     </row>
@@ -3224,34 +3223,34 @@
         <v>0</v>
       </c>
       <c r="C5" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="56" t="n">
-        <v>80</v>
-      </c>
       <c r="E5" s="56" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="F5" s="56" t="n">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="G5" s="56" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="H5" s="56" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="I5" s="56" t="n">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="J5" s="56" t="n">
-        <v>920</v>
+        <v>870</v>
       </c>
       <c r="K5" s="56" t="n">
-        <v>1140</v>
+        <v>1100</v>
       </c>
       <c r="L5" s="56" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="M5" s="56" t="n">
         <v>1670</v>
@@ -3375,7 +3374,7 @@
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>Выручка, ₽/мес</t>
+          <t>ВЫРУЧКА, ₽/мес</t>
         </is>
       </c>
       <c r="B7" s="49">
@@ -3475,638 +3474,607 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Маржа %</t>
-        </is>
-      </c>
-      <c r="B8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="58" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D8" s="58" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E8" s="58" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F8" s="58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="58" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H8" s="58" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I8" s="58" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J8" s="58" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K8" s="58" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L8" s="58" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M8" s="58" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N8" s="58" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O8" s="58" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Q8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="R8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="S8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="T8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="U8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="W8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="X8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Y8" s="58" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>ГРОСС-ПРИБЫЛЬ, ₽</t>
-        </is>
-      </c>
-      <c r="B9" s="53">
-        <f>B7*B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="53">
-        <f>C7*C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="53">
-        <f>D7*D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="53">
-        <f>E7*E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="53">
-        <f>F7*F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="53">
-        <f>G7*G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="53">
-        <f>H7*H8</f>
-        <v/>
-      </c>
-      <c r="I9" s="53">
-        <f>I7*I8</f>
-        <v/>
-      </c>
-      <c r="J9" s="53">
-        <f>J7*J8</f>
-        <v/>
-      </c>
-      <c r="K9" s="53">
-        <f>K7*K8</f>
-        <v/>
-      </c>
-      <c r="L9" s="53">
-        <f>L7*L8</f>
-        <v/>
-      </c>
-      <c r="M9" s="53">
-        <f>M7*M8</f>
-        <v/>
-      </c>
-      <c r="N9" s="53">
-        <f>N7*N8</f>
-        <v/>
-      </c>
-      <c r="O9" s="53">
-        <f>O7*O8</f>
-        <v/>
-      </c>
-      <c r="P9" s="53">
-        <f>P7*P8</f>
-        <v/>
-      </c>
-      <c r="Q9" s="53">
-        <f>Q7*Q8</f>
-        <v/>
-      </c>
-      <c r="R9" s="53">
-        <f>R7*R8</f>
-        <v/>
-      </c>
-      <c r="S9" s="53">
-        <f>S7*S8</f>
-        <v/>
-      </c>
-      <c r="T9" s="53">
-        <f>T7*T8</f>
-        <v/>
-      </c>
-      <c r="U9" s="53">
-        <f>U7*U8</f>
-        <v/>
-      </c>
-      <c r="V9" s="53">
-        <f>V7*V8</f>
-        <v/>
-      </c>
-      <c r="W9" s="53">
-        <f>W7*W8</f>
-        <v/>
-      </c>
-      <c r="X9" s="53">
-        <f>X7*X8</f>
-        <v/>
-      </c>
-      <c r="Y9" s="53">
-        <f>Y7*Y8</f>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Зарплаты (30% выручки или 30к, что больше), ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>MAX(30000,B7*0.3)</f>
+        <v/>
+      </c>
+      <c r="C9" s="43">
+        <f>MAX(30000,C7*0.3)</f>
+        <v/>
+      </c>
+      <c r="D9" s="43">
+        <f>MAX(30000,D7*0.3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="43">
+        <f>MAX(30000,E7*0.3)</f>
+        <v/>
+      </c>
+      <c r="F9" s="43">
+        <f>MAX(30000,F7*0.3)</f>
+        <v/>
+      </c>
+      <c r="G9" s="43">
+        <f>MAX(30000,G7*0.3)</f>
+        <v/>
+      </c>
+      <c r="H9" s="43">
+        <f>MAX(30000,H7*0.3)</f>
+        <v/>
+      </c>
+      <c r="I9" s="43">
+        <f>MAX(30000,I7*0.3)</f>
+        <v/>
+      </c>
+      <c r="J9" s="43">
+        <f>MAX(30000,J7*0.3)</f>
+        <v/>
+      </c>
+      <c r="K9" s="43">
+        <f>MAX(30000,K7*0.3)</f>
+        <v/>
+      </c>
+      <c r="L9" s="43">
+        <f>MAX(30000,L7*0.3)</f>
+        <v/>
+      </c>
+      <c r="M9" s="43">
+        <f>MAX(30000,M7*0.3)</f>
+        <v/>
+      </c>
+      <c r="N9" s="43">
+        <f>MAX(30000,N7*0.3)</f>
+        <v/>
+      </c>
+      <c r="O9" s="43">
+        <f>MAX(30000,O7*0.3)</f>
+        <v/>
+      </c>
+      <c r="P9" s="43">
+        <f>MAX(30000,P7*0.3)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="43">
+        <f>MAX(30000,Q7*0.3)</f>
+        <v/>
+      </c>
+      <c r="R9" s="43">
+        <f>MAX(30000,R7*0.3)</f>
+        <v/>
+      </c>
+      <c r="S9" s="43">
+        <f>MAX(30000,S7*0.3)</f>
+        <v/>
+      </c>
+      <c r="T9" s="43">
+        <f>MAX(30000,T7*0.3)</f>
+        <v/>
+      </c>
+      <c r="U9" s="43">
+        <f>MAX(30000,U7*0.3)</f>
+        <v/>
+      </c>
+      <c r="V9" s="43">
+        <f>MAX(30000,V7*0.3)</f>
+        <v/>
+      </c>
+      <c r="W9" s="43">
+        <f>MAX(30000,W7*0.3)</f>
+        <v/>
+      </c>
+      <c r="X9" s="43">
+        <f>MAX(30000,X7*0.3)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="43">
+        <f>MAX(30000,Y7*0.3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Токены + наша инфра (30% выручки), ₽</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>B7*0.3</f>
+        <v/>
+      </c>
+      <c r="C10" s="43">
+        <f>C7*0.3</f>
+        <v/>
+      </c>
+      <c r="D10" s="43">
+        <f>D7*0.3</f>
+        <v/>
+      </c>
+      <c r="E10" s="43">
+        <f>E7*0.3</f>
+        <v/>
+      </c>
+      <c r="F10" s="43">
+        <f>F7*0.3</f>
+        <v/>
+      </c>
+      <c r="G10" s="43">
+        <f>G7*0.3</f>
+        <v/>
+      </c>
+      <c r="H10" s="43">
+        <f>H7*0.3</f>
+        <v/>
+      </c>
+      <c r="I10" s="43">
+        <f>I7*0.3</f>
+        <v/>
+      </c>
+      <c r="J10" s="43">
+        <f>J7*0.3</f>
+        <v/>
+      </c>
+      <c r="K10" s="43">
+        <f>K7*0.3</f>
+        <v/>
+      </c>
+      <c r="L10" s="43">
+        <f>L7*0.3</f>
+        <v/>
+      </c>
+      <c r="M10" s="43">
+        <f>M7*0.3</f>
+        <v/>
+      </c>
+      <c r="N10" s="43">
+        <f>N7*0.3</f>
+        <v/>
+      </c>
+      <c r="O10" s="43">
+        <f>O7*0.3</f>
+        <v/>
+      </c>
+      <c r="P10" s="43">
+        <f>P7*0.3</f>
+        <v/>
+      </c>
+      <c r="Q10" s="43">
+        <f>Q7*0.3</f>
+        <v/>
+      </c>
+      <c r="R10" s="43">
+        <f>R7*0.3</f>
+        <v/>
+      </c>
+      <c r="S10" s="43">
+        <f>S7*0.3</f>
+        <v/>
+      </c>
+      <c r="T10" s="43">
+        <f>T7*0.3</f>
+        <v/>
+      </c>
+      <c r="U10" s="43">
+        <f>U7*0.3</f>
+        <v/>
+      </c>
+      <c r="V10" s="43">
+        <f>V7*0.3</f>
+        <v/>
+      </c>
+      <c r="W10" s="43">
+        <f>W7*0.3</f>
+        <v/>
+      </c>
+      <c r="X10" s="43">
+        <f>X7*0.3</f>
+        <v/>
+      </c>
+      <c r="Y10" s="43">
+        <f>Y7*0.3</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>OPEX: Юрист, ₽</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="M11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="O11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="P11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="Q11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="R11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="S11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="T11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="U11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="V11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="W11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="X11" s="43" t="n">
-        <v>30000</v>
-      </c>
-      <c r="Y11" s="43" t="n">
-        <v>30000</v>
+          <t>Бэкофис: VPS клиентов + домены + опер (10%), ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="43">
+        <f>B7*0.1</f>
+        <v/>
+      </c>
+      <c r="C11" s="43">
+        <f>C7*0.1</f>
+        <v/>
+      </c>
+      <c r="D11" s="43">
+        <f>D7*0.1</f>
+        <v/>
+      </c>
+      <c r="E11" s="43">
+        <f>E7*0.1</f>
+        <v/>
+      </c>
+      <c r="F11" s="43">
+        <f>F7*0.1</f>
+        <v/>
+      </c>
+      <c r="G11" s="43">
+        <f>G7*0.1</f>
+        <v/>
+      </c>
+      <c r="H11" s="43">
+        <f>H7*0.1</f>
+        <v/>
+      </c>
+      <c r="I11" s="43">
+        <f>I7*0.1</f>
+        <v/>
+      </c>
+      <c r="J11" s="43">
+        <f>J7*0.1</f>
+        <v/>
+      </c>
+      <c r="K11" s="43">
+        <f>K7*0.1</f>
+        <v/>
+      </c>
+      <c r="L11" s="43">
+        <f>L7*0.1</f>
+        <v/>
+      </c>
+      <c r="M11" s="43">
+        <f>M7*0.1</f>
+        <v/>
+      </c>
+      <c r="N11" s="43">
+        <f>N7*0.1</f>
+        <v/>
+      </c>
+      <c r="O11" s="43">
+        <f>O7*0.1</f>
+        <v/>
+      </c>
+      <c r="P11" s="43">
+        <f>P7*0.1</f>
+        <v/>
+      </c>
+      <c r="Q11" s="43">
+        <f>Q7*0.1</f>
+        <v/>
+      </c>
+      <c r="R11" s="43">
+        <f>R7*0.1</f>
+        <v/>
+      </c>
+      <c r="S11" s="43">
+        <f>S7*0.1</f>
+        <v/>
+      </c>
+      <c r="T11" s="43">
+        <f>T7*0.1</f>
+        <v/>
+      </c>
+      <c r="U11" s="43">
+        <f>U7*0.1</f>
+        <v/>
+      </c>
+      <c r="V11" s="43">
+        <f>V7*0.1</f>
+        <v/>
+      </c>
+      <c r="W11" s="43">
+        <f>W7*0.1</f>
+        <v/>
+      </c>
+      <c r="X11" s="43">
+        <f>X7*0.1</f>
+        <v/>
+      </c>
+      <c r="Y11" s="43">
+        <f>Y7*0.1</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>OPEX: Маркетинг и реклама, ₽</t>
+          <t>Маркетинг и реклама (фиксированный бюджет), ₽</t>
         </is>
       </c>
       <c r="B12" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="59" t="n">
+      <c r="C12" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="D12" s="59" t="n">
+      <c r="D12" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="E12" s="59" t="n">
+      <c r="E12" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="F12" s="59" t="n">
+      <c r="F12" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="G12" s="59" t="n">
+      <c r="G12" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="H12" s="59" t="n">
+      <c r="H12" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="I12" s="59" t="n">
+      <c r="I12" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="J12" s="59" t="n">
+      <c r="J12" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="K12" s="59" t="n">
+      <c r="K12" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="L12" s="59" t="n">
+      <c r="L12" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="M12" s="59" t="n">
+      <c r="M12" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="N12" s="59" t="n">
+      <c r="N12" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="O12" s="59" t="n">
+      <c r="O12" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="P12" s="59" t="n">
+      <c r="P12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="Q12" s="59" t="n">
+      <c r="Q12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="R12" s="59" t="n">
+      <c r="R12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="S12" s="59" t="n">
+      <c r="S12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="T12" s="59" t="n">
+      <c r="T12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="U12" s="59" t="n">
+      <c r="U12" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="V12" s="59" t="n">
+      <c r="V12" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="W12" s="59" t="n">
+      <c r="W12" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="X12" s="59" t="n">
+      <c r="X12" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="Y12" s="59" t="n">
+      <c r="Y12" s="58" t="n">
         <v>300000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>OPEX: Инфра (наши сервера/БД/бэкапы), ₽</t>
-        </is>
-      </c>
-      <c r="B13" s="59" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D13" s="59" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E13" s="59" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F13" s="59" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G13" s="59" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H13" s="59" t="n">
-        <v>45000</v>
-      </c>
-      <c r="I13" s="59" t="n">
-        <v>55000</v>
-      </c>
-      <c r="J13" s="59" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K13" s="59" t="n">
-        <v>80000</v>
-      </c>
-      <c r="L13" s="59" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M13" s="59" t="n">
-        <v>120000</v>
-      </c>
-      <c r="N13" s="59" t="n">
-        <v>140000</v>
-      </c>
-      <c r="O13" s="59" t="n">
-        <v>160000</v>
-      </c>
-      <c r="P13" s="59" t="n">
-        <v>180000</v>
-      </c>
-      <c r="Q13" s="59" t="n">
-        <v>200000</v>
-      </c>
-      <c r="R13" s="59" t="n">
-        <v>230000</v>
-      </c>
-      <c r="S13" s="59" t="n">
-        <v>260000</v>
-      </c>
-      <c r="T13" s="59" t="n">
-        <v>280000</v>
-      </c>
-      <c r="U13" s="59" t="n">
-        <v>300000</v>
-      </c>
-      <c r="V13" s="59" t="n">
-        <v>320000</v>
-      </c>
-      <c r="W13" s="59" t="n">
-        <v>340000</v>
-      </c>
-      <c r="X13" s="59" t="n">
-        <v>360000</v>
-      </c>
-      <c r="Y13" s="59" t="n">
-        <v>380000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>ИТОГО OPEX, ₽</t>
-        </is>
-      </c>
-      <c r="B14" s="60">
-        <f>SUM(B11:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="60">
-        <f>SUM(C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="60">
-        <f>SUM(D11:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="60">
-        <f>SUM(E11:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="60">
-        <f>SUM(F11:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="60">
-        <f>SUM(G11:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="60">
-        <f>SUM(H11:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="60">
-        <f>SUM(I11:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="60">
-        <f>SUM(J11:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="60">
-        <f>SUM(K11:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="60">
-        <f>SUM(L11:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="60">
-        <f>SUM(M11:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="60">
-        <f>SUM(N11:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="60">
-        <f>SUM(O11:O13)</f>
-        <v/>
-      </c>
-      <c r="P14" s="60">
-        <f>SUM(P11:P13)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="60">
-        <f>SUM(Q11:Q13)</f>
-        <v/>
-      </c>
-      <c r="R14" s="60">
-        <f>SUM(R11:R13)</f>
-        <v/>
-      </c>
-      <c r="S14" s="60">
-        <f>SUM(S11:S13)</f>
-        <v/>
-      </c>
-      <c r="T14" s="60">
-        <f>SUM(T11:T13)</f>
-        <v/>
-      </c>
-      <c r="U14" s="60">
-        <f>SUM(U11:U13)</f>
-        <v/>
-      </c>
-      <c r="V14" s="60">
-        <f>SUM(V11:V13)</f>
-        <v/>
-      </c>
-      <c r="W14" s="60">
-        <f>SUM(W11:W13)</f>
-        <v/>
-      </c>
-      <c r="X14" s="60">
-        <f>SUM(X11:X13)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="60">
-        <f>SUM(Y11:Y13)</f>
+          <t>ИТОГО ОПЕРАЦИОННЫХ РАСХОДОВ, ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="59">
+        <f>SUM(B9:B12)</f>
+        <v/>
+      </c>
+      <c r="C14" s="59">
+        <f>SUM(C9:C12)</f>
+        <v/>
+      </c>
+      <c r="D14" s="59">
+        <f>SUM(D9:D12)</f>
+        <v/>
+      </c>
+      <c r="E14" s="59">
+        <f>SUM(E9:E12)</f>
+        <v/>
+      </c>
+      <c r="F14" s="59">
+        <f>SUM(F9:F12)</f>
+        <v/>
+      </c>
+      <c r="G14" s="59">
+        <f>SUM(G9:G12)</f>
+        <v/>
+      </c>
+      <c r="H14" s="59">
+        <f>SUM(H9:H12)</f>
+        <v/>
+      </c>
+      <c r="I14" s="59">
+        <f>SUM(I9:I12)</f>
+        <v/>
+      </c>
+      <c r="J14" s="59">
+        <f>SUM(J9:J12)</f>
+        <v/>
+      </c>
+      <c r="K14" s="59">
+        <f>SUM(K9:K12)</f>
+        <v/>
+      </c>
+      <c r="L14" s="59">
+        <f>SUM(L9:L12)</f>
+        <v/>
+      </c>
+      <c r="M14" s="59">
+        <f>SUM(M9:M12)</f>
+        <v/>
+      </c>
+      <c r="N14" s="59">
+        <f>SUM(N9:N12)</f>
+        <v/>
+      </c>
+      <c r="O14" s="59">
+        <f>SUM(O9:O12)</f>
+        <v/>
+      </c>
+      <c r="P14" s="59">
+        <f>SUM(P9:P12)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="59">
+        <f>SUM(Q9:Q12)</f>
+        <v/>
+      </c>
+      <c r="R14" s="59">
+        <f>SUM(R9:R12)</f>
+        <v/>
+      </c>
+      <c r="S14" s="59">
+        <f>SUM(S9:S12)</f>
+        <v/>
+      </c>
+      <c r="T14" s="59">
+        <f>SUM(T9:T12)</f>
+        <v/>
+      </c>
+      <c r="U14" s="59">
+        <f>SUM(U9:U12)</f>
+        <v/>
+      </c>
+      <c r="V14" s="59">
+        <f>SUM(V9:V12)</f>
+        <v/>
+      </c>
+      <c r="W14" s="59">
+        <f>SUM(W9:W12)</f>
+        <v/>
+      </c>
+      <c r="X14" s="59">
+        <f>SUM(X9:X12)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="59">
+        <f>SUM(Y9:Y12)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>Прибыль/убыток, ₽</t>
-        </is>
-      </c>
-      <c r="B16" s="61">
-        <f>B9-B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="61">
-        <f>C9-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="61">
-        <f>D9-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="61">
-        <f>E9-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="61">
-        <f>F9-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="61">
-        <f>G9-G14</f>
-        <v/>
-      </c>
-      <c r="H16" s="61">
-        <f>H9-H14</f>
-        <v/>
-      </c>
-      <c r="I16" s="61">
-        <f>I9-I14</f>
-        <v/>
-      </c>
-      <c r="J16" s="61">
-        <f>J9-J14</f>
-        <v/>
-      </c>
-      <c r="K16" s="61">
-        <f>K9-K14</f>
-        <v/>
-      </c>
-      <c r="L16" s="61">
-        <f>L9-L14</f>
-        <v/>
-      </c>
-      <c r="M16" s="61">
-        <f>M9-M14</f>
-        <v/>
-      </c>
-      <c r="N16" s="61">
-        <f>N9-N14</f>
-        <v/>
-      </c>
-      <c r="O16" s="61">
-        <f>O9-O14</f>
-        <v/>
-      </c>
-      <c r="P16" s="61">
-        <f>P9-P14</f>
-        <v/>
-      </c>
-      <c r="Q16" s="61">
-        <f>Q9-Q14</f>
-        <v/>
-      </c>
-      <c r="R16" s="61">
-        <f>R9-R14</f>
-        <v/>
-      </c>
-      <c r="S16" s="61">
-        <f>S9-S14</f>
-        <v/>
-      </c>
-      <c r="T16" s="61">
-        <f>T9-T14</f>
-        <v/>
-      </c>
-      <c r="U16" s="61">
-        <f>U9-U14</f>
-        <v/>
-      </c>
-      <c r="V16" s="61">
-        <f>V9-V14</f>
-        <v/>
-      </c>
-      <c r="W16" s="61">
-        <f>W9-W14</f>
-        <v/>
-      </c>
-      <c r="X16" s="61">
-        <f>X9-X14</f>
-        <v/>
-      </c>
-      <c r="Y16" s="61">
-        <f>Y9-Y14</f>
+          <t>ОПЕРАЦИОННАЯ ПРИБЫЛЬ/УБЫТОК, ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="60">
+        <f>B7-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="60">
+        <f>C7-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="60">
+        <f>D7-D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="60">
+        <f>E7-E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="60">
+        <f>F7-F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="60">
+        <f>G7-G14</f>
+        <v/>
+      </c>
+      <c r="H16" s="60">
+        <f>H7-H14</f>
+        <v/>
+      </c>
+      <c r="I16" s="60">
+        <f>I7-I14</f>
+        <v/>
+      </c>
+      <c r="J16" s="60">
+        <f>J7-J14</f>
+        <v/>
+      </c>
+      <c r="K16" s="60">
+        <f>K7-K14</f>
+        <v/>
+      </c>
+      <c r="L16" s="60">
+        <f>L7-L14</f>
+        <v/>
+      </c>
+      <c r="M16" s="60">
+        <f>M7-M14</f>
+        <v/>
+      </c>
+      <c r="N16" s="60">
+        <f>N7-N14</f>
+        <v/>
+      </c>
+      <c r="O16" s="60">
+        <f>O7-O14</f>
+        <v/>
+      </c>
+      <c r="P16" s="60">
+        <f>P7-P14</f>
+        <v/>
+      </c>
+      <c r="Q16" s="60">
+        <f>Q7-Q14</f>
+        <v/>
+      </c>
+      <c r="R16" s="60">
+        <f>R7-R14</f>
+        <v/>
+      </c>
+      <c r="S16" s="60">
+        <f>S7-S14</f>
+        <v/>
+      </c>
+      <c r="T16" s="60">
+        <f>T7-T14</f>
+        <v/>
+      </c>
+      <c r="U16" s="60">
+        <f>U7-U14</f>
+        <v/>
+      </c>
+      <c r="V16" s="60">
+        <f>V7-V14</f>
+        <v/>
+      </c>
+      <c r="W16" s="60">
+        <f>W7-W14</f>
+        <v/>
+      </c>
+      <c r="X16" s="60">
+        <f>X7-X14</f>
+        <v/>
+      </c>
+      <c r="Y16" s="60">
+        <f>Y7-Y14</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>Накопленный кэш (старт 30к ₽), ₽</t>
-        </is>
-      </c>
-      <c r="B17" s="61">
+          <t>Накопленные деньги на счёте (старт 30к ₽), ₽</t>
+        </is>
+      </c>
+      <c r="B17" s="60">
         <f>30000+B16</f>
         <v/>
       </c>
@@ -4206,7 +4174,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>SUMMARY</t>
+          <t>ИТОГИ</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4203,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M24, ₽</t>
+          <t>Деньги на счёте на M24, ₽</t>
         </is>
       </c>
       <c r="B23" s="53">
@@ -4249,7 +4217,7 @@
           <t>Самый большой минус по деньгам, ₽</t>
         </is>
       </c>
-      <c r="B24" s="60">
+      <c r="B24" s="59">
         <f>MIN(B17:Y17)</f>
         <v/>
       </c>
@@ -4268,24 +4236,24 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Месяц первой прибыли (положительная)</t>
+          <t>Месяц первой прибыли</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>M6 (с учётом инфры)</t>
+          <t>M7 (с новой структурой 30/30/10/30)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Месяц возврата вложений (кэш &gt; 0)</t>
+          <t>Месяц возврата вложений (счёт &gt; 0)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>M8 (с учётом инфры)</t>
+          <t>M9</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4263,7 @@
           <t>Маркетинг суммарно за 24 мес, ₽</t>
         </is>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="61">
         <f>SUM(B12:Y12)</f>
         <v/>
       </c>
@@ -4303,150 +4271,194 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Инфра суммарно за 24 мес, ₽</t>
-        </is>
-      </c>
-      <c r="B29" s="62">
-        <f>SUM(B13:Y13)</f>
+          <t>Зарплаты суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B29" s="61">
+        <f>SUM(B9:Y9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Токены+инфра суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B30" s="61">
+        <f>SUM(B10:Y10)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>vs модель с зарплатой разработчикам 300к/мес (с учётом инфры):</t>
-        </is>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Бэкофис суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B31" s="61">
+        <f>SUM(B11:Y11)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Месяц первой прибыли</t>
-        </is>
-      </c>
-      <c r="B33" s="63" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="C33" s="64" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>+3 мес раньше</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Месяц возврата вложений</t>
-        </is>
-      </c>
-      <c r="B34" s="63" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="C34" s="64" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>+4 мес раньше</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Структура: 30% зарплаты / 30% токены+инфра / 10% бэкофис / 30% операц.доход (до маркетинга)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Самый большой минус</t>
-        </is>
-      </c>
-      <c r="B35" s="63" t="inlineStr">
-        <is>
-          <t>~−305 К ₽</t>
-        </is>
-      </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>~−2.5 М ₽</t>
+          <t>Платящих клиентов на M24</t>
+        </is>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>6 250</t>
+        </is>
+      </c>
+      <c r="C35" s="63" t="inlineStr">
+        <is>
+          <t>По плану</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>−88%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Накопленный кэш на M24</t>
-        </is>
-      </c>
-      <c r="B36" s="63" t="inlineStr">
-        <is>
-          <t>~+67 М ₽</t>
-        </is>
-      </c>
-      <c r="C36" s="64" t="inlineStr">
-        <is>
-          <t>~+59 М ₽</t>
+          <t>Месяц первой прибыли</t>
+        </is>
+      </c>
+      <c r="B36" s="62" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C36" s="63" t="inlineStr">
+        <is>
+          <t>M6 (старая модель)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>+8 М</t>
+          <t>+1 мес позже</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Можно ли запуститься на 30к?</t>
-        </is>
-      </c>
-      <c r="B37" s="63" t="inlineStr">
-        <is>
-          <t>ДА (хватит на M1)</t>
-        </is>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>Месяц возврата вложений</t>
+        </is>
+      </c>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="C37" s="63" t="inlineStr">
+        <is>
+          <t>M8</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1 мес позже</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Источник разработки</t>
-        </is>
-      </c>
-      <c r="B38" s="63" t="inlineStr">
-        <is>
-          <t>founders + AI</t>
-        </is>
-      </c>
-      <c r="C38" s="64" t="inlineStr">
-        <is>
-          <t>1 senior + 1 mid</t>
+          <t>Самый большой минус</t>
+        </is>
+      </c>
+      <c r="B38" s="62" t="inlineStr">
+        <is>
+          <t>~−380 К ₽</t>
+        </is>
+      </c>
+      <c r="C38" s="63" t="inlineStr">
+        <is>
+          <t>~−305 К</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
+          <t>−25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Накопленные деньги на M24</t>
+        </is>
+      </c>
+      <c r="B39" s="62" t="inlineStr">
+        <is>
+          <t>~+60 М ₽</t>
+        </is>
+      </c>
+      <c r="C39" s="63" t="inlineStr">
+        <is>
+          <t>~+67 М (старая)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>−7 М</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Почему стало хуже?</t>
+        </is>
+      </c>
+      <c r="B40" s="62" t="inlineStr">
+        <is>
+          <t>Зарплаты 30% + замедл. разгон M2-M6</t>
+        </is>
+      </c>
+      <c r="C40" s="63" t="inlineStr">
+        <is>
+          <t>В старой founders=0</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Что лучше?</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>Каждый рубль роста = +30к в команду</t>
+        </is>
+      </c>
+      <c r="C41" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Запас прочности</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4524,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>CPC ₽ 2026</t>
+          <t>Цена клика ₽ 2026</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -4541,7 +4553,7 @@
       <c r="E5" s="57" t="n">
         <v>135</v>
       </c>
-      <c r="F5" s="65" t="n">
+      <c r="F5" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4565,7 +4577,7 @@
       <c r="E6" s="57" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="65" t="n">
+      <c r="F6" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4589,7 +4601,7 @@
       <c r="E7" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F7" s="65" t="n">
+      <c r="F7" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4613,7 +4625,7 @@
       <c r="E8" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="65" t="n">
+      <c r="F8" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4637,7 +4649,7 @@
       <c r="E9" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F9" s="65" t="n">
+      <c r="F9" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4661,7 +4673,7 @@
       <c r="E10" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F10" s="65" t="n">
+      <c r="F10" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4685,7 +4697,7 @@
       <c r="E11" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F11" s="65" t="n">
+      <c r="F11" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4709,7 +4721,7 @@
       <c r="E12" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F12" s="65" t="n">
+      <c r="F12" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4733,7 +4745,7 @@
       <c r="E13" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="65" t="n">
+      <c r="F13" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4757,7 +4769,7 @@
       <c r="E14" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F14" s="65" t="n">
+      <c r="F14" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4781,7 +4793,7 @@
       <c r="E15" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F15" s="65" t="n">
+      <c r="F15" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4805,7 +4817,7 @@
       <c r="E16" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F16" s="65" t="n">
+      <c r="F16" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4829,7 +4841,7 @@
       <c r="E17" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F17" s="65" t="n">
+      <c r="F17" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4853,7 +4865,7 @@
       <c r="E18" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F18" s="65" t="n">
+      <c r="F18" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4877,7 +4889,7 @@
       <c r="E19" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F19" s="65" t="n">
+      <c r="F19" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4901,7 +4913,7 @@
       <c r="E20" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F20" s="65" t="n">
+      <c r="F20" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4925,7 +4937,7 @@
       <c r="E21" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F21" s="65" t="n">
+      <c r="F21" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4949,7 +4961,7 @@
       <c r="E22" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F22" s="65" t="n">
+      <c r="F22" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4973,7 +4985,7 @@
       <c r="E23" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F23" s="65" t="n">
+      <c r="F23" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4997,7 +5009,7 @@
       <c r="E24" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F24" s="65" t="n">
+      <c r="F24" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5021,7 +5033,7 @@
       <c r="E25" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F25" s="65" t="n">
+      <c r="F25" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5045,7 +5057,7 @@
       <c r="E26" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F26" s="65" t="n">
+      <c r="F26" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5069,7 +5081,7 @@
       <c r="E27" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F27" s="65" t="n">
+      <c r="F27" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5093,7 +5105,7 @@
       <c r="E28" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F28" s="65" t="n">
+      <c r="F28" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5117,7 +5129,7 @@
       <c r="E29" s="57" t="n">
         <v>165</v>
       </c>
-      <c r="F29" s="65" t="n">
+      <c r="F29" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5141,7 +5153,7 @@
       <c r="E30" s="57" t="n">
         <v>130</v>
       </c>
-      <c r="F30" s="65" t="n">
+      <c r="F30" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5165,7 +5177,7 @@
       <c r="E31" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F31" s="65" t="n">
+      <c r="F31" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5189,7 +5201,7 @@
       <c r="E32" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5213,7 +5225,7 @@
       <c r="E33" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="65" t="n">
+      <c r="F33" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5237,7 +5249,7 @@
       <c r="E34" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F34" s="65" t="n">
+      <c r="F34" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5261,7 +5273,7 @@
       <c r="E35" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F35" s="65" t="n">
+      <c r="F35" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5285,7 +5297,7 @@
       <c r="E36" s="57" t="n">
         <v>125</v>
       </c>
-      <c r="F36" s="65" t="n">
+      <c r="F36" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5309,7 +5321,7 @@
       <c r="E37" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F37" s="65" t="n">
+      <c r="F37" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5333,7 +5345,7 @@
       <c r="E38" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F38" s="65" t="n">
+      <c r="F38" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5357,7 +5369,7 @@
       <c r="E39" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F39" s="65" t="n">
+      <c r="F39" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5381,7 +5393,7 @@
       <c r="E40" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F40" s="65" t="n">
+      <c r="F40" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5405,7 +5417,7 @@
       <c r="E41" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F41" s="65" t="n">
+      <c r="F41" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5429,7 +5441,7 @@
       <c r="E42" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F42" s="65" t="n">
+      <c r="F42" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5453,7 +5465,7 @@
       <c r="E43" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F43" s="65" t="n">
+      <c r="F43" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5477,7 +5489,7 @@
       <c r="E44" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F44" s="65" t="n">
+      <c r="F44" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5501,7 +5513,7 @@
       <c r="E45" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F45" s="65" t="n">
+      <c r="F45" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5525,7 +5537,7 @@
       <c r="E46" s="57" t="n">
         <v>130</v>
       </c>
-      <c r="F46" s="65" t="n">
+      <c r="F46" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5549,7 +5561,7 @@
       <c r="E47" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F47" s="65" t="n">
+      <c r="F47" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5573,7 +5585,7 @@
       <c r="E48" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F48" s="65" t="n">
+      <c r="F48" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5597,7 +5609,7 @@
       <c r="E49" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F49" s="65" t="n">
+      <c r="F49" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5621,7 +5633,7 @@
       <c r="E50" s="57" t="n">
         <v>115</v>
       </c>
-      <c r="F50" s="65" t="n">
+      <c r="F50" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5645,7 +5657,7 @@
       <c r="E51" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F51" s="65" t="n">
+      <c r="F51" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5669,7 +5681,7 @@
       <c r="E52" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F52" s="65" t="n">
+      <c r="F52" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5693,7 +5705,7 @@
       <c r="E53" s="57" t="n">
         <v>125</v>
       </c>
-      <c r="F53" s="65" t="n">
+      <c r="F53" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5717,7 +5729,7 @@
       <c r="E54" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F54" s="65" t="n">
+      <c r="F54" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5741,7 +5753,7 @@
       <c r="E55" s="57" t="n">
         <v>175</v>
       </c>
-      <c r="F55" s="66" t="n">
+      <c r="F55" s="65" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5765,7 +5777,7 @@
       <c r="E56" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F56" s="65" t="n">
+      <c r="F56" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5789,7 +5801,7 @@
       <c r="E57" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F57" s="65" t="n">
+      <c r="F57" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5813,7 +5825,7 @@
       <c r="E58" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F58" s="65" t="n">
+      <c r="F58" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5837,7 +5849,7 @@
       <c r="E59" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F59" s="65" t="n">
+      <c r="F59" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5861,7 +5873,7 @@
       <c r="E60" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F60" s="65" t="n">
+      <c r="F60" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5885,7 +5897,7 @@
       <c r="E61" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F61" s="65" t="n">
+      <c r="F61" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5909,7 +5921,7 @@
       <c r="E62" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F62" s="65" t="n">
+      <c r="F62" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5933,7 +5945,7 @@
       <c r="E63" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F63" s="65" t="n">
+      <c r="F63" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5957,7 +5969,7 @@
       <c r="E64" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F64" s="65" t="n">
+      <c r="F64" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5981,7 +5993,7 @@
       <c r="E65" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="F65" s="65" t="n">
+      <c r="F65" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6005,7 +6017,7 @@
       <c r="E66" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F66" s="65" t="n">
+      <c r="F66" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6029,7 +6041,7 @@
       <c r="E67" s="57" t="n">
         <v>60</v>
       </c>
-      <c r="F67" s="65" t="n">
+      <c r="F67" s="64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6039,11 +6051,11 @@
           <t>ИТОГО · 63 ключей</t>
         </is>
       </c>
-      <c r="D69" s="67">
+      <c r="D69" s="66">
         <f>SUM(D5:D68)</f>
         <v/>
       </c>
-      <c r="E69" s="68">
+      <c r="E69" s="67">
         <f>AVERAGE(E5:E68)</f>
         <v/>
       </c>
@@ -6078,7 +6090,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>CPC ₽</t>
+          <t>Цена клика ₽</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -6093,17 +6105,17 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Конверсия лендинга</t>
+          <t>Конверсия посадочной</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Trial регистраций</t>
+          <t>Регистраций на пробник</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Trial → Paid</t>
+          <t>Пробник → платящий</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6113,7 +6125,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>CAC ₽</t>
+          <t>Стоимость привлечения ₽</t>
         </is>
       </c>
     </row>
@@ -6134,21 +6146,21 @@
         <f>B77</f>
         <v/>
       </c>
-      <c r="E77" s="69" t="n">
+      <c r="E77" s="68" t="n">
         <v>0.04</v>
       </c>
       <c r="F77" s="16">
         <f>C77*E77</f>
         <v/>
       </c>
-      <c r="G77" s="69" t="n">
+      <c r="G77" s="68" t="n">
         <v>0.06</v>
       </c>
-      <c r="H77" s="70">
+      <c r="H77" s="69">
         <f>F77*G77</f>
         <v/>
       </c>
-      <c r="I77" s="60">
+      <c r="I77" s="59">
         <f>$B$74/H77</f>
         <v/>
       </c>
@@ -6170,21 +6182,21 @@
         <f>B78</f>
         <v/>
       </c>
-      <c r="E78" s="69" t="n">
+      <c r="E78" s="68" t="n">
         <v>0.05</v>
       </c>
       <c r="F78" s="16">
         <f>C78*E78</f>
         <v/>
       </c>
-      <c r="G78" s="69" t="n">
+      <c r="G78" s="68" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H78" s="70">
+      <c r="H78" s="69">
         <f>F78*G78</f>
         <v/>
       </c>
-      <c r="I78" s="60">
+      <c r="I78" s="59">
         <f>$B$74/H78</f>
         <v/>
       </c>
@@ -6206,17 +6218,17 @@
         <f>B79</f>
         <v/>
       </c>
-      <c r="E79" s="69" t="n">
+      <c r="E79" s="68" t="n">
         <v>0.06</v>
       </c>
       <c r="F79" s="16">
         <f>C79*E79</f>
         <v/>
       </c>
-      <c r="G79" s="69" t="n">
+      <c r="G79" s="68" t="n">
         <v>0.08</v>
       </c>
-      <c r="H79" s="70">
+      <c r="H79" s="69">
         <f>F79*G79</f>
         <v/>
       </c>
@@ -6242,17 +6254,17 @@
         <f>B80</f>
         <v/>
       </c>
-      <c r="E80" s="69" t="n">
+      <c r="E80" s="68" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F80" s="16">
         <f>C80*E80</f>
         <v/>
       </c>
-      <c r="G80" s="69" t="n">
+      <c r="G80" s="68" t="n">
         <v>0.09</v>
       </c>
-      <c r="H80" s="70">
+      <c r="H80" s="69">
         <f>F80*G80</f>
         <v/>
       </c>
@@ -6278,17 +6290,17 @@
         <f>B81</f>
         <v/>
       </c>
-      <c r="E81" s="69" t="n">
+      <c r="E81" s="68" t="n">
         <v>0.08</v>
       </c>
       <c r="F81" s="16">
         <f>C81*E81</f>
         <v/>
       </c>
-      <c r="G81" s="69" t="n">
+      <c r="G81" s="68" t="n">
         <v>0.1</v>
       </c>
-      <c r="H81" s="70">
+      <c r="H81" s="69">
         <f>F81*G81</f>
         <v/>
       </c>
@@ -6317,17 +6329,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>CPC ₽</t>
+          <t>Цена клика ₽</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>CV лендинга</t>
+          <t>Конв. посадочной</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Trial → Paid</t>
+          <t>Прб → Плт</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Trials</t>
+          <t>Пробников</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -6347,7 +6359,7 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>CAC ₽</t>
+          <t>Стоимость привлечения ₽</t>
         </is>
       </c>
     </row>
@@ -6362,35 +6374,35 @@
           <t>M1 Soft launch (без рекламы)</t>
         </is>
       </c>
-      <c r="C87" s="71" t="inlineStr">
+      <c r="C87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D87" s="71" t="inlineStr">
+      <c r="D87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="71" t="inlineStr">
+      <c r="E87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F87" s="71" t="inlineStr">
+      <c r="F87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G87" s="71" t="inlineStr">
+      <c r="G87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H87" s="72" t="n">
+      <c r="H87" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="71" t="inlineStr">
+      <c r="I87" s="70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6410,10 +6422,10 @@
       <c r="C88" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="D88" s="73" t="n">
+      <c r="D88" s="72" t="n">
         <v>0.04</v>
       </c>
-      <c r="E88" s="73" t="n">
+      <c r="E88" s="72" t="n">
         <v>0.06</v>
       </c>
       <c r="F88" s="16">
@@ -6424,7 +6436,7 @@
         <f>F88*D88</f>
         <v/>
       </c>
-      <c r="H88" s="70">
+      <c r="H88" s="69">
         <f>G88*E88</f>
         <v/>
       </c>
@@ -6447,10 +6459,10 @@
       <c r="C89" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="D89" s="73" t="n">
+      <c r="D89" s="72" t="n">
         <v>0.05</v>
       </c>
-      <c r="E89" s="73" t="n">
+      <c r="E89" s="72" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F89" s="16">
@@ -6461,7 +6473,7 @@
         <f>F89*D89</f>
         <v/>
       </c>
-      <c r="H89" s="70">
+      <c r="H89" s="69">
         <f>G89*E89</f>
         <v/>
       </c>
@@ -6484,10 +6496,10 @@
       <c r="C90" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="D90" s="73" t="n">
+      <c r="D90" s="72" t="n">
         <v>0.06</v>
       </c>
-      <c r="E90" s="73" t="n">
+      <c r="E90" s="72" t="n">
         <v>0.08</v>
       </c>
       <c r="F90" s="16">
@@ -6498,7 +6510,7 @@
         <f>F90*D90</f>
         <v/>
       </c>
-      <c r="H90" s="70">
+      <c r="H90" s="69">
         <f>G90*E90</f>
         <v/>
       </c>
@@ -6521,10 +6533,10 @@
       <c r="C91" s="43" t="n">
         <v>60</v>
       </c>
-      <c r="D91" s="73" t="n">
+      <c r="D91" s="72" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E91" s="73" t="n">
+      <c r="E91" s="72" t="n">
         <v>0.09</v>
       </c>
       <c r="F91" s="16">
@@ -6535,7 +6547,7 @@
         <f>F91*D91</f>
         <v/>
       </c>
-      <c r="H91" s="70">
+      <c r="H91" s="69">
         <f>G91*E91</f>
         <v/>
       </c>
@@ -6558,10 +6570,10 @@
       <c r="C92" s="43" t="n">
         <v>55</v>
       </c>
-      <c r="D92" s="73" t="n">
+      <c r="D92" s="72" t="n">
         <v>0.08</v>
       </c>
-      <c r="E92" s="73" t="n">
+      <c r="E92" s="72" t="n">
         <v>0.1</v>
       </c>
       <c r="F92" s="16">
@@ -6572,7 +6584,7 @@
         <f>F92*D92</f>
         <v/>
       </c>
-      <c r="H92" s="70">
+      <c r="H92" s="69">
         <f>G92*E92</f>
         <v/>
       </c>
@@ -6587,7 +6599,7 @@
           <t>ИТОГО за 6 мес (новых платящих)</t>
         </is>
       </c>
-      <c r="H93" s="74">
+      <c r="H93" s="73">
         <f>SUM(H87:H92)</f>
         <v/>
       </c>
@@ -6638,7 +6650,7 @@
       <c r="C99" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D99" s="63" t="inlineStr">
+      <c r="D99" s="62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6661,7 +6673,7 @@
       <c r="C100" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D100" s="72" t="inlineStr">
+      <c r="D100" s="71" t="inlineStr">
         <is>
           <t>−27</t>
         </is>
@@ -6684,7 +6696,7 @@
       <c r="C101" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D101" s="72" t="inlineStr">
+      <c r="D101" s="71" t="inlineStr">
         <is>
           <t>−75</t>
         </is>
@@ -6707,7 +6719,7 @@
       <c r="C102" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="D102" s="72" t="inlineStr">
+      <c r="D102" s="71" t="inlineStr">
         <is>
           <t>−143</t>
         </is>
@@ -6730,7 +6742,7 @@
       <c r="C103" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="D103" s="72" t="inlineStr">
+      <c r="D103" s="71" t="inlineStr">
         <is>
           <t>−240</t>
         </is>
@@ -6753,7 +6765,7 @@
       <c r="C104" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D104" s="72" t="inlineStr">
+      <c r="D104" s="71" t="inlineStr">
         <is>
           <t>−365</t>
         </is>
@@ -6770,17 +6782,17 @@
           <t>M7+</t>
         </is>
       </c>
-      <c r="B105" s="71" t="inlineStr">
+      <c r="B105" s="70" t="inlineStr">
         <is>
           <t>540+</t>
         </is>
       </c>
-      <c r="C105" s="71" t="inlineStr">
+      <c r="C105" s="70" t="inlineStr">
         <is>
           <t>20-30</t>
         </is>
       </c>
-      <c r="D105" s="63" t="inlineStr">
+      <c r="D105" s="62" t="inlineStr">
         <is>
           <t>догоняет</t>
         </is>
@@ -6792,7 +6804,7 @@
       </c>
     </row>
     <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="75" t="inlineStr">
+      <c r="A108" s="74" t="inlineStr">
         <is>
           <t>ВЫВОД: 100К ₽ ТОЛЬКО на ЧИСТЫХ запросах в Direct в первый месяц = 3 платящих (vs 1 на грязном ядре). Грязные запросы (тильда / создать сайт / сайт бесплатно) — это freebie hunters и loyalty конкурентов, downstream conversion 0.5-1%. На чистых vertical / AI / pain ключах CV лендинга +60% и Trial→Paid +20%. Финплан М2=30 требует мульти-канал (Direct 60К + VK 25К + Telegram 15К → 8-12) + buzz (VC.ru → +14).</t>
         </is>

--- a/docs/Token_Economics_v1.xlsx
+++ b/docs/Token_Economics_v1.xlsx
@@ -21,7 +21,7 @@
     <sheet name="12. Qwen self-hosted" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="13. Lean opex" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="14. Lean точки безубыточности" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15. Финмодель 24 мес" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15. Финмодель РЕАЛЬНАЯ 24м" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="16. Маркетинг 2026 (clean)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,12 +214,7 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,6 +227,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3048,7 +3044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3075,14 +3071,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финмодель 24 месяца · структура расходов как доля выручки</t>
+          <t>РЕАЛИСТИЧНАЯ финмодель 24 месяца · все 9 категорий расходов май 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Зарплаты = 30% выручки (с минимумом 30к в M1-M4) · Токены+инфра = 30% · Бэкофис (VPS клиенту + домены + операционка) = 10% · Маркетинг = отдельно фиксированно. Платящие пересчитаны под маркетинговую реальность 2026.</t>
+          <t>Зарплаты по плану найма (gross × 1.13 с IT-аккредитацией) · Токены 30% · Инфра ступенчато · Бэкофис 9% (включая 2.8% эквайринг) · Юр/бух/ПО/Резерв/Налог · Маркетинг фикс. Стартовый капитал 3 М ₽.</t>
         </is>
       </c>
     </row>
@@ -3477,988 +3473,1275 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Зарплаты (30% выручки или 30к, что больше), ₽</t>
-        </is>
-      </c>
-      <c r="B9" s="43">
-        <f>MAX(30000,B7*0.3)</f>
-        <v/>
-      </c>
-      <c r="C9" s="43">
-        <f>MAX(30000,C7*0.3)</f>
-        <v/>
-      </c>
-      <c r="D9" s="43">
-        <f>MAX(30000,D7*0.3)</f>
-        <v/>
-      </c>
-      <c r="E9" s="43">
-        <f>MAX(30000,E7*0.3)</f>
-        <v/>
-      </c>
-      <c r="F9" s="43">
-        <f>MAX(30000,F7*0.3)</f>
-        <v/>
-      </c>
-      <c r="G9" s="43">
-        <f>MAX(30000,G7*0.3)</f>
-        <v/>
-      </c>
-      <c r="H9" s="43">
-        <f>MAX(30000,H7*0.3)</f>
-        <v/>
-      </c>
-      <c r="I9" s="43">
-        <f>MAX(30000,I7*0.3)</f>
-        <v/>
-      </c>
-      <c r="J9" s="43">
-        <f>MAX(30000,J7*0.3)</f>
-        <v/>
-      </c>
-      <c r="K9" s="43">
-        <f>MAX(30000,K7*0.3)</f>
-        <v/>
-      </c>
-      <c r="L9" s="43">
-        <f>MAX(30000,L7*0.3)</f>
-        <v/>
-      </c>
-      <c r="M9" s="43">
-        <f>MAX(30000,M7*0.3)</f>
-        <v/>
-      </c>
-      <c r="N9" s="43">
-        <f>MAX(30000,N7*0.3)</f>
-        <v/>
-      </c>
-      <c r="O9" s="43">
-        <f>MAX(30000,O7*0.3)</f>
-        <v/>
-      </c>
-      <c r="P9" s="43">
-        <f>MAX(30000,P7*0.3)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="43">
-        <f>MAX(30000,Q7*0.3)</f>
-        <v/>
-      </c>
-      <c r="R9" s="43">
-        <f>MAX(30000,R7*0.3)</f>
-        <v/>
-      </c>
-      <c r="S9" s="43">
-        <f>MAX(30000,S7*0.3)</f>
-        <v/>
-      </c>
-      <c r="T9" s="43">
-        <f>MAX(30000,T7*0.3)</f>
-        <v/>
-      </c>
-      <c r="U9" s="43">
-        <f>MAX(30000,U7*0.3)</f>
-        <v/>
-      </c>
-      <c r="V9" s="43">
-        <f>MAX(30000,V7*0.3)</f>
-        <v/>
-      </c>
-      <c r="W9" s="43">
-        <f>MAX(30000,W7*0.3)</f>
-        <v/>
-      </c>
-      <c r="X9" s="43">
-        <f>MAX(30000,X7*0.3)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="43">
-        <f>MAX(30000,Y7*0.3)</f>
-        <v/>
+          <t>Команда (ФОТ × 1.10–1.13 страх+бенеф), ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>61800</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>144200</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>144200</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>426800</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>503940</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>596960</v>
+      </c>
+      <c r="H9" s="43" t="n">
+        <v>788739</v>
+      </c>
+      <c r="I9" s="43" t="n">
+        <v>979709</v>
+      </c>
+      <c r="J9" s="43" t="n">
+        <v>979709</v>
+      </c>
+      <c r="K9" s="43" t="n">
+        <v>1424929</v>
+      </c>
+      <c r="L9" s="43" t="n">
+        <v>1424929</v>
+      </c>
+      <c r="M9" s="43" t="n">
+        <v>1908569</v>
+      </c>
+      <c r="N9" s="43" t="n">
+        <v>1908569</v>
+      </c>
+      <c r="O9" s="43" t="n">
+        <v>1908569</v>
+      </c>
+      <c r="P9" s="43" t="n">
+        <v>2583179</v>
+      </c>
+      <c r="Q9" s="43" t="n">
+        <v>2583179</v>
+      </c>
+      <c r="R9" s="43" t="n">
+        <v>2583179</v>
+      </c>
+      <c r="S9" s="43" t="n">
+        <v>2939129</v>
+      </c>
+      <c r="T9" s="43" t="n">
+        <v>2939129</v>
+      </c>
+      <c r="U9" s="43" t="n">
+        <v>2939129</v>
+      </c>
+      <c r="V9" s="43" t="n">
+        <v>3079249</v>
+      </c>
+      <c r="W9" s="43" t="n">
+        <v>3079249</v>
+      </c>
+      <c r="X9" s="43" t="n">
+        <v>3079249</v>
+      </c>
+      <c r="Y9" s="43" t="n">
+        <v>3079249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Токены + наша инфра (30% выручки), ₽</t>
+          <t>Токены LLM (30% выручки), ₽</t>
         </is>
       </c>
       <c r="B10" s="43">
-        <f>B7*0.3</f>
+        <f>B7*0.30</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>C7*0.3</f>
+        <f>C7*0.30</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>D7*0.3</f>
+        <f>D7*0.30</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>E7*0.3</f>
+        <f>E7*0.30</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>F7*0.3</f>
+        <f>F7*0.30</f>
         <v/>
       </c>
       <c r="G10" s="43">
-        <f>G7*0.3</f>
+        <f>G7*0.30</f>
         <v/>
       </c>
       <c r="H10" s="43">
-        <f>H7*0.3</f>
+        <f>H7*0.30</f>
         <v/>
       </c>
       <c r="I10" s="43">
-        <f>I7*0.3</f>
+        <f>I7*0.30</f>
         <v/>
       </c>
       <c r="J10" s="43">
-        <f>J7*0.3</f>
+        <f>J7*0.30</f>
         <v/>
       </c>
       <c r="K10" s="43">
-        <f>K7*0.3</f>
+        <f>K7*0.30</f>
         <v/>
       </c>
       <c r="L10" s="43">
-        <f>L7*0.3</f>
+        <f>L7*0.30</f>
         <v/>
       </c>
       <c r="M10" s="43">
-        <f>M7*0.3</f>
+        <f>M7*0.30</f>
         <v/>
       </c>
       <c r="N10" s="43">
-        <f>N7*0.3</f>
+        <f>N7*0.30</f>
         <v/>
       </c>
       <c r="O10" s="43">
-        <f>O7*0.3</f>
+        <f>O7*0.30</f>
         <v/>
       </c>
       <c r="P10" s="43">
-        <f>P7*0.3</f>
+        <f>P7*0.30</f>
         <v/>
       </c>
       <c r="Q10" s="43">
-        <f>Q7*0.3</f>
+        <f>Q7*0.30</f>
         <v/>
       </c>
       <c r="R10" s="43">
-        <f>R7*0.3</f>
+        <f>R7*0.30</f>
         <v/>
       </c>
       <c r="S10" s="43">
-        <f>S7*0.3</f>
+        <f>S7*0.30</f>
         <v/>
       </c>
       <c r="T10" s="43">
-        <f>T7*0.3</f>
+        <f>T7*0.30</f>
         <v/>
       </c>
       <c r="U10" s="43">
-        <f>U7*0.3</f>
+        <f>U7*0.30</f>
         <v/>
       </c>
       <c r="V10" s="43">
-        <f>V7*0.3</f>
+        <f>V7*0.30</f>
         <v/>
       </c>
       <c r="W10" s="43">
-        <f>W7*0.3</f>
+        <f>W7*0.30</f>
         <v/>
       </c>
       <c r="X10" s="43">
-        <f>X7*0.3</f>
+        <f>X7*0.30</f>
         <v/>
       </c>
       <c r="Y10" s="43">
-        <f>Y7*0.3</f>
+        <f>Y7*0.30</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Бэкофис: VPS клиентов + домены + опер (10%), ₽</t>
-        </is>
-      </c>
-      <c r="B11" s="43">
-        <f>B7*0.1</f>
-        <v/>
-      </c>
-      <c r="C11" s="43">
-        <f>C7*0.1</f>
-        <v/>
-      </c>
-      <c r="D11" s="43">
-        <f>D7*0.1</f>
-        <v/>
-      </c>
-      <c r="E11" s="43">
-        <f>E7*0.1</f>
-        <v/>
-      </c>
-      <c r="F11" s="43">
-        <f>F7*0.1</f>
-        <v/>
-      </c>
-      <c r="G11" s="43">
-        <f>G7*0.1</f>
-        <v/>
-      </c>
-      <c r="H11" s="43">
-        <f>H7*0.1</f>
-        <v/>
-      </c>
-      <c r="I11" s="43">
-        <f>I7*0.1</f>
-        <v/>
-      </c>
-      <c r="J11" s="43">
-        <f>J7*0.1</f>
-        <v/>
-      </c>
-      <c r="K11" s="43">
-        <f>K7*0.1</f>
-        <v/>
-      </c>
-      <c r="L11" s="43">
-        <f>L7*0.1</f>
-        <v/>
-      </c>
-      <c r="M11" s="43">
-        <f>M7*0.1</f>
-        <v/>
-      </c>
-      <c r="N11" s="43">
-        <f>N7*0.1</f>
-        <v/>
-      </c>
-      <c r="O11" s="43">
-        <f>O7*0.1</f>
-        <v/>
-      </c>
-      <c r="P11" s="43">
-        <f>P7*0.1</f>
-        <v/>
-      </c>
-      <c r="Q11" s="43">
-        <f>Q7*0.1</f>
-        <v/>
-      </c>
-      <c r="R11" s="43">
-        <f>R7*0.1</f>
-        <v/>
-      </c>
-      <c r="S11" s="43">
-        <f>S7*0.1</f>
-        <v/>
-      </c>
-      <c r="T11" s="43">
-        <f>T7*0.1</f>
-        <v/>
-      </c>
-      <c r="U11" s="43">
-        <f>U7*0.1</f>
-        <v/>
-      </c>
-      <c r="V11" s="43">
-        <f>V7*0.1</f>
-        <v/>
-      </c>
-      <c r="W11" s="43">
-        <f>W7*0.1</f>
-        <v/>
-      </c>
-      <c r="X11" s="43">
-        <f>X7*0.1</f>
-        <v/>
-      </c>
-      <c r="Y11" s="43">
-        <f>Y7*0.1</f>
-        <v/>
+          <t>Наша инфра (Yandex/Selectel/мониторинг), ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H11" s="43" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I11" s="43" t="n">
+        <v>85000</v>
+      </c>
+      <c r="J11" s="43" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K11" s="43" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L11" s="43" t="n">
+        <v>160000</v>
+      </c>
+      <c r="M11" s="43" t="n">
+        <v>195000</v>
+      </c>
+      <c r="N11" s="43" t="n">
+        <v>235000</v>
+      </c>
+      <c r="O11" s="43" t="n">
+        <v>280000</v>
+      </c>
+      <c r="P11" s="43" t="n">
+        <v>330000</v>
+      </c>
+      <c r="Q11" s="43" t="n">
+        <v>380000</v>
+      </c>
+      <c r="R11" s="43" t="n">
+        <v>430000</v>
+      </c>
+      <c r="S11" s="43" t="n">
+        <v>480000</v>
+      </c>
+      <c r="T11" s="43" t="n">
+        <v>530000</v>
+      </c>
+      <c r="U11" s="43" t="n">
+        <v>580000</v>
+      </c>
+      <c r="V11" s="43" t="n">
+        <v>630000</v>
+      </c>
+      <c r="W11" s="43" t="n">
+        <v>680000</v>
+      </c>
+      <c r="X11" s="43" t="n">
+        <v>730000</v>
+      </c>
+      <c r="Y11" s="43" t="n">
+        <v>780000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Маркетинг и реклама (фиксированный бюджет), ₽</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="n">
+          <t>Бэкофис: эквайринг+VPS клиентов+домены (9%), ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="43">
+        <f>B7*0.09</f>
+        <v/>
+      </c>
+      <c r="C12" s="43">
+        <f>C7*0.09</f>
+        <v/>
+      </c>
+      <c r="D12" s="43">
+        <f>D7*0.09</f>
+        <v/>
+      </c>
+      <c r="E12" s="43">
+        <f>E7*0.09</f>
+        <v/>
+      </c>
+      <c r="F12" s="43">
+        <f>F7*0.09</f>
+        <v/>
+      </c>
+      <c r="G12" s="43">
+        <f>G7*0.09</f>
+        <v/>
+      </c>
+      <c r="H12" s="43">
+        <f>H7*0.09</f>
+        <v/>
+      </c>
+      <c r="I12" s="43">
+        <f>I7*0.09</f>
+        <v/>
+      </c>
+      <c r="J12" s="43">
+        <f>J7*0.09</f>
+        <v/>
+      </c>
+      <c r="K12" s="43">
+        <f>K7*0.09</f>
+        <v/>
+      </c>
+      <c r="L12" s="43">
+        <f>L7*0.09</f>
+        <v/>
+      </c>
+      <c r="M12" s="43">
+        <f>M7*0.09</f>
+        <v/>
+      </c>
+      <c r="N12" s="43">
+        <f>N7*0.09</f>
+        <v/>
+      </c>
+      <c r="O12" s="43">
+        <f>O7*0.09</f>
+        <v/>
+      </c>
+      <c r="P12" s="43">
+        <f>P7*0.09</f>
+        <v/>
+      </c>
+      <c r="Q12" s="43">
+        <f>Q7*0.09</f>
+        <v/>
+      </c>
+      <c r="R12" s="43">
+        <f>R7*0.09</f>
+        <v/>
+      </c>
+      <c r="S12" s="43">
+        <f>S7*0.09</f>
+        <v/>
+      </c>
+      <c r="T12" s="43">
+        <f>T7*0.09</f>
+        <v/>
+      </c>
+      <c r="U12" s="43">
+        <f>U7*0.09</f>
+        <v/>
+      </c>
+      <c r="V12" s="43">
+        <f>V7*0.09</f>
+        <v/>
+      </c>
+      <c r="W12" s="43">
+        <f>W7*0.09</f>
+        <v/>
+      </c>
+      <c r="X12" s="43">
+        <f>X7*0.09</f>
+        <v/>
+      </c>
+      <c r="Y12" s="43">
+        <f>Y7*0.09</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Юристы / бухгалтеры / банк / аудит, ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F13" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K13" s="43" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L13" s="43" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M13" s="43" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N13" s="43" t="n">
+        <v>80000</v>
+      </c>
+      <c r="O13" s="43" t="n">
+        <v>80000</v>
+      </c>
+      <c r="P13" s="43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Q13" s="43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R13" s="43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S13" s="43" t="n">
+        <v>120000</v>
+      </c>
+      <c r="T13" s="43" t="n">
+        <v>120000</v>
+      </c>
+      <c r="U13" s="43" t="n">
+        <v>120000</v>
+      </c>
+      <c r="V13" s="43" t="n">
+        <v>140000</v>
+      </c>
+      <c r="W13" s="43" t="n">
+        <v>140000</v>
+      </c>
+      <c r="X13" s="43" t="n">
+        <v>140000</v>
+      </c>
+      <c r="Y13" s="43" t="n">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ПО на сотрудника (Figma/JetBrains/...), ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G14" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H14" s="43" t="n">
+        <v>35000</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>42000</v>
+      </c>
+      <c r="J14" s="43" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K14" s="43" t="n">
+        <v>49000</v>
+      </c>
+      <c r="L14" s="43" t="n">
+        <v>49000</v>
+      </c>
+      <c r="M14" s="43" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N14" s="43" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O14" s="43" t="n">
+        <v>63000</v>
+      </c>
+      <c r="P14" s="43" t="n">
+        <v>77000</v>
+      </c>
+      <c r="Q14" s="43" t="n">
+        <v>77000</v>
+      </c>
+      <c r="R14" s="43" t="n">
+        <v>77000</v>
+      </c>
+      <c r="S14" s="43" t="n">
+        <v>84000</v>
+      </c>
+      <c r="T14" s="43" t="n">
+        <v>84000</v>
+      </c>
+      <c r="U14" s="43" t="n">
+        <v>84000</v>
+      </c>
+      <c r="V14" s="43" t="n">
+        <v>91000</v>
+      </c>
+      <c r="W14" s="43" t="n">
+        <v>91000</v>
+      </c>
+      <c r="X14" s="43" t="n">
+        <v>91000</v>
+      </c>
+      <c r="Y14" s="43" t="n">
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Маркетинг фикс.бюджет, ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="58" t="n">
+      <c r="C15" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="D12" s="58" t="n">
+      <c r="D15" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="E12" s="58" t="n">
+      <c r="E15" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="F12" s="58" t="n">
+      <c r="F15" s="58" t="n">
         <v>100000</v>
       </c>
-      <c r="G12" s="58" t="n">
+      <c r="G15" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="H12" s="58" t="n">
+      <c r="H15" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="I12" s="58" t="n">
+      <c r="I15" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="J12" s="58" t="n">
+      <c r="J15" s="58" t="n">
         <v>150000</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K15" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L15" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="M12" s="58" t="n">
+      <c r="M15" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="N12" s="58" t="n">
+      <c r="N15" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="O12" s="58" t="n">
+      <c r="O15" s="58" t="n">
         <v>200000</v>
       </c>
-      <c r="P12" s="58" t="n">
+      <c r="P15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="Q12" s="58" t="n">
+      <c r="Q15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="R12" s="58" t="n">
+      <c r="R15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="S12" s="58" t="n">
+      <c r="S15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="T12" s="58" t="n">
+      <c r="T15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="U12" s="58" t="n">
+      <c r="U15" s="58" t="n">
         <v>250000</v>
       </c>
-      <c r="V12" s="58" t="n">
+      <c r="V15" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="W12" s="58" t="n">
+      <c r="W15" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="X12" s="58" t="n">
+      <c r="X15" s="58" t="n">
         <v>300000</v>
       </c>
-      <c r="Y12" s="58" t="n">
+      <c r="Y15" s="58" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Резервы (refunds 1.5% + штрафы 0.5% + 1.5% прочее), ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>B7*0.035</f>
+        <v/>
+      </c>
+      <c r="C16" s="43">
+        <f>C7*0.035</f>
+        <v/>
+      </c>
+      <c r="D16" s="43">
+        <f>D7*0.035</f>
+        <v/>
+      </c>
+      <c r="E16" s="43">
+        <f>E7*0.035</f>
+        <v/>
+      </c>
+      <c r="F16" s="43">
+        <f>F7*0.035</f>
+        <v/>
+      </c>
+      <c r="G16" s="43">
+        <f>G7*0.035</f>
+        <v/>
+      </c>
+      <c r="H16" s="43">
+        <f>H7*0.035</f>
+        <v/>
+      </c>
+      <c r="I16" s="43">
+        <f>I7*0.035</f>
+        <v/>
+      </c>
+      <c r="J16" s="43">
+        <f>J7*0.035</f>
+        <v/>
+      </c>
+      <c r="K16" s="43">
+        <f>K7*0.035</f>
+        <v/>
+      </c>
+      <c r="L16" s="43">
+        <f>L7*0.035</f>
+        <v/>
+      </c>
+      <c r="M16" s="43">
+        <f>M7*0.035</f>
+        <v/>
+      </c>
+      <c r="N16" s="43">
+        <f>N7*0.035</f>
+        <v/>
+      </c>
+      <c r="O16" s="43">
+        <f>O7*0.035</f>
+        <v/>
+      </c>
+      <c r="P16" s="43">
+        <f>P7*0.035</f>
+        <v/>
+      </c>
+      <c r="Q16" s="43">
+        <f>Q7*0.035</f>
+        <v/>
+      </c>
+      <c r="R16" s="43">
+        <f>R7*0.035</f>
+        <v/>
+      </c>
+      <c r="S16" s="43">
+        <f>S7*0.035</f>
+        <v/>
+      </c>
+      <c r="T16" s="43">
+        <f>T7*0.035</f>
+        <v/>
+      </c>
+      <c r="U16" s="43">
+        <f>U7*0.035</f>
+        <v/>
+      </c>
+      <c r="V16" s="43">
+        <f>V7*0.035</f>
+        <v/>
+      </c>
+      <c r="W16" s="43">
+        <f>W7*0.035</f>
+        <v/>
+      </c>
+      <c r="X16" s="43">
+        <f>X7*0.035</f>
+        <v/>
+      </c>
+      <c r="Y16" s="43">
+        <f>Y7*0.035</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Налоги (УСН 6%→1% с M4 IT-льгота), ₽</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>B7*0.06</f>
+        <v/>
+      </c>
+      <c r="C17" s="43">
+        <f>C7*0.06</f>
+        <v/>
+      </c>
+      <c r="D17" s="43">
+        <f>D7*0.06</f>
+        <v/>
+      </c>
+      <c r="E17" s="43">
+        <f>E7*0.01</f>
+        <v/>
+      </c>
+      <c r="F17" s="43">
+        <f>F7*0.01</f>
+        <v/>
+      </c>
+      <c r="G17" s="43">
+        <f>G7*0.01</f>
+        <v/>
+      </c>
+      <c r="H17" s="43">
+        <f>H7*0.01</f>
+        <v/>
+      </c>
+      <c r="I17" s="43">
+        <f>I7*0.01</f>
+        <v/>
+      </c>
+      <c r="J17" s="43">
+        <f>J7*0.01</f>
+        <v/>
+      </c>
+      <c r="K17" s="43">
+        <f>K7*0.01</f>
+        <v/>
+      </c>
+      <c r="L17" s="43">
+        <f>L7*0.01</f>
+        <v/>
+      </c>
+      <c r="M17" s="43">
+        <f>M7*0.01</f>
+        <v/>
+      </c>
+      <c r="N17" s="43">
+        <f>N7*0.01</f>
+        <v/>
+      </c>
+      <c r="O17" s="43">
+        <f>O7*0.01</f>
+        <v/>
+      </c>
+      <c r="P17" s="43">
+        <f>P7*0.01</f>
+        <v/>
+      </c>
+      <c r="Q17" s="43">
+        <f>Q7*0.01</f>
+        <v/>
+      </c>
+      <c r="R17" s="43">
+        <f>R7*0.01</f>
+        <v/>
+      </c>
+      <c r="S17" s="43">
+        <f>S7*0.01</f>
+        <v/>
+      </c>
+      <c r="T17" s="43">
+        <f>T7*0.01</f>
+        <v/>
+      </c>
+      <c r="U17" s="43">
+        <f>U7*0.01</f>
+        <v/>
+      </c>
+      <c r="V17" s="43">
+        <f>V7*0.01</f>
+        <v/>
+      </c>
+      <c r="W17" s="43">
+        <f>W7*0.01</f>
+        <v/>
+      </c>
+      <c r="X17" s="43">
+        <f>X7*0.01</f>
+        <v/>
+      </c>
+      <c r="Y17" s="43">
+        <f>Y7*0.01</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>ИТОГО ОПЕРАЦИОННЫХ РАСХОДОВ, ₽</t>
         </is>
       </c>
-      <c r="B14" s="59">
-        <f>SUM(B9:B12)</f>
-        <v/>
-      </c>
-      <c r="C14" s="59">
-        <f>SUM(C9:C12)</f>
-        <v/>
-      </c>
-      <c r="D14" s="59">
-        <f>SUM(D9:D12)</f>
-        <v/>
-      </c>
-      <c r="E14" s="59">
-        <f>SUM(E9:E12)</f>
-        <v/>
-      </c>
-      <c r="F14" s="59">
-        <f>SUM(F9:F12)</f>
-        <v/>
-      </c>
-      <c r="G14" s="59">
-        <f>SUM(G9:G12)</f>
-        <v/>
-      </c>
-      <c r="H14" s="59">
-        <f>SUM(H9:H12)</f>
-        <v/>
-      </c>
-      <c r="I14" s="59">
-        <f>SUM(I9:I12)</f>
-        <v/>
-      </c>
-      <c r="J14" s="59">
-        <f>SUM(J9:J12)</f>
-        <v/>
-      </c>
-      <c r="K14" s="59">
-        <f>SUM(K9:K12)</f>
-        <v/>
-      </c>
-      <c r="L14" s="59">
-        <f>SUM(L9:L12)</f>
-        <v/>
-      </c>
-      <c r="M14" s="59">
-        <f>SUM(M9:M12)</f>
-        <v/>
-      </c>
-      <c r="N14" s="59">
-        <f>SUM(N9:N12)</f>
-        <v/>
-      </c>
-      <c r="O14" s="59">
-        <f>SUM(O9:O12)</f>
-        <v/>
-      </c>
-      <c r="P14" s="59">
-        <f>SUM(P9:P12)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="59">
-        <f>SUM(Q9:Q12)</f>
-        <v/>
-      </c>
-      <c r="R14" s="59">
-        <f>SUM(R9:R12)</f>
-        <v/>
-      </c>
-      <c r="S14" s="59">
-        <f>SUM(S9:S12)</f>
-        <v/>
-      </c>
-      <c r="T14" s="59">
-        <f>SUM(T9:T12)</f>
-        <v/>
-      </c>
-      <c r="U14" s="59">
-        <f>SUM(U9:U12)</f>
-        <v/>
-      </c>
-      <c r="V14" s="59">
-        <f>SUM(V9:V12)</f>
-        <v/>
-      </c>
-      <c r="W14" s="59">
-        <f>SUM(W9:W12)</f>
-        <v/>
-      </c>
-      <c r="X14" s="59">
-        <f>SUM(X9:X12)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="59">
-        <f>SUM(Y9:Y12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>ОПЕРАЦИОННАЯ ПРИБЫЛЬ/УБЫТОК, ₽</t>
-        </is>
-      </c>
-      <c r="B16" s="60">
-        <f>B7-B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="60">
-        <f>C7-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="60">
-        <f>D7-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="60">
-        <f>E7-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="60">
-        <f>F7-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="60">
-        <f>G7-G14</f>
-        <v/>
-      </c>
-      <c r="H16" s="60">
-        <f>H7-H14</f>
-        <v/>
-      </c>
-      <c r="I16" s="60">
-        <f>I7-I14</f>
-        <v/>
-      </c>
-      <c r="J16" s="60">
-        <f>J7-J14</f>
-        <v/>
-      </c>
-      <c r="K16" s="60">
-        <f>K7-K14</f>
-        <v/>
-      </c>
-      <c r="L16" s="60">
-        <f>L7-L14</f>
-        <v/>
-      </c>
-      <c r="M16" s="60">
-        <f>M7-M14</f>
-        <v/>
-      </c>
-      <c r="N16" s="60">
-        <f>N7-N14</f>
-        <v/>
-      </c>
-      <c r="O16" s="60">
-        <f>O7-O14</f>
-        <v/>
-      </c>
-      <c r="P16" s="60">
-        <f>P7-P14</f>
-        <v/>
-      </c>
-      <c r="Q16" s="60">
-        <f>Q7-Q14</f>
-        <v/>
-      </c>
-      <c r="R16" s="60">
-        <f>R7-R14</f>
-        <v/>
-      </c>
-      <c r="S16" s="60">
-        <f>S7-S14</f>
-        <v/>
-      </c>
-      <c r="T16" s="60">
-        <f>T7-T14</f>
-        <v/>
-      </c>
-      <c r="U16" s="60">
-        <f>U7-U14</f>
-        <v/>
-      </c>
-      <c r="V16" s="60">
-        <f>V7-V14</f>
-        <v/>
-      </c>
-      <c r="W16" s="60">
-        <f>W7-W14</f>
-        <v/>
-      </c>
-      <c r="X16" s="60">
-        <f>X7-X14</f>
-        <v/>
-      </c>
-      <c r="Y16" s="60">
-        <f>Y7-Y14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>Накопленные деньги на счёте (старт 30к ₽), ₽</t>
-        </is>
-      </c>
-      <c r="B17" s="60">
-        <f>30000+B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="49">
-        <f>B17+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="49">
-        <f>C17+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="49">
-        <f>D17+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="49">
-        <f>E17+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="49">
-        <f>F17+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="49">
-        <f>G17+H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="49">
-        <f>H17+I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="49">
-        <f>I17+J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="49">
-        <f>J17+K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="49">
-        <f>K17+L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="49">
-        <f>L17+M16</f>
-        <v/>
-      </c>
-      <c r="N17" s="49">
-        <f>M17+N16</f>
-        <v/>
-      </c>
-      <c r="O17" s="49">
-        <f>N17+O16</f>
-        <v/>
-      </c>
-      <c r="P17" s="49">
-        <f>O17+P16</f>
-        <v/>
-      </c>
-      <c r="Q17" s="49">
-        <f>P17+Q16</f>
-        <v/>
-      </c>
-      <c r="R17" s="49">
-        <f>Q17+R16</f>
-        <v/>
-      </c>
-      <c r="S17" s="49">
-        <f>R17+S16</f>
-        <v/>
-      </c>
-      <c r="T17" s="49">
-        <f>S17+T16</f>
-        <v/>
-      </c>
-      <c r="U17" s="49">
-        <f>T17+U16</f>
-        <v/>
-      </c>
-      <c r="V17" s="49">
-        <f>U17+V16</f>
-        <v/>
-      </c>
-      <c r="W17" s="49">
-        <f>V17+W16</f>
-        <v/>
-      </c>
-      <c r="X17" s="49">
-        <f>W17+X16</f>
-        <v/>
-      </c>
-      <c r="Y17" s="49">
-        <f>X17+Y16</f>
+      <c r="B19" s="59">
+        <f>SUM(B9:B17)</f>
+        <v/>
+      </c>
+      <c r="C19" s="59">
+        <f>SUM(C9:C17)</f>
+        <v/>
+      </c>
+      <c r="D19" s="59">
+        <f>SUM(D9:D17)</f>
+        <v/>
+      </c>
+      <c r="E19" s="59">
+        <f>SUM(E9:E17)</f>
+        <v/>
+      </c>
+      <c r="F19" s="59">
+        <f>SUM(F9:F17)</f>
+        <v/>
+      </c>
+      <c r="G19" s="59">
+        <f>SUM(G9:G17)</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>SUM(H9:H17)</f>
+        <v/>
+      </c>
+      <c r="I19" s="59">
+        <f>SUM(I9:I17)</f>
+        <v/>
+      </c>
+      <c r="J19" s="59">
+        <f>SUM(J9:J17)</f>
+        <v/>
+      </c>
+      <c r="K19" s="59">
+        <f>SUM(K9:K17)</f>
+        <v/>
+      </c>
+      <c r="L19" s="59">
+        <f>SUM(L9:L17)</f>
+        <v/>
+      </c>
+      <c r="M19" s="59">
+        <f>SUM(M9:M17)</f>
+        <v/>
+      </c>
+      <c r="N19" s="59">
+        <f>SUM(N9:N17)</f>
+        <v/>
+      </c>
+      <c r="O19" s="59">
+        <f>SUM(O9:O17)</f>
+        <v/>
+      </c>
+      <c r="P19" s="59">
+        <f>SUM(P9:P17)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="59">
+        <f>SUM(Q9:Q17)</f>
+        <v/>
+      </c>
+      <c r="R19" s="59">
+        <f>SUM(R9:R17)</f>
+        <v/>
+      </c>
+      <c r="S19" s="59">
+        <f>SUM(S9:S17)</f>
+        <v/>
+      </c>
+      <c r="T19" s="59">
+        <f>SUM(T9:T17)</f>
+        <v/>
+      </c>
+      <c r="U19" s="59">
+        <f>SUM(U9:U17)</f>
+        <v/>
+      </c>
+      <c r="V19" s="59">
+        <f>SUM(V9:V17)</f>
+        <v/>
+      </c>
+      <c r="W19" s="59">
+        <f>SUM(W9:W17)</f>
+        <v/>
+      </c>
+      <c r="X19" s="59">
+        <f>SUM(X9:X17)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="59">
+        <f>SUM(Y9:Y17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>ПРИБЫЛЬ/УБЫТОК, ₽</t>
+        </is>
+      </c>
+      <c r="B20" s="60">
+        <f>B7-B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="60">
+        <f>C7-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="60">
+        <f>D7-D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="60">
+        <f>E7-E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="60">
+        <f>F7-F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="60">
+        <f>G7-G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="60">
+        <f>H7-H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="60">
+        <f>I7-I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="60">
+        <f>J7-J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="60">
+        <f>K7-K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="60">
+        <f>L7-L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="60">
+        <f>M7-M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="60">
+        <f>N7-N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="60">
+        <f>O7-O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="60">
+        <f>P7-P19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="60">
+        <f>Q7-Q19</f>
+        <v/>
+      </c>
+      <c r="R20" s="60">
+        <f>R7-R19</f>
+        <v/>
+      </c>
+      <c r="S20" s="60">
+        <f>S7-S19</f>
+        <v/>
+      </c>
+      <c r="T20" s="60">
+        <f>T7-T19</f>
+        <v/>
+      </c>
+      <c r="U20" s="60">
+        <f>U7-U19</f>
+        <v/>
+      </c>
+      <c r="V20" s="60">
+        <f>V7-V19</f>
+        <v/>
+      </c>
+      <c r="W20" s="60">
+        <f>W7-W19</f>
+        <v/>
+      </c>
+      <c r="X20" s="60">
+        <f>X7-X19</f>
+        <v/>
+      </c>
+      <c r="Y20" s="60">
+        <f>Y7-Y19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Деньги на счёте (старт 3 М ₽), ₽</t>
+        </is>
+      </c>
+      <c r="B21" s="60">
+        <f>3000000+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="49">
+        <f>B21+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="49">
+        <f>C21+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="49">
+        <f>D21+E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="49">
+        <f>E21+F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="49">
+        <f>F21+G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="49">
+        <f>G21+H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="49">
+        <f>H21+I20</f>
+        <v/>
+      </c>
+      <c r="J21" s="49">
+        <f>I21+J20</f>
+        <v/>
+      </c>
+      <c r="K21" s="49">
+        <f>J21+K20</f>
+        <v/>
+      </c>
+      <c r="L21" s="49">
+        <f>K21+L20</f>
+        <v/>
+      </c>
+      <c r="M21" s="49">
+        <f>L21+M20</f>
+        <v/>
+      </c>
+      <c r="N21" s="49">
+        <f>M21+N20</f>
+        <v/>
+      </c>
+      <c r="O21" s="49">
+        <f>N21+O20</f>
+        <v/>
+      </c>
+      <c r="P21" s="49">
+        <f>O21+P20</f>
+        <v/>
+      </c>
+      <c r="Q21" s="49">
+        <f>P21+Q20</f>
+        <v/>
+      </c>
+      <c r="R21" s="49">
+        <f>Q21+R20</f>
+        <v/>
+      </c>
+      <c r="S21" s="49">
+        <f>R21+S20</f>
+        <v/>
+      </c>
+      <c r="T21" s="49">
+        <f>S21+T20</f>
+        <v/>
+      </c>
+      <c r="U21" s="49">
+        <f>T21+U20</f>
+        <v/>
+      </c>
+      <c r="V21" s="49">
+        <f>U21+V20</f>
+        <v/>
+      </c>
+      <c r="W21" s="49">
+        <f>V21+W20</f>
+        <v/>
+      </c>
+      <c r="X21" s="49">
+        <f>W21+X20</f>
+        <v/>
+      </c>
+      <c r="Y21" s="49">
+        <f>X21+Y20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>ИТОГИ</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Выручка/мес на M24, ₽</t>
-        </is>
-      </c>
-      <c r="B21" s="53">
-        <f>Y7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Выручка/год на M24, ₽</t>
-        </is>
-      </c>
-      <c r="B22" s="53">
-        <f>Y7*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Деньги на счёте на M24, ₽</t>
-        </is>
-      </c>
-      <c r="B23" s="53">
-        <f>Y17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Самый большой минус по деньгам, ₽</t>
-        </is>
-      </c>
-      <c r="B24" s="59">
-        <f>MIN(B17:Y17)</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Платящих клиентов на M24</t>
-        </is>
-      </c>
-      <c r="B25" s="52">
-        <f>Y5</f>
+          <t>Выручка/мес на M24, ₽</t>
+        </is>
+      </c>
+      <c r="B25" s="53">
+        <f>Y7</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Месяц первой прибыли</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>M7 (с новой структурой 30/30/10/30)</t>
-        </is>
+          <t>Выручка/год на M24, ₽</t>
+        </is>
+      </c>
+      <c r="B26" s="53">
+        <f>Y7*12</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Месяц возврата вложений (счёт &gt; 0)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
+          <t>Деньги на счёте на M24, ₽</t>
+        </is>
+      </c>
+      <c r="B27" s="53">
+        <f>Y21</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Маркетинг суммарно за 24 мес, ₽</t>
-        </is>
-      </c>
-      <c r="B28" s="61">
-        <f>SUM(B12:Y12)</f>
+          <t>Самый большой минус (M9 ≈ -2.4 М)</t>
+        </is>
+      </c>
+      <c r="B28" s="59">
+        <f>MIN(B21:Y21)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Зарплаты суммарно за 24 мес, ₽</t>
-        </is>
-      </c>
-      <c r="B29" s="61">
-        <f>SUM(B9:Y9)</f>
+          <t>Платящих клиентов на M24</t>
+        </is>
+      </c>
+      <c r="B29" s="52">
+        <f>Y5</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Токены+инфра суммарно за 24 мес, ₽</t>
-        </is>
-      </c>
-      <c r="B30" s="61">
-        <f>SUM(B10:Y10)</f>
-        <v/>
+          <t>Месяц первой прибыли</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>M11 (с реалистичной командой)</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Бэкофис суммарно за 24 мес, ₽</t>
-        </is>
-      </c>
-      <c r="B31" s="61">
+          <t>Месяц возврата вложений (счёт &gt; 0)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Команда суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B32" s="61">
+        <f>SUM(B9:Y9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Токены суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B33" s="61">
+        <f>SUM(B10:Y10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Инфра суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B34" s="61">
         <f>SUM(B11:Y11)</f>
         <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Структура: 30% зарплаты / 30% токены+инфра / 10% бэкофис / 30% операц.доход (до маркетинга)</t>
-        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Платящих клиентов на M24</t>
-        </is>
-      </c>
-      <c r="B35" s="62" t="inlineStr">
-        <is>
-          <t>6 250</t>
-        </is>
-      </c>
-      <c r="C35" s="63" t="inlineStr">
-        <is>
-          <t>По плану</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Бэкофис суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B35" s="61">
+        <f>SUM(B12:Y12)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Месяц первой прибыли</t>
-        </is>
-      </c>
-      <c r="B36" s="62" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="C36" s="63" t="inlineStr">
-        <is>
-          <t>M6 (старая модель)</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>+1 мес позже</t>
-        </is>
+          <t>Юр+ПО+Резервы+Налоги суммарно, ₽</t>
+        </is>
+      </c>
+      <c r="B36" s="61">
+        <f>SUM(B13:Y14)+SUM(B16:Y17)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Месяц возврата вложений</t>
-        </is>
-      </c>
-      <c r="B37" s="62" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="C37" s="63" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>+1 мес позже</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Самый большой минус</t>
-        </is>
-      </c>
-      <c r="B38" s="62" t="inlineStr">
-        <is>
-          <t>~−380 К ₽</t>
-        </is>
-      </c>
-      <c r="C38" s="63" t="inlineStr">
-        <is>
-          <t>~−305 К</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>−25%</t>
-        </is>
+          <t>Маркетинг суммарно за 24 мес, ₽</t>
+        </is>
+      </c>
+      <c r="B37" s="61">
+        <f>SUM(B15:Y15)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Накопленные деньги на M24</t>
-        </is>
-      </c>
-      <c r="B39" s="62" t="inlineStr">
-        <is>
-          <t>~+60 М ₽</t>
-        </is>
-      </c>
-      <c r="C39" s="63" t="inlineStr">
-        <is>
-          <t>~+67 М (старая)</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>−7 М</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Почему стало хуже?</t>
-        </is>
-      </c>
-      <c r="B40" s="62" t="inlineStr">
-        <is>
-          <t>Зарплаты 30% + замедл. разгон M2-M6</t>
-        </is>
-      </c>
-      <c r="C40" s="63" t="inlineStr">
-        <is>
-          <t>В старой founders=0</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Что лучше?</t>
-        </is>
-      </c>
-      <c r="B41" s="62" t="inlineStr">
-        <is>
-          <t>Каждый рубль роста = +30к в команду</t>
-        </is>
-      </c>
-      <c r="C41" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Запас прочности</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Стартовый капитал 3 М ₽ обязателен. Минимум на счёте M9 ≈ +570 К ₽ (потеряли 2.4 М за 9 мес).</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4553,7 +4836,7 @@
       <c r="E5" s="57" t="n">
         <v>135</v>
       </c>
-      <c r="F5" s="64" t="n">
+      <c r="F5" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4577,7 +4860,7 @@
       <c r="E6" s="57" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="64" t="n">
+      <c r="F6" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4601,7 +4884,7 @@
       <c r="E7" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F7" s="64" t="n">
+      <c r="F7" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4625,7 +4908,7 @@
       <c r="E8" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="64" t="n">
+      <c r="F8" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4649,7 +4932,7 @@
       <c r="E9" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F9" s="64" t="n">
+      <c r="F9" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4673,7 +4956,7 @@
       <c r="E10" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F10" s="64" t="n">
+      <c r="F10" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4697,7 +4980,7 @@
       <c r="E11" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F11" s="64" t="n">
+      <c r="F11" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4721,7 +5004,7 @@
       <c r="E12" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F12" s="64" t="n">
+      <c r="F12" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4745,7 +5028,7 @@
       <c r="E13" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="64" t="n">
+      <c r="F13" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4769,7 +5052,7 @@
       <c r="E14" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F14" s="64" t="n">
+      <c r="F14" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4793,7 +5076,7 @@
       <c r="E15" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F15" s="64" t="n">
+      <c r="F15" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4817,7 +5100,7 @@
       <c r="E16" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F16" s="64" t="n">
+      <c r="F16" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4841,7 +5124,7 @@
       <c r="E17" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F17" s="64" t="n">
+      <c r="F17" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4865,7 +5148,7 @@
       <c r="E18" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F18" s="64" t="n">
+      <c r="F18" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4889,7 +5172,7 @@
       <c r="E19" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F19" s="64" t="n">
+      <c r="F19" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4913,7 +5196,7 @@
       <c r="E20" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F20" s="64" t="n">
+      <c r="F20" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4937,7 +5220,7 @@
       <c r="E21" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="F21" s="64" t="n">
+      <c r="F21" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4961,7 +5244,7 @@
       <c r="E22" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F22" s="64" t="n">
+      <c r="F22" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4985,7 +5268,7 @@
       <c r="E23" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F23" s="64" t="n">
+      <c r="F23" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5009,7 +5292,7 @@
       <c r="E24" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F24" s="64" t="n">
+      <c r="F24" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5033,7 +5316,7 @@
       <c r="E25" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F25" s="64" t="n">
+      <c r="F25" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5057,7 +5340,7 @@
       <c r="E26" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F26" s="64" t="n">
+      <c r="F26" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5081,7 +5364,7 @@
       <c r="E27" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F27" s="64" t="n">
+      <c r="F27" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5105,7 +5388,7 @@
       <c r="E28" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F28" s="64" t="n">
+      <c r="F28" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5129,7 +5412,7 @@
       <c r="E29" s="57" t="n">
         <v>165</v>
       </c>
-      <c r="F29" s="64" t="n">
+      <c r="F29" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5153,7 +5436,7 @@
       <c r="E30" s="57" t="n">
         <v>130</v>
       </c>
-      <c r="F30" s="64" t="n">
+      <c r="F30" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5177,7 +5460,7 @@
       <c r="E31" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F31" s="64" t="n">
+      <c r="F31" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5201,7 +5484,7 @@
       <c r="E32" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F32" s="64" t="n">
+      <c r="F32" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5225,7 +5508,7 @@
       <c r="E33" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="64" t="n">
+      <c r="F33" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5249,7 +5532,7 @@
       <c r="E34" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F34" s="64" t="n">
+      <c r="F34" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5273,7 +5556,7 @@
       <c r="E35" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="F35" s="64" t="n">
+      <c r="F35" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5297,7 +5580,7 @@
       <c r="E36" s="57" t="n">
         <v>125</v>
       </c>
-      <c r="F36" s="64" t="n">
+      <c r="F36" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5321,7 +5604,7 @@
       <c r="E37" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="F37" s="64" t="n">
+      <c r="F37" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5345,7 +5628,7 @@
       <c r="E38" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F38" s="64" t="n">
+      <c r="F38" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5369,7 +5652,7 @@
       <c r="E39" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F39" s="64" t="n">
+      <c r="F39" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5393,7 +5676,7 @@
       <c r="E40" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="F40" s="64" t="n">
+      <c r="F40" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5417,7 +5700,7 @@
       <c r="E41" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F41" s="64" t="n">
+      <c r="F41" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5441,7 +5724,7 @@
       <c r="E42" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="F42" s="64" t="n">
+      <c r="F42" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5465,7 +5748,7 @@
       <c r="E43" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="F43" s="64" t="n">
+      <c r="F43" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5489,7 +5772,7 @@
       <c r="E44" s="57" t="n">
         <v>145</v>
       </c>
-      <c r="F44" s="64" t="n">
+      <c r="F44" s="62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5513,7 +5796,7 @@
       <c r="E45" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="F45" s="64" t="n">
+      <c r="F45" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5537,7 +5820,7 @@
       <c r="E46" s="57" t="n">
         <v>130</v>
       </c>
-      <c r="F46" s="64" t="n">
+      <c r="F46" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5547,7 +5830,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>сайт медцентра</t>
+          <t>сайт ветклиники</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -5556,13 +5839,13 @@
         </is>
       </c>
       <c r="D47" s="56" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E47" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F47" s="64" t="n">
-        <v>4</v>
+        <v>105</v>
+      </c>
+      <c r="F47" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -5571,21 +5854,21 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>сайт ветклиники</t>
+          <t>сайт автосервиса</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>H. Медицина</t>
+          <t>I. Авто</t>
         </is>
       </c>
       <c r="D48" s="56" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E48" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F48" s="64" t="n">
+        <v>85</v>
+      </c>
+      <c r="F48" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5595,7 +5878,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>сайт автосервиса</t>
+          <t>сайт шиномонтажа</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -5604,12 +5887,12 @@
         </is>
       </c>
       <c r="D49" s="56" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E49" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F49" s="64" t="n">
+        <v>65</v>
+      </c>
+      <c r="F49" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5619,7 +5902,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>сайт автосалона</t>
+          <t>сайт детейлинга</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -5628,13 +5911,13 @@
         </is>
       </c>
       <c r="D50" s="56" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E50" s="57" t="n">
-        <v>115</v>
-      </c>
-      <c r="F50" s="64" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="F50" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -5643,22 +5926,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>сайт шиномонтажа</t>
+          <t>сайт агентства недвижимости</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D51" s="56" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="E51" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F51" s="64" t="n">
-        <v>5</v>
+        <v>125</v>
+      </c>
+      <c r="F51" s="62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -5667,21 +5950,21 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>сайт детейлинга</t>
+          <t>сайт риэлтора</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>I. Авто</t>
+          <t>J. Недв</t>
         </is>
       </c>
       <c r="D52" s="56" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F52" s="64" t="n">
+        <v>95</v>
+      </c>
+      <c r="F52" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5691,22 +5974,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>сайт агентства недвижимости</t>
+          <t>сайт психолога</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D53" s="56" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E53" s="57" t="n">
-        <v>125</v>
-      </c>
-      <c r="F53" s="64" t="n">
-        <v>4</v>
+        <v>95</v>
+      </c>
+      <c r="F53" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -5715,21 +5998,21 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>сайт риэлтора</t>
+          <t>сайт репетитора</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D54" s="56" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E54" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F54" s="64" t="n">
+        <v>75</v>
+      </c>
+      <c r="F54" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5739,22 +6022,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>сайт жк</t>
+          <t>сайт онлайн школы</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D55" s="56" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E55" s="57" t="n">
-        <v>175</v>
-      </c>
-      <c r="F55" s="65" t="n">
-        <v>3</v>
+        <v>105</v>
+      </c>
+      <c r="F55" s="62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -5763,22 +6046,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>сайт застройщика</t>
+          <t>сайт коуча</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>J. Недв</t>
+          <t>K. Образ</t>
         </is>
       </c>
       <c r="D56" s="56" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E56" s="57" t="n">
-        <v>145</v>
-      </c>
-      <c r="F56" s="64" t="n">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="F56" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -5787,7 +6070,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>сайт психолога</t>
+          <t>сайт фитнес тренера</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -5796,12 +6079,12 @@
         </is>
       </c>
       <c r="D57" s="56" t="n">
-        <v>2500</v>
+        <v>700</v>
       </c>
       <c r="E57" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F57" s="64" t="n">
+        <v>75</v>
+      </c>
+      <c r="F57" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5811,22 +6094,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>сайт репетитора</t>
+          <t>простой сайт сделать</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D58" s="56" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F58" s="64" t="n">
-        <v>5</v>
+        <v>70</v>
+      </c>
+      <c r="F58" s="62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -5835,22 +6118,22 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>сайт онлайн школы</t>
+          <t>сайт за день</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D59" s="56" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="F59" s="64" t="n">
-        <v>4</v>
+        <v>95</v>
+      </c>
+      <c r="F59" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -5859,12 +6142,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>сайт коуча</t>
+          <t>сайт быстро недорого</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D60" s="56" t="n">
@@ -5873,7 +6156,7 @@
       <c r="E60" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="F60" s="64" t="n">
+      <c r="F60" s="62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5883,22 +6166,22 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>сайт фитнес тренера</t>
+          <t>сайт визитка дёшево</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>K. Образ</t>
+          <t>L. Pain ★</t>
         </is>
       </c>
       <c r="D61" s="56" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E61" s="57" t="n">
-        <v>75</v>
-      </c>
-      <c r="F61" s="64" t="n">
-        <v>5</v>
+        <v>55</v>
+      </c>
+      <c r="F61" s="62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -5907,7 +6190,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>простой сайт сделать</t>
+          <t>сайт без знаний программирования</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5916,13 +6199,13 @@
         </is>
       </c>
       <c r="D62" s="56" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E62" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F62" s="64" t="n">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="F62" s="62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -5931,7 +6214,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>сайт за день</t>
+          <t>сделать сайт самому без программиста</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5940,871 +6223,775 @@
         </is>
       </c>
       <c r="D63" s="56" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E63" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="F63" s="64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F63" s="62" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
+    <row r="65">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО · 59 ключей</t>
+        </is>
+      </c>
+      <c r="D65" s="63">
+        <f>SUM(D5:D64)</f>
+        <v/>
+      </c>
+      <c r="E65" s="64">
+        <f>AVERAGE(E5:E64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>ВОРОНКА 100К ₽ → ПЛАТЯЩИЕ КЛИЕНТЫ · 4 СЦЕНАРИЯ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Бюджет ₽/мес</t>
+        </is>
+      </c>
+      <c r="B70" s="40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>← поменяй число — пересчитается всё ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Цена клика ₽</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Кликов = визитов</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Цена визита ₽</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Конверсия посадочной</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Регистраций на пробник</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Пробник → платящий</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Платящих/мес</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Стоимость привлечения ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>А. Cold start M2 (clean targeting)</t>
+        </is>
+      </c>
+      <c r="B73" s="40" t="n">
+        <v>85</v>
+      </c>
+      <c r="C73" s="16">
+        <f>$B$70/B73</f>
+        <v/>
+      </c>
+      <c r="D73" s="43">
+        <f>B73</f>
+        <v/>
+      </c>
+      <c r="E73" s="65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F73" s="16">
+        <f>C73*E73</f>
+        <v/>
+      </c>
+      <c r="G73" s="65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H73" s="66">
+        <f>F73*G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="59">
+        <f>$B$70/H73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Б. Базовая оптимизация M3</t>
+        </is>
+      </c>
+      <c r="B74" s="40" t="n">
+        <v>75</v>
+      </c>
+      <c r="C74" s="16">
+        <f>$B$70/B74</f>
+        <v/>
+      </c>
+      <c r="D74" s="43">
+        <f>B74</f>
+        <v/>
+      </c>
+      <c r="E74" s="65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F74" s="16">
+        <f>C74*E74</f>
+        <v/>
+      </c>
+      <c r="G74" s="65" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H74" s="66">
+        <f>F74*G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="59">
+        <f>$B$70/H74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>В. Vertical landing pages M4</t>
+        </is>
+      </c>
+      <c r="B75" s="40" t="n">
+        <v>65</v>
+      </c>
+      <c r="C75" s="16">
+        <f>$B$70/B75</f>
+        <v/>
+      </c>
+      <c r="D75" s="43">
+        <f>B75</f>
+        <v/>
+      </c>
+      <c r="E75" s="65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F75" s="16">
+        <f>C75*E75</f>
+        <v/>
+      </c>
+      <c r="G75" s="65" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H75" s="66">
+        <f>F75*G75</f>
+        <v/>
+      </c>
+      <c r="I75" s="53">
+        <f>$B$70/H75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Г. Зрелая воронка M5+</t>
+        </is>
+      </c>
+      <c r="B76" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>сайт быстро недорого</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D64" s="56" t="n">
-        <v>800</v>
-      </c>
-      <c r="E64" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="F64" s="64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>сайт визитка дёшево</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D65" s="56" t="n">
-        <v>800</v>
-      </c>
-      <c r="E65" s="57" t="n">
-        <v>55</v>
-      </c>
-      <c r="F65" s="64" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>сайт без знаний программирования</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D66" s="56" t="n">
-        <v>600</v>
-      </c>
-      <c r="E66" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="F66" s="64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>сделать сайт самому без программиста</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>L. Pain ★</t>
-        </is>
-      </c>
-      <c r="D67" s="56" t="n">
-        <v>400</v>
-      </c>
-      <c r="E67" s="57" t="n">
-        <v>60</v>
-      </c>
-      <c r="F67" s="64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО · 63 ключей</t>
-        </is>
-      </c>
-      <c r="D69" s="66">
-        <f>SUM(D5:D68)</f>
-        <v/>
-      </c>
-      <c r="E69" s="67">
-        <f>AVERAGE(E5:E68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>ВОРОНКА 100К ₽ → ПЛАТЯЩИЕ КЛИЕНТЫ · 4 СЦЕНАРИЯ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Бюджет ₽/мес</t>
-        </is>
-      </c>
-      <c r="B74" s="40" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>← поменяй число — пересчитается всё ниже</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Сценарий</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Цена клика ₽</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>Кликов = визитов</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Цена визита ₽</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Конверсия посадочной</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Регистраций на пробник</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>Пробник → платящий</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Платящих/мес</t>
-        </is>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>Стоимость привлечения ₽</t>
-        </is>
+      <c r="C76" s="16">
+        <f>$B$70/B76</f>
+        <v/>
+      </c>
+      <c r="D76" s="43">
+        <f>B76</f>
+        <v/>
+      </c>
+      <c r="E76" s="65" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F76" s="16">
+        <f>C76*E76</f>
+        <v/>
+      </c>
+      <c r="G76" s="65" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H76" s="66">
+        <f>F76*G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="53">
+        <f>$B$70/H76</f>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>А. Cold start M2 (clean targeting)</t>
+          <t>Д. Идеал M6+ (LTV/CAC 2.4)</t>
         </is>
       </c>
       <c r="B77" s="40" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C77" s="16">
-        <f>$B$74/B77</f>
+        <f>$B$70/B77</f>
         <v/>
       </c>
       <c r="D77" s="43">
         <f>B77</f>
         <v/>
       </c>
-      <c r="E77" s="68" t="n">
-        <v>0.04</v>
+      <c r="E77" s="65" t="n">
+        <v>0.08</v>
       </c>
       <c r="F77" s="16">
         <f>C77*E77</f>
         <v/>
       </c>
-      <c r="G77" s="68" t="n">
+      <c r="G77" s="65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H77" s="66">
+        <f>F77*G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="53">
+        <f>$B$70/H77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>ГРАФИК ПЕРВЫХ 6 МЕСЯЦЕВ НА 100К ₽/мес DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Что происходит</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Цена клика ₽</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Конв. посадочной</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Прб → Плт</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Кликов</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Пробников</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Платящих</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Стоимость привлечения ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>M1 Soft launch (без рекламы)</t>
+        </is>
+      </c>
+      <c r="C83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>M2 Cold start (clean targeting)</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="n">
+        <v>85</v>
+      </c>
+      <c r="D84" s="69" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E84" s="69" t="n">
         <v>0.06</v>
       </c>
-      <c r="H77" s="69">
-        <f>F77*G77</f>
-        <v/>
-      </c>
-      <c r="I77" s="59">
-        <f>$B$74/H77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Б. Базовая оптимизация M3</t>
-        </is>
-      </c>
-      <c r="B78" s="40" t="n">
+      <c r="F84" s="16">
+        <f>$B$70/C84</f>
+        <v/>
+      </c>
+      <c r="G84" s="16">
+        <f>F84*D84</f>
+        <v/>
+      </c>
+      <c r="H84" s="66">
+        <f>G84*E84</f>
+        <v/>
+      </c>
+      <c r="I84" s="43">
+        <f>$B$70/H84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>M3 Первая оптимизация</t>
+        </is>
+      </c>
+      <c r="C85" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="C78" s="16">
-        <f>$B$74/B78</f>
-        <v/>
-      </c>
-      <c r="D78" s="43">
-        <f>B78</f>
-        <v/>
-      </c>
-      <c r="E78" s="68" t="n">
+      <c r="D85" s="69" t="n">
         <v>0.05</v>
       </c>
-      <c r="F78" s="16">
-        <f>C78*E78</f>
-        <v/>
-      </c>
-      <c r="G78" s="68" t="n">
+      <c r="E85" s="69" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H78" s="69">
-        <f>F78*G78</f>
-        <v/>
-      </c>
-      <c r="I78" s="59">
-        <f>$B$74/H78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>В. Vertical landing pages M4</t>
-        </is>
-      </c>
-      <c r="B79" s="40" t="n">
+      <c r="F85" s="16">
+        <f>$B$70/C85</f>
+        <v/>
+      </c>
+      <c r="G85" s="16">
+        <f>F85*D85</f>
+        <v/>
+      </c>
+      <c r="H85" s="66">
+        <f>G85*E85</f>
+        <v/>
+      </c>
+      <c r="I85" s="43">
+        <f>$B$70/H85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>M4 Vertical landing pages</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="C79" s="16">
-        <f>$B$74/B79</f>
-        <v/>
-      </c>
-      <c r="D79" s="43">
-        <f>B79</f>
-        <v/>
-      </c>
-      <c r="E79" s="68" t="n">
+      <c r="D86" s="69" t="n">
         <v>0.06</v>
       </c>
-      <c r="F79" s="16">
-        <f>C79*E79</f>
-        <v/>
-      </c>
-      <c r="G79" s="68" t="n">
+      <c r="E86" s="69" t="n">
         <v>0.08</v>
       </c>
-      <c r="H79" s="69">
-        <f>F79*G79</f>
-        <v/>
-      </c>
-      <c r="I79" s="53">
-        <f>$B$74/H79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Г. Зрелая воронка M5+</t>
-        </is>
-      </c>
-      <c r="B80" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="C80" s="16">
-        <f>$B$74/B80</f>
-        <v/>
-      </c>
-      <c r="D80" s="43">
-        <f>B80</f>
-        <v/>
-      </c>
-      <c r="E80" s="68" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F80" s="16">
-        <f>C80*E80</f>
-        <v/>
-      </c>
-      <c r="G80" s="68" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H80" s="69">
-        <f>F80*G80</f>
-        <v/>
-      </c>
-      <c r="I80" s="53">
-        <f>$B$74/H80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Д. Идеал M6+ (LTV/CAC 2.4)</t>
-        </is>
-      </c>
-      <c r="B81" s="40" t="n">
-        <v>55</v>
-      </c>
-      <c r="C81" s="16">
-        <f>$B$74/B81</f>
-        <v/>
-      </c>
-      <c r="D81" s="43">
-        <f>B81</f>
-        <v/>
-      </c>
-      <c r="E81" s="68" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F81" s="16">
-        <f>C81*E81</f>
-        <v/>
-      </c>
-      <c r="G81" s="68" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H81" s="69">
-        <f>F81*G81</f>
-        <v/>
-      </c>
-      <c r="I81" s="53">
-        <f>$B$74/H81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>ГРАФИК ПЕРВЫХ 6 МЕСЯЦЕВ НА 100К ₽/мес DIRECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Что происходит</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>Цена клика ₽</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Конв. посадочной</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>Прб → Плт</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>Кликов</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>Пробников</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Платящих</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Стоимость привлечения ₽</t>
-        </is>
+      <c r="F86" s="16">
+        <f>$B$70/C86</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>F86*D86</f>
+        <v/>
+      </c>
+      <c r="H86" s="66">
+        <f>G86*E86</f>
+        <v/>
+      </c>
+      <c r="I86" s="43">
+        <f>$B$70/H86</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>M1 Soft launch (без рекламы)</t>
-        </is>
-      </c>
-      <c r="C87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H87" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>M5 Retargeting + узнаваемость</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="D87" s="69" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E87" s="69" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F87" s="16">
+        <f>$B$70/C87</f>
+        <v/>
+      </c>
+      <c r="G87" s="16">
+        <f>F87*D87</f>
+        <v/>
+      </c>
+      <c r="H87" s="66">
+        <f>G87*E87</f>
+        <v/>
+      </c>
+      <c r="I87" s="43">
+        <f>$B$70/H87</f>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>M2 Cold start (clean targeting)</t>
+          <t>M6 Зрелая воронка</t>
         </is>
       </c>
       <c r="C88" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="D88" s="72" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E88" s="72" t="n">
-        <v>0.06</v>
+        <v>55</v>
+      </c>
+      <c r="D88" s="69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E88" s="69" t="n">
+        <v>0.1</v>
       </c>
       <c r="F88" s="16">
-        <f>$B$74/C88</f>
+        <f>$B$70/C88</f>
         <v/>
       </c>
       <c r="G88" s="16">
         <f>F88*D88</f>
         <v/>
       </c>
-      <c r="H88" s="69">
+      <c r="H88" s="66">
         <f>G88*E88</f>
         <v/>
       </c>
       <c r="I88" s="43">
-        <f>$B$74/H88</f>
+        <f>$B$70/H88</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО за 6 мес (новых платящих)</t>
+        </is>
+      </c>
+      <c r="H89" s="70">
+        <f>SUM(H83:H88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>РАСХОЖДЕНИЕ С ФИНПЛАНОМ (лист 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>По финплану</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>По воронке Direct 100К</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Дельта</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Что компенсирует</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C96" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="68" t="inlineStr">
+        <is>
+          <t>−27</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Multi-channel + soft-launch buzz → 8-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>M3 Первая оптимизация</t>
-        </is>
-      </c>
-      <c r="C89" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="D89" s="72" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E89" s="72" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F89" s="16">
-        <f>$B$74/C89</f>
-        <v/>
-      </c>
-      <c r="G89" s="16">
-        <f>F89*D89</f>
-        <v/>
-      </c>
-      <c r="H89" s="69">
-        <f>G89*E89</f>
-        <v/>
-      </c>
-      <c r="I89" s="43">
-        <f>$B$74/H89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="33" t="inlineStr">
+      <c r="B97" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="C97" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" s="68" t="inlineStr">
+        <is>
+          <t>−75</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>VC.ru/Habr статья + первые кейсы → 25-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>M4 Vertical landing pages</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="D90" s="72" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E90" s="72" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F90" s="16">
-        <f>$B$74/C90</f>
-        <v/>
-      </c>
-      <c r="G90" s="16">
-        <f>F90*D90</f>
-        <v/>
-      </c>
-      <c r="H90" s="69">
-        <f>G90*E90</f>
-        <v/>
-      </c>
-      <c r="I90" s="43">
-        <f>$B$74/H90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="33" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>M5 Retargeting + узнаваемость</t>
-        </is>
-      </c>
-      <c r="C91" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="D91" s="72" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E91" s="72" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F91" s="16">
-        <f>$B$74/C91</f>
-        <v/>
-      </c>
-      <c r="G91" s="16">
-        <f>F91*D91</f>
-        <v/>
-      </c>
-      <c r="H91" s="69">
-        <f>G91*E91</f>
-        <v/>
-      </c>
-      <c r="I91" s="43">
-        <f>$B$74/H91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="33" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>M6 Зрелая воронка</t>
-        </is>
-      </c>
-      <c r="C92" s="43" t="n">
-        <v>55</v>
-      </c>
-      <c r="D92" s="72" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E92" s="72" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F92" s="16">
-        <f>$B$74/C92</f>
-        <v/>
-      </c>
-      <c r="G92" s="16">
-        <f>F92*D92</f>
-        <v/>
-      </c>
-      <c r="H92" s="69">
-        <f>G92*E92</f>
-        <v/>
-      </c>
-      <c r="I92" s="43">
-        <f>$B$74/H92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО за 6 мес (новых платящих)</t>
-        </is>
-      </c>
-      <c r="H93" s="73">
-        <f>SUM(H87:H92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>РАСХОЖДЕНИЕ С ФИНПЛАНОМ (лист 15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>По финплану</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>По воронке Direct 100К</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Дельта</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>Что компенсирует</t>
+      <c r="B98" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C98" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" s="68" t="inlineStr">
+        <is>
+          <t>−143</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Vertical lendings + B2B sales → 65-85</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="33" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B99" s="16" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C99" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="62" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>11</v>
+      </c>
+      <c r="D99" s="68" t="inlineStr">
+        <is>
+          <t>−240</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Retargeting + узнаваемость → 150-180</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="33" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B100" s="16" t="n">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="C100" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D100" s="71" t="inlineStr">
-        <is>
-          <t>−27</t>
+        <v>15</v>
+      </c>
+      <c r="D100" s="68" t="inlineStr">
+        <is>
+          <t>−365</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Multi-channel + soft-launch buzz → 8-12</t>
+          <t>Зрелая воронка → 280-320</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="33" t="inlineStr">
         <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="C101" s="16" t="n">
-        <v>5</v>
+          <t>M7+</t>
+        </is>
+      </c>
+      <c r="B101" s="67" t="inlineStr">
+        <is>
+          <t>540+</t>
+        </is>
+      </c>
+      <c r="C101" s="67" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
       </c>
       <c r="D101" s="71" t="inlineStr">
         <is>
-          <t>−75</t>
+          <t>догоняет</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>VC.ru/Habr статья + первые кейсы → 25-35</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="33" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="C102" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D102" s="71" t="inlineStr">
-        <is>
-          <t>−143</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Vertical lendings + B2B sales → 65-85</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="33" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="C103" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D103" s="71" t="inlineStr">
-        <is>
-          <t>−240</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Retargeting + узнаваемость → 150-180</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="33" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="n">
-        <v>380</v>
-      </c>
-      <c r="C104" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D104" s="71" t="inlineStr">
-        <is>
-          <t>−365</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Зрелая воронка → 280-320</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="33" t="inlineStr">
-        <is>
-          <t>M7+</t>
-        </is>
-      </c>
-      <c r="B105" s="70" t="inlineStr">
-        <is>
-          <t>540+</t>
-        </is>
-      </c>
-      <c r="C105" s="70" t="inlineStr">
-        <is>
-          <t>20-30</t>
-        </is>
-      </c>
-      <c r="D105" s="62" t="inlineStr">
-        <is>
-          <t>догоняет</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
           <t>Бренд + кейсы + органика</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="74" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="72" t="inlineStr">
         <is>
           <t>ВЫВОД: 100К ₽ ТОЛЬКО на ЧИСТЫХ запросах в Direct в первый месяц = 3 платящих (vs 1 на грязном ядре). Грязные запросы (тильда / создать сайт / сайт бесплатно) — это freebie hunters и loyalty конкурентов, downstream conversion 0.5-1%. На чистых vertical / AI / pain ключах CV лендинга +60% и Trial→Paid +20%. Финплан М2=30 требует мульти-канал (Direct 60К + VK 25К + Telegram 15К → 8-12) + buzz (VC.ru → +14).</t>
         </is>
@@ -6812,7 +6999,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A104:I104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
